--- a/gratis/archivos/control-ventas-gastos/Control_de_Ventas_y_Gastos_MixShopDigital.xlsx
+++ b/gratis/archivos/control-ventas-gastos/Control_de_Ventas_y_Gastos_MixShopDigital.xlsx
@@ -42,7 +42,7 @@
     <numFmt numFmtId="167" formatCode="0%;-0%;0%"/>
     <numFmt numFmtId="168" formatCode="0.0%;-0.0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,12 @@
       <name val="Arial"/>
       <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B2A7A"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -204,7 +210,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -231,6 +237,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7A00"/>
+        <bgColor rgb="00FF7A00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB800"/>
+        <bgColor rgb="00FFB800"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000094FB"/>
+        <bgColor rgb="000094FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF3CC"/>
         <bgColor rgb="00FFF3CC"/>
       </patternFill>
@@ -249,14 +279,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F8F7"/>
-        <bgColor rgb="00F2F8F7"/>
+        <fgColor rgb="002ECC40"/>
+        <bgColor rgb="002ECC40"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="008727E2"/>
+        <bgColor rgb="008727E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F8F7"/>
+        <bgColor rgb="00F2F8F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -318,12 +354,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -332,204 +369,209 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1162,6 +1204,121 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1474,69 +1631,86 @@
     <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>CONTROL DE VENTAS Y GASTOS</t>
         </is>
       </c>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Tu negocio, de un vistazo</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="11" t="n"/>
+      <c r="M3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>El panel se arma solo con lo que anotás en MOVIMIENTOS. No hace falta escribir nada acá, salvo elegir el período.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>+  Anotar movimientos</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Ajustes</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Ayuda</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Período a mirar:</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="12">
         <f>"Año de control: "&amp;AnioCtl&amp;"   ·   "&amp;NombreNegocio</f>
         <v/>
       </c>
@@ -1552,22 +1726,22 @@
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>INGRESOS DEL PERÍODO</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>GASTOS DEL PERÍODO</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="19" t="inlineStr">
         <is>
           <t>GANANCIA</t>
         </is>
       </c>
-      <c r="K8" s="14" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>MARGEN</t>
         </is>
@@ -1578,38 +1752,38 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="15">
+      <c r="B9" s="21">
         <f>IF(MesN=0,C29,INDEX(C17:C28,MesN))</f>
         <v/>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="22">
         <f>IF(MesN=0,D29,INDEX(D17:D28,MesN))</f>
         <v/>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="23">
         <f>B9-E9</f>
         <v/>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="24">
         <f>IF(B9=0,0,H9/B9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="19">
+      <c r="B10" s="25">
         <f>Moneda</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="26">
         <f>Moneda</f>
         <v/>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>ingresos − gastos</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr">
+      <c r="K10" s="28" t="inlineStr">
         <is>
           <t>qué parte de lo que vendés es ganancia</t>
         </is>
@@ -1617,629 +1791,629 @@
     </row>
     <row r="11" ht="8" customHeight="1"/>
     <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="23">
+      <c r="B12" s="29">
         <f>IF(AND(B9=0,E9=0),"Anotá tus primeros movimientos en la hoja MOVIMIENTOS para ver tu panel.",IF(H9&lt;0,"✖ Pérdida: gastaste más de lo que vendiste en este período.",IF(K9&lt;0.1,"⚠ Ganás poco: menos del 10 % de lo que vendés. Revisá tus gastos.","✔ Muy bien: te quedó el "&amp;ROUND(K9*100,1)&amp;" % de lo que vendiste.")))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Tu meta:</t>
         </is>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="30">
         <f>IF(MesN=0,MetaMes*12,MetaMes)</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="31">
         <f>IF(C13&lt;=0,0,MAX(0,MIN(1,H9/C13)))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>MES A MES</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>Ingresos</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>Gastos</t>
         </is>
       </c>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>Ganancia</t>
         </is>
       </c>
-      <c r="F16" s="27" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>Acumulado</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Enero</t>
         </is>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,1,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,2,1))</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,1,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,2,1))</f>
         <v/>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="36">
         <f>C17-D17</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="37">
         <f>SUM($E$17:E17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>Febrero</t>
         </is>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,2,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,3,1))</f>
         <v/>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,2,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,3,1))</f>
         <v/>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="40">
         <f>C18-D18</f>
         <v/>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="41">
         <f>SUM($E$17:E18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Marzo</t>
         </is>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,3,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,4,1))</f>
         <v/>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,3,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,4,1))</f>
         <v/>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="36">
         <f>C19-D19</f>
         <v/>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="37">
         <f>SUM($E$17:E19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t>Abril</t>
         </is>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,4,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,5,1))</f>
         <v/>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,4,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,5,1))</f>
         <v/>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="40">
         <f>C20-D20</f>
         <v/>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="41">
         <f>SUM($E$17:E20)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Mayo</t>
         </is>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,5,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,6,1))</f>
         <v/>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,5,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,6,1))</f>
         <v/>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="36">
         <f>C21-D21</f>
         <v/>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="37">
         <f>SUM($E$17:E21)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>Junio</t>
         </is>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,6,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,7,1))</f>
         <v/>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,6,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,7,1))</f>
         <v/>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="40">
         <f>C22-D22</f>
         <v/>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="41">
         <f>SUM($E$17:E22)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Julio</t>
         </is>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,7,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,8,1))</f>
         <v/>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,7,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,8,1))</f>
         <v/>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="36">
         <f>C23-D23</f>
         <v/>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="37">
         <f>SUM($E$17:E23)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>Agosto</t>
         </is>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,8,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,9,1))</f>
         <v/>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,8,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,9,1))</f>
         <v/>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="40">
         <f>C24-D24</f>
         <v/>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="41">
         <f>SUM($E$17:E24)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,9,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,10,1))</f>
         <v/>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,9,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,10,1))</f>
         <v/>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="36">
         <f>C25-D25</f>
         <v/>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="37">
         <f>SUM($E$17:E25)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>Octubre</t>
         </is>
       </c>
-      <c r="C26" s="33">
+      <c r="C26" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,10,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,11,1))</f>
         <v/>
       </c>
-      <c r="D26" s="33">
+      <c r="D26" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,10,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,11,1))</f>
         <v/>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="40">
         <f>C26-D26</f>
         <v/>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="41">
         <f>SUM($E$17:E26)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="28" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,11,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,12,1))</f>
         <v/>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="35">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,11,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,12,1))</f>
         <v/>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="36">
         <f>C27-D27</f>
         <v/>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="37">
         <f>SUM($E$17:E27)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Ingreso",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,12,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,13,1))</f>
         <v/>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="39">
         <f>SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;DATE(AnioCtl,12,1),'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;DATE(AnioCtl,13,1))</f>
         <v/>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="40">
         <f>C28-D28</f>
         <v/>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="41">
         <f>SUM($E$17:E28)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="42" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C29" s="37">
+      <c r="C29" s="43">
         <f>SUM(C17:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="37">
+      <c r="D29" s="43">
         <f>SUM(D17:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="37">
+      <c r="E29" s="43">
         <f>SUM(E17:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="37">
+      <c r="F29" s="43">
         <f>F28</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="44" t="inlineStr">
         <is>
           <t>¿EN QUÉ SE VA TU PLATA? (gastos del período elegido)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="27" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Categoría de gasto</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="39">
+      <c r="B33" s="45">
         <f>IF('AJUSTES'!$C$15="","",'AJUSTES'!$C$15)</f>
         <v/>
       </c>
-      <c r="D33" s="40">
+      <c r="D33" s="46">
         <f>IF(B33="",0,SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$D$7:$D$406,B33,'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;FIni,'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;FFin))</f>
         <v/>
       </c>
-      <c r="E33" s="41">
+      <c r="E33" s="47">
         <f>IF($E$9=0,0,D33/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="39">
+      <c r="B34" s="45">
         <f>IF('AJUSTES'!$C$16="","",'AJUSTES'!$C$16)</f>
         <v/>
       </c>
-      <c r="D34" s="40">
+      <c r="D34" s="46">
         <f>IF(B34="",0,SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$D$7:$D$406,B34,'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;FIni,'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;FFin))</f>
         <v/>
       </c>
-      <c r="E34" s="41">
+      <c r="E34" s="47">
         <f>IF($E$9=0,0,D34/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="39">
+      <c r="B35" s="45">
         <f>IF('AJUSTES'!$C$17="","",'AJUSTES'!$C$17)</f>
         <v/>
       </c>
-      <c r="D35" s="40">
+      <c r="D35" s="46">
         <f>IF(B35="",0,SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$D$7:$D$406,B35,'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;FIni,'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;FFin))</f>
         <v/>
       </c>
-      <c r="E35" s="41">
+      <c r="E35" s="47">
         <f>IF($E$9=0,0,D35/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="39">
+      <c r="B36" s="45">
         <f>IF('AJUSTES'!$C$18="","",'AJUSTES'!$C$18)</f>
         <v/>
       </c>
-      <c r="D36" s="40">
+      <c r="D36" s="46">
         <f>IF(B36="",0,SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$D$7:$D$406,B36,'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;FIni,'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;FFin))</f>
         <v/>
       </c>
-      <c r="E36" s="41">
+      <c r="E36" s="47">
         <f>IF($E$9=0,0,D36/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="39">
+      <c r="B37" s="45">
         <f>IF('AJUSTES'!$C$19="","",'AJUSTES'!$C$19)</f>
         <v/>
       </c>
-      <c r="D37" s="40">
+      <c r="D37" s="46">
         <f>IF(B37="",0,SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$D$7:$D$406,B37,'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;FIni,'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;FFin))</f>
         <v/>
       </c>
-      <c r="E37" s="41">
+      <c r="E37" s="47">
         <f>IF($E$9=0,0,D37/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="39">
+      <c r="B38" s="45">
         <f>IF('AJUSTES'!$C$20="","",'AJUSTES'!$C$20)</f>
         <v/>
       </c>
-      <c r="D38" s="40">
+      <c r="D38" s="46">
         <f>IF(B38="",0,SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$D$7:$D$406,B38,'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;FIni,'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;FFin))</f>
         <v/>
       </c>
-      <c r="E38" s="41">
+      <c r="E38" s="47">
         <f>IF($E$9=0,0,D38/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="39">
+      <c r="B39" s="45">
         <f>IF('AJUSTES'!$C$21="","",'AJUSTES'!$C$21)</f>
         <v/>
       </c>
-      <c r="D39" s="40">
+      <c r="D39" s="46">
         <f>IF(B39="",0,SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$D$7:$D$406,B39,'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;FIni,'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;FFin))</f>
         <v/>
       </c>
-      <c r="E39" s="41">
+      <c r="E39" s="47">
         <f>IF($E$9=0,0,D39/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="B40" s="39">
+      <c r="B40" s="45">
         <f>IF('AJUSTES'!$C$22="","",'AJUSTES'!$C$22)</f>
         <v/>
       </c>
-      <c r="D40" s="40">
+      <c r="D40" s="46">
         <f>IF(B40="",0,SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$D$7:$D$406,B40,'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;FIni,'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;FFin))</f>
         <v/>
       </c>
-      <c r="E40" s="41">
+      <c r="E40" s="47">
         <f>IF($E$9=0,0,D40/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="39">
+      <c r="B41" s="45">
         <f>IF('AJUSTES'!$C$23="","",'AJUSTES'!$C$23)</f>
         <v/>
       </c>
-      <c r="D41" s="40">
+      <c r="D41" s="46">
         <f>IF(B41="",0,SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$D$7:$D$406,B41,'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;FIni,'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;FFin))</f>
         <v/>
       </c>
-      <c r="E41" s="41">
+      <c r="E41" s="47">
         <f>IF($E$9=0,0,D41/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="39">
+      <c r="B42" s="45">
         <f>IF('AJUSTES'!$C$24="","",'AJUSTES'!$C$24)</f>
         <v/>
       </c>
-      <c r="D42" s="40">
+      <c r="D42" s="46">
         <f>IF(B42="",0,SUMIFS('MOVIMIENTOS'!$F$7:$F$406,'MOVIMIENTOS'!$C$7:$C$406,"Gasto",'MOVIMIENTOS'!$D$7:$D$406,B42,'MOVIMIENTOS'!$B$7:$B$406,"&gt;="&amp;FIni,'MOVIMIENTOS'!$B$7:$B$406,"&lt;"&amp;FFin))</f>
         <v/>
       </c>
-      <c r="E42" s="41">
+      <c r="E42" s="47">
         <f>IF($E$9=0,0,D42/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="42" t="inlineStr">
+      <c r="B43" s="48" t="inlineStr">
         <is>
           <t>Sin categoría / otras</t>
         </is>
       </c>
-      <c r="D43" s="40">
+      <c r="D43" s="46">
         <f>MAX(0,E9-SUM(D33:D42))</f>
         <v/>
       </c>
-      <c r="E43" s="41">
+      <c r="E43" s="47">
         <f>IF($E$9=0,0,D43/$E$9)</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="43" t="inlineStr">
+      <c r="B44" s="49" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D44" s="44">
+      <c r="D44" s="50">
         <f>SUM(D33:D43)</f>
         <v/>
       </c>
-      <c r="E44" s="45">
+      <c r="E44" s="51">
         <f>SUM(E33:E43)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="46" t="inlineStr">
+      <c r="B46" s="52" t="inlineStr">
         <is>
           <t>TU GANANCIA ACUMULADA Y PUNTOS CLAVE</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="I47" s="14" t="inlineStr">
+      <c r="I47" s="20" t="inlineStr">
         <is>
           <t>MEJOR MES</t>
         </is>
       </c>
-      <c r="L47" s="14" t="inlineStr">
+      <c r="L47" s="20" t="inlineStr">
         <is>
           <t>MAYOR GASTO</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="I48" s="47">
+      <c r="I48" s="53">
         <f>IF(MAX(E17:E28)&lt;=0,"-",INDEX(B17:B28,MATCH(MAX(E17:E28),E17:E28,0)))</f>
         <v/>
       </c>
-      <c r="L48" s="48">
+      <c r="L48" s="54">
         <f>IF(MAX(D33:D42)&lt;=0,"-",INDEX(B33:B42,MATCH(MAX(D33:D42),D33:D42,0)))</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="I49" s="22" t="inlineStr">
+      <c r="I49" s="28" t="inlineStr">
         <is>
           <t>el de mayor ganancia</t>
         </is>
       </c>
-      <c r="L49" s="22" t="inlineStr">
+      <c r="L49" s="28" t="inlineStr">
         <is>
           <t>en el período</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="I52" s="14" t="inlineStr">
+      <c r="I52" s="20" t="inlineStr">
         <is>
           <t>GANANCIA PROMEDIO POR MES</t>
         </is>
       </c>
-      <c r="L52" s="14" t="inlineStr">
+      <c r="L52" s="20" t="inlineStr">
         <is>
           <t>GANANCIA DEL AÑO</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="I53" s="49">
+      <c r="I53" s="55">
         <f>IFERROR(E29/SUMPRODUCT(--((C17:C28+D17:D28)&gt;0)),0)</f>
         <v/>
       </c>
-      <c r="L53" s="50">
+      <c r="L53" s="56">
         <f>E29</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="I54" s="22" t="inlineStr">
+      <c r="I54" s="28" t="inlineStr">
         <is>
           <t>meses con movimientos</t>
         </is>
       </c>
-      <c r="L54" s="22">
+      <c r="L54" s="28">
         <f>Moneda</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="I57" s="51" t="inlineStr">
+      <c r="I57" s="57" t="inlineStr">
         <is>
           <t>Consejo: anotá cada movimiento el mismo día. Así el panel siempre está al día.</t>
         </is>
@@ -2248,17 +2422,17 @@
     <row r="58"/>
     <row r="59"/>
     <row r="64" ht="8" customHeight="1">
-      <c r="B64" s="52" t="n"/>
+      <c r="B64" s="58" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="B65" s="53" t="inlineStr">
+      <c r="B65" s="59" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="B66" s="54" t="inlineStr">
+      <c r="B66" s="60" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Para gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY  →  mixshopdigital.com.py</t>
         </is>
@@ -2266,7 +2440,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="89C1"/>
-  <mergeCells count="58">
+  <mergeCells count="57">
     <mergeCell ref="I47:K47"/>
     <mergeCell ref="L48:M48"/>
     <mergeCell ref="E10:G10"/>
@@ -2310,7 +2484,6 @@
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="L52:M52"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B3:M3"/>
     <mergeCell ref="K9:M9"/>
     <mergeCell ref="B31:M31"/>
     <mergeCell ref="E8:G8"/>
@@ -2433,2890 +2606,2893 @@
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>MOVIMIENTOS</t>
         </is>
       </c>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Anotá cada venta y cada gasto</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>← PANEL</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Una fila por movimiento. Completá solamente las celdas amarillas. Podés ordenar y filtrar con la fila de títulos.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="56">
+      <c r="B5" s="62">
         <f>"Registros cargados: "&amp;COUNT(F7:F406)&amp;" de 400   ·   Ingresos del año: "&amp;FIXED(PANEL!C29,0)&amp;"   ·   Gastos del año: "&amp;FIXED(PANEL!D29,0)&amp;" "&amp;Moneda</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Detalle (opcional)</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="57" t="n"/>
-      <c r="C7" s="58" t="n"/>
-      <c r="D7" s="59" t="n"/>
-      <c r="E7" s="59" t="n"/>
-      <c r="F7" s="60" t="n"/>
+      <c r="B7" s="63" t="n"/>
+      <c r="C7" s="64" t="n"/>
+      <c r="D7" s="65" t="n"/>
+      <c r="E7" s="65" t="n"/>
+      <c r="F7" s="66" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="57" t="n"/>
-      <c r="C8" s="58" t="n"/>
-      <c r="D8" s="59" t="n"/>
-      <c r="E8" s="59" t="n"/>
-      <c r="F8" s="60" t="n"/>
+      <c r="B8" s="63" t="n"/>
+      <c r="C8" s="64" t="n"/>
+      <c r="D8" s="65" t="n"/>
+      <c r="E8" s="65" t="n"/>
+      <c r="F8" s="66" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="57" t="n"/>
-      <c r="C9" s="58" t="n"/>
-      <c r="D9" s="59" t="n"/>
-      <c r="E9" s="59" t="n"/>
-      <c r="F9" s="60" t="n"/>
+      <c r="B9" s="63" t="n"/>
+      <c r="C9" s="64" t="n"/>
+      <c r="D9" s="65" t="n"/>
+      <c r="E9" s="65" t="n"/>
+      <c r="F9" s="66" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="57" t="n"/>
-      <c r="C10" s="58" t="n"/>
-      <c r="D10" s="59" t="n"/>
-      <c r="E10" s="59" t="n"/>
-      <c r="F10" s="60" t="n"/>
+      <c r="B10" s="63" t="n"/>
+      <c r="C10" s="64" t="n"/>
+      <c r="D10" s="65" t="n"/>
+      <c r="E10" s="65" t="n"/>
+      <c r="F10" s="66" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="57" t="n"/>
-      <c r="C11" s="58" t="n"/>
-      <c r="D11" s="59" t="n"/>
-      <c r="E11" s="59" t="n"/>
-      <c r="F11" s="60" t="n"/>
+      <c r="B11" s="63" t="n"/>
+      <c r="C11" s="64" t="n"/>
+      <c r="D11" s="65" t="n"/>
+      <c r="E11" s="65" t="n"/>
+      <c r="F11" s="66" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="57" t="n"/>
-      <c r="C12" s="58" t="n"/>
-      <c r="D12" s="59" t="n"/>
-      <c r="E12" s="59" t="n"/>
-      <c r="F12" s="60" t="n"/>
+      <c r="B12" s="63" t="n"/>
+      <c r="C12" s="64" t="n"/>
+      <c r="D12" s="65" t="n"/>
+      <c r="E12" s="65" t="n"/>
+      <c r="F12" s="66" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="57" t="n"/>
-      <c r="C13" s="58" t="n"/>
-      <c r="D13" s="59" t="n"/>
-      <c r="E13" s="59" t="n"/>
-      <c r="F13" s="60" t="n"/>
+      <c r="B13" s="63" t="n"/>
+      <c r="C13" s="64" t="n"/>
+      <c r="D13" s="65" t="n"/>
+      <c r="E13" s="65" t="n"/>
+      <c r="F13" s="66" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="57" t="n"/>
-      <c r="C14" s="58" t="n"/>
-      <c r="D14" s="59" t="n"/>
-      <c r="E14" s="59" t="n"/>
-      <c r="F14" s="60" t="n"/>
+      <c r="B14" s="63" t="n"/>
+      <c r="C14" s="64" t="n"/>
+      <c r="D14" s="65" t="n"/>
+      <c r="E14" s="65" t="n"/>
+      <c r="F14" s="66" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="57" t="n"/>
-      <c r="C15" s="58" t="n"/>
-      <c r="D15" s="59" t="n"/>
-      <c r="E15" s="59" t="n"/>
-      <c r="F15" s="60" t="n"/>
+      <c r="B15" s="63" t="n"/>
+      <c r="C15" s="64" t="n"/>
+      <c r="D15" s="65" t="n"/>
+      <c r="E15" s="65" t="n"/>
+      <c r="F15" s="66" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="57" t="n"/>
-      <c r="C16" s="58" t="n"/>
-      <c r="D16" s="59" t="n"/>
-      <c r="E16" s="59" t="n"/>
-      <c r="F16" s="60" t="n"/>
+      <c r="B16" s="63" t="n"/>
+      <c r="C16" s="64" t="n"/>
+      <c r="D16" s="65" t="n"/>
+      <c r="E16" s="65" t="n"/>
+      <c r="F16" s="66" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="57" t="n"/>
-      <c r="C17" s="58" t="n"/>
-      <c r="D17" s="59" t="n"/>
-      <c r="E17" s="59" t="n"/>
-      <c r="F17" s="60" t="n"/>
+      <c r="B17" s="63" t="n"/>
+      <c r="C17" s="64" t="n"/>
+      <c r="D17" s="65" t="n"/>
+      <c r="E17" s="65" t="n"/>
+      <c r="F17" s="66" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="57" t="n"/>
-      <c r="C18" s="58" t="n"/>
-      <c r="D18" s="59" t="n"/>
-      <c r="E18" s="59" t="n"/>
-      <c r="F18" s="60" t="n"/>
+      <c r="B18" s="63" t="n"/>
+      <c r="C18" s="64" t="n"/>
+      <c r="D18" s="65" t="n"/>
+      <c r="E18" s="65" t="n"/>
+      <c r="F18" s="66" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="57" t="n"/>
-      <c r="C19" s="58" t="n"/>
-      <c r="D19" s="59" t="n"/>
-      <c r="E19" s="59" t="n"/>
-      <c r="F19" s="60" t="n"/>
+      <c r="B19" s="63" t="n"/>
+      <c r="C19" s="64" t="n"/>
+      <c r="D19" s="65" t="n"/>
+      <c r="E19" s="65" t="n"/>
+      <c r="F19" s="66" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="57" t="n"/>
-      <c r="C20" s="58" t="n"/>
-      <c r="D20" s="59" t="n"/>
-      <c r="E20" s="59" t="n"/>
-      <c r="F20" s="60" t="n"/>
+      <c r="B20" s="63" t="n"/>
+      <c r="C20" s="64" t="n"/>
+      <c r="D20" s="65" t="n"/>
+      <c r="E20" s="65" t="n"/>
+      <c r="F20" s="66" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="57" t="n"/>
-      <c r="C21" s="58" t="n"/>
-      <c r="D21" s="59" t="n"/>
-      <c r="E21" s="59" t="n"/>
-      <c r="F21" s="60" t="n"/>
+      <c r="B21" s="63" t="n"/>
+      <c r="C21" s="64" t="n"/>
+      <c r="D21" s="65" t="n"/>
+      <c r="E21" s="65" t="n"/>
+      <c r="F21" s="66" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="57" t="n"/>
-      <c r="C22" s="58" t="n"/>
-      <c r="D22" s="59" t="n"/>
-      <c r="E22" s="59" t="n"/>
-      <c r="F22" s="60" t="n"/>
+      <c r="B22" s="63" t="n"/>
+      <c r="C22" s="64" t="n"/>
+      <c r="D22" s="65" t="n"/>
+      <c r="E22" s="65" t="n"/>
+      <c r="F22" s="66" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="57" t="n"/>
-      <c r="C23" s="58" t="n"/>
-      <c r="D23" s="59" t="n"/>
-      <c r="E23" s="59" t="n"/>
-      <c r="F23" s="60" t="n"/>
+      <c r="B23" s="63" t="n"/>
+      <c r="C23" s="64" t="n"/>
+      <c r="D23" s="65" t="n"/>
+      <c r="E23" s="65" t="n"/>
+      <c r="F23" s="66" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="57" t="n"/>
-      <c r="C24" s="58" t="n"/>
-      <c r="D24" s="59" t="n"/>
-      <c r="E24" s="59" t="n"/>
-      <c r="F24" s="60" t="n"/>
+      <c r="B24" s="63" t="n"/>
+      <c r="C24" s="64" t="n"/>
+      <c r="D24" s="65" t="n"/>
+      <c r="E24" s="65" t="n"/>
+      <c r="F24" s="66" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="57" t="n"/>
-      <c r="C25" s="58" t="n"/>
-      <c r="D25" s="59" t="n"/>
-      <c r="E25" s="59" t="n"/>
-      <c r="F25" s="60" t="n"/>
+      <c r="B25" s="63" t="n"/>
+      <c r="C25" s="64" t="n"/>
+      <c r="D25" s="65" t="n"/>
+      <c r="E25" s="65" t="n"/>
+      <c r="F25" s="66" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="57" t="n"/>
-      <c r="C26" s="58" t="n"/>
-      <c r="D26" s="59" t="n"/>
-      <c r="E26" s="59" t="n"/>
-      <c r="F26" s="60" t="n"/>
+      <c r="B26" s="63" t="n"/>
+      <c r="C26" s="64" t="n"/>
+      <c r="D26" s="65" t="n"/>
+      <c r="E26" s="65" t="n"/>
+      <c r="F26" s="66" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="57" t="n"/>
-      <c r="C27" s="58" t="n"/>
-      <c r="D27" s="59" t="n"/>
-      <c r="E27" s="59" t="n"/>
-      <c r="F27" s="60" t="n"/>
+      <c r="B27" s="63" t="n"/>
+      <c r="C27" s="64" t="n"/>
+      <c r="D27" s="65" t="n"/>
+      <c r="E27" s="65" t="n"/>
+      <c r="F27" s="66" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="57" t="n"/>
-      <c r="C28" s="58" t="n"/>
-      <c r="D28" s="59" t="n"/>
-      <c r="E28" s="59" t="n"/>
-      <c r="F28" s="60" t="n"/>
+      <c r="B28" s="63" t="n"/>
+      <c r="C28" s="64" t="n"/>
+      <c r="D28" s="65" t="n"/>
+      <c r="E28" s="65" t="n"/>
+      <c r="F28" s="66" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="57" t="n"/>
-      <c r="C29" s="58" t="n"/>
-      <c r="D29" s="59" t="n"/>
-      <c r="E29" s="59" t="n"/>
-      <c r="F29" s="60" t="n"/>
+      <c r="B29" s="63" t="n"/>
+      <c r="C29" s="64" t="n"/>
+      <c r="D29" s="65" t="n"/>
+      <c r="E29" s="65" t="n"/>
+      <c r="F29" s="66" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="57" t="n"/>
-      <c r="C30" s="58" t="n"/>
-      <c r="D30" s="59" t="n"/>
-      <c r="E30" s="59" t="n"/>
-      <c r="F30" s="60" t="n"/>
+      <c r="B30" s="63" t="n"/>
+      <c r="C30" s="64" t="n"/>
+      <c r="D30" s="65" t="n"/>
+      <c r="E30" s="65" t="n"/>
+      <c r="F30" s="66" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="57" t="n"/>
-      <c r="C31" s="58" t="n"/>
-      <c r="D31" s="59" t="n"/>
-      <c r="E31" s="59" t="n"/>
-      <c r="F31" s="60" t="n"/>
+      <c r="B31" s="63" t="n"/>
+      <c r="C31" s="64" t="n"/>
+      <c r="D31" s="65" t="n"/>
+      <c r="E31" s="65" t="n"/>
+      <c r="F31" s="66" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="57" t="n"/>
-      <c r="C32" s="58" t="n"/>
-      <c r="D32" s="59" t="n"/>
-      <c r="E32" s="59" t="n"/>
-      <c r="F32" s="60" t="n"/>
+      <c r="B32" s="63" t="n"/>
+      <c r="C32" s="64" t="n"/>
+      <c r="D32" s="65" t="n"/>
+      <c r="E32" s="65" t="n"/>
+      <c r="F32" s="66" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="57" t="n"/>
-      <c r="C33" s="58" t="n"/>
-      <c r="D33" s="59" t="n"/>
-      <c r="E33" s="59" t="n"/>
-      <c r="F33" s="60" t="n"/>
+      <c r="B33" s="63" t="n"/>
+      <c r="C33" s="64" t="n"/>
+      <c r="D33" s="65" t="n"/>
+      <c r="E33" s="65" t="n"/>
+      <c r="F33" s="66" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="57" t="n"/>
-      <c r="C34" s="58" t="n"/>
-      <c r="D34" s="59" t="n"/>
-      <c r="E34" s="59" t="n"/>
-      <c r="F34" s="60" t="n"/>
+      <c r="B34" s="63" t="n"/>
+      <c r="C34" s="64" t="n"/>
+      <c r="D34" s="65" t="n"/>
+      <c r="E34" s="65" t="n"/>
+      <c r="F34" s="66" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="57" t="n"/>
-      <c r="C35" s="58" t="n"/>
-      <c r="D35" s="59" t="n"/>
-      <c r="E35" s="59" t="n"/>
-      <c r="F35" s="60" t="n"/>
+      <c r="B35" s="63" t="n"/>
+      <c r="C35" s="64" t="n"/>
+      <c r="D35" s="65" t="n"/>
+      <c r="E35" s="65" t="n"/>
+      <c r="F35" s="66" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="57" t="n"/>
-      <c r="C36" s="58" t="n"/>
-      <c r="D36" s="59" t="n"/>
-      <c r="E36" s="59" t="n"/>
-      <c r="F36" s="60" t="n"/>
+      <c r="B36" s="63" t="n"/>
+      <c r="C36" s="64" t="n"/>
+      <c r="D36" s="65" t="n"/>
+      <c r="E36" s="65" t="n"/>
+      <c r="F36" s="66" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="57" t="n"/>
-      <c r="C37" s="58" t="n"/>
-      <c r="D37" s="59" t="n"/>
-      <c r="E37" s="59" t="n"/>
-      <c r="F37" s="60" t="n"/>
+      <c r="B37" s="63" t="n"/>
+      <c r="C37" s="64" t="n"/>
+      <c r="D37" s="65" t="n"/>
+      <c r="E37" s="65" t="n"/>
+      <c r="F37" s="66" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="57" t="n"/>
-      <c r="C38" s="58" t="n"/>
-      <c r="D38" s="59" t="n"/>
-      <c r="E38" s="59" t="n"/>
-      <c r="F38" s="60" t="n"/>
+      <c r="B38" s="63" t="n"/>
+      <c r="C38" s="64" t="n"/>
+      <c r="D38" s="65" t="n"/>
+      <c r="E38" s="65" t="n"/>
+      <c r="F38" s="66" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="57" t="n"/>
-      <c r="C39" s="58" t="n"/>
-      <c r="D39" s="59" t="n"/>
-      <c r="E39" s="59" t="n"/>
-      <c r="F39" s="60" t="n"/>
+      <c r="B39" s="63" t="n"/>
+      <c r="C39" s="64" t="n"/>
+      <c r="D39" s="65" t="n"/>
+      <c r="E39" s="65" t="n"/>
+      <c r="F39" s="66" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="57" t="n"/>
-      <c r="C40" s="58" t="n"/>
-      <c r="D40" s="59" t="n"/>
-      <c r="E40" s="59" t="n"/>
-      <c r="F40" s="60" t="n"/>
+      <c r="B40" s="63" t="n"/>
+      <c r="C40" s="64" t="n"/>
+      <c r="D40" s="65" t="n"/>
+      <c r="E40" s="65" t="n"/>
+      <c r="F40" s="66" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="57" t="n"/>
-      <c r="C41" s="58" t="n"/>
-      <c r="D41" s="59" t="n"/>
-      <c r="E41" s="59" t="n"/>
-      <c r="F41" s="60" t="n"/>
+      <c r="B41" s="63" t="n"/>
+      <c r="C41" s="64" t="n"/>
+      <c r="D41" s="65" t="n"/>
+      <c r="E41" s="65" t="n"/>
+      <c r="F41" s="66" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="57" t="n"/>
-      <c r="C42" s="58" t="n"/>
-      <c r="D42" s="59" t="n"/>
-      <c r="E42" s="59" t="n"/>
-      <c r="F42" s="60" t="n"/>
+      <c r="B42" s="63" t="n"/>
+      <c r="C42" s="64" t="n"/>
+      <c r="D42" s="65" t="n"/>
+      <c r="E42" s="65" t="n"/>
+      <c r="F42" s="66" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="57" t="n"/>
-      <c r="C43" s="58" t="n"/>
-      <c r="D43" s="59" t="n"/>
-      <c r="E43" s="59" t="n"/>
-      <c r="F43" s="60" t="n"/>
+      <c r="B43" s="63" t="n"/>
+      <c r="C43" s="64" t="n"/>
+      <c r="D43" s="65" t="n"/>
+      <c r="E43" s="65" t="n"/>
+      <c r="F43" s="66" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="57" t="n"/>
-      <c r="C44" s="58" t="n"/>
-      <c r="D44" s="59" t="n"/>
-      <c r="E44" s="59" t="n"/>
-      <c r="F44" s="60" t="n"/>
+      <c r="B44" s="63" t="n"/>
+      <c r="C44" s="64" t="n"/>
+      <c r="D44" s="65" t="n"/>
+      <c r="E44" s="65" t="n"/>
+      <c r="F44" s="66" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="57" t="n"/>
-      <c r="C45" s="58" t="n"/>
-      <c r="D45" s="59" t="n"/>
-      <c r="E45" s="59" t="n"/>
-      <c r="F45" s="60" t="n"/>
+      <c r="B45" s="63" t="n"/>
+      <c r="C45" s="64" t="n"/>
+      <c r="D45" s="65" t="n"/>
+      <c r="E45" s="65" t="n"/>
+      <c r="F45" s="66" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="57" t="n"/>
-      <c r="C46" s="58" t="n"/>
-      <c r="D46" s="59" t="n"/>
-      <c r="E46" s="59" t="n"/>
-      <c r="F46" s="60" t="n"/>
+      <c r="B46" s="63" t="n"/>
+      <c r="C46" s="64" t="n"/>
+      <c r="D46" s="65" t="n"/>
+      <c r="E46" s="65" t="n"/>
+      <c r="F46" s="66" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="57" t="n"/>
-      <c r="C47" s="58" t="n"/>
-      <c r="D47" s="59" t="n"/>
-      <c r="E47" s="59" t="n"/>
-      <c r="F47" s="60" t="n"/>
+      <c r="B47" s="63" t="n"/>
+      <c r="C47" s="64" t="n"/>
+      <c r="D47" s="65" t="n"/>
+      <c r="E47" s="65" t="n"/>
+      <c r="F47" s="66" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="57" t="n"/>
-      <c r="C48" s="58" t="n"/>
-      <c r="D48" s="59" t="n"/>
-      <c r="E48" s="59" t="n"/>
-      <c r="F48" s="60" t="n"/>
+      <c r="B48" s="63" t="n"/>
+      <c r="C48" s="64" t="n"/>
+      <c r="D48" s="65" t="n"/>
+      <c r="E48" s="65" t="n"/>
+      <c r="F48" s="66" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="57" t="n"/>
-      <c r="C49" s="58" t="n"/>
-      <c r="D49" s="59" t="n"/>
-      <c r="E49" s="59" t="n"/>
-      <c r="F49" s="60" t="n"/>
+      <c r="B49" s="63" t="n"/>
+      <c r="C49" s="64" t="n"/>
+      <c r="D49" s="65" t="n"/>
+      <c r="E49" s="65" t="n"/>
+      <c r="F49" s="66" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="57" t="n"/>
-      <c r="C50" s="58" t="n"/>
-      <c r="D50" s="59" t="n"/>
-      <c r="E50" s="59" t="n"/>
-      <c r="F50" s="60" t="n"/>
+      <c r="B50" s="63" t="n"/>
+      <c r="C50" s="64" t="n"/>
+      <c r="D50" s="65" t="n"/>
+      <c r="E50" s="65" t="n"/>
+      <c r="F50" s="66" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="57" t="n"/>
-      <c r="C51" s="58" t="n"/>
-      <c r="D51" s="59" t="n"/>
-      <c r="E51" s="59" t="n"/>
-      <c r="F51" s="60" t="n"/>
+      <c r="B51" s="63" t="n"/>
+      <c r="C51" s="64" t="n"/>
+      <c r="D51" s="65" t="n"/>
+      <c r="E51" s="65" t="n"/>
+      <c r="F51" s="66" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="57" t="n"/>
-      <c r="C52" s="58" t="n"/>
-      <c r="D52" s="59" t="n"/>
-      <c r="E52" s="59" t="n"/>
-      <c r="F52" s="60" t="n"/>
+      <c r="B52" s="63" t="n"/>
+      <c r="C52" s="64" t="n"/>
+      <c r="D52" s="65" t="n"/>
+      <c r="E52" s="65" t="n"/>
+      <c r="F52" s="66" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="57" t="n"/>
-      <c r="C53" s="58" t="n"/>
-      <c r="D53" s="59" t="n"/>
-      <c r="E53" s="59" t="n"/>
-      <c r="F53" s="60" t="n"/>
+      <c r="B53" s="63" t="n"/>
+      <c r="C53" s="64" t="n"/>
+      <c r="D53" s="65" t="n"/>
+      <c r="E53" s="65" t="n"/>
+      <c r="F53" s="66" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="57" t="n"/>
-      <c r="C54" s="58" t="n"/>
-      <c r="D54" s="59" t="n"/>
-      <c r="E54" s="59" t="n"/>
-      <c r="F54" s="60" t="n"/>
+      <c r="B54" s="63" t="n"/>
+      <c r="C54" s="64" t="n"/>
+      <c r="D54" s="65" t="n"/>
+      <c r="E54" s="65" t="n"/>
+      <c r="F54" s="66" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="57" t="n"/>
-      <c r="C55" s="58" t="n"/>
-      <c r="D55" s="59" t="n"/>
-      <c r="E55" s="59" t="n"/>
-      <c r="F55" s="60" t="n"/>
+      <c r="B55" s="63" t="n"/>
+      <c r="C55" s="64" t="n"/>
+      <c r="D55" s="65" t="n"/>
+      <c r="E55" s="65" t="n"/>
+      <c r="F55" s="66" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="57" t="n"/>
-      <c r="C56" s="58" t="n"/>
-      <c r="D56" s="59" t="n"/>
-      <c r="E56" s="59" t="n"/>
-      <c r="F56" s="60" t="n"/>
+      <c r="B56" s="63" t="n"/>
+      <c r="C56" s="64" t="n"/>
+      <c r="D56" s="65" t="n"/>
+      <c r="E56" s="65" t="n"/>
+      <c r="F56" s="66" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="57" t="n"/>
-      <c r="C57" s="58" t="n"/>
-      <c r="D57" s="59" t="n"/>
-      <c r="E57" s="59" t="n"/>
-      <c r="F57" s="60" t="n"/>
+      <c r="B57" s="63" t="n"/>
+      <c r="C57" s="64" t="n"/>
+      <c r="D57" s="65" t="n"/>
+      <c r="E57" s="65" t="n"/>
+      <c r="F57" s="66" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="57" t="n"/>
-      <c r="C58" s="58" t="n"/>
-      <c r="D58" s="59" t="n"/>
-      <c r="E58" s="59" t="n"/>
-      <c r="F58" s="60" t="n"/>
+      <c r="B58" s="63" t="n"/>
+      <c r="C58" s="64" t="n"/>
+      <c r="D58" s="65" t="n"/>
+      <c r="E58" s="65" t="n"/>
+      <c r="F58" s="66" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="57" t="n"/>
-      <c r="C59" s="58" t="n"/>
-      <c r="D59" s="59" t="n"/>
-      <c r="E59" s="59" t="n"/>
-      <c r="F59" s="60" t="n"/>
+      <c r="B59" s="63" t="n"/>
+      <c r="C59" s="64" t="n"/>
+      <c r="D59" s="65" t="n"/>
+      <c r="E59" s="65" t="n"/>
+      <c r="F59" s="66" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="57" t="n"/>
-      <c r="C60" s="58" t="n"/>
-      <c r="D60" s="59" t="n"/>
-      <c r="E60" s="59" t="n"/>
-      <c r="F60" s="60" t="n"/>
+      <c r="B60" s="63" t="n"/>
+      <c r="C60" s="64" t="n"/>
+      <c r="D60" s="65" t="n"/>
+      <c r="E60" s="65" t="n"/>
+      <c r="F60" s="66" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="57" t="n"/>
-      <c r="C61" s="58" t="n"/>
-      <c r="D61" s="59" t="n"/>
-      <c r="E61" s="59" t="n"/>
-      <c r="F61" s="60" t="n"/>
+      <c r="B61" s="63" t="n"/>
+      <c r="C61" s="64" t="n"/>
+      <c r="D61" s="65" t="n"/>
+      <c r="E61" s="65" t="n"/>
+      <c r="F61" s="66" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="57" t="n"/>
-      <c r="C62" s="58" t="n"/>
-      <c r="D62" s="59" t="n"/>
-      <c r="E62" s="59" t="n"/>
-      <c r="F62" s="60" t="n"/>
+      <c r="B62" s="63" t="n"/>
+      <c r="C62" s="64" t="n"/>
+      <c r="D62" s="65" t="n"/>
+      <c r="E62" s="65" t="n"/>
+      <c r="F62" s="66" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="57" t="n"/>
-      <c r="C63" s="58" t="n"/>
-      <c r="D63" s="59" t="n"/>
-      <c r="E63" s="59" t="n"/>
-      <c r="F63" s="60" t="n"/>
+      <c r="B63" s="63" t="n"/>
+      <c r="C63" s="64" t="n"/>
+      <c r="D63" s="65" t="n"/>
+      <c r="E63" s="65" t="n"/>
+      <c r="F63" s="66" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="57" t="n"/>
-      <c r="C64" s="58" t="n"/>
-      <c r="D64" s="59" t="n"/>
-      <c r="E64" s="59" t="n"/>
-      <c r="F64" s="60" t="n"/>
+      <c r="B64" s="63" t="n"/>
+      <c r="C64" s="64" t="n"/>
+      <c r="D64" s="65" t="n"/>
+      <c r="E64" s="65" t="n"/>
+      <c r="F64" s="66" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="57" t="n"/>
-      <c r="C65" s="58" t="n"/>
-      <c r="D65" s="59" t="n"/>
-      <c r="E65" s="59" t="n"/>
-      <c r="F65" s="60" t="n"/>
+      <c r="B65" s="63" t="n"/>
+      <c r="C65" s="64" t="n"/>
+      <c r="D65" s="65" t="n"/>
+      <c r="E65" s="65" t="n"/>
+      <c r="F65" s="66" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="57" t="n"/>
-      <c r="C66" s="58" t="n"/>
-      <c r="D66" s="59" t="n"/>
-      <c r="E66" s="59" t="n"/>
-      <c r="F66" s="60" t="n"/>
+      <c r="B66" s="63" t="n"/>
+      <c r="C66" s="64" t="n"/>
+      <c r="D66" s="65" t="n"/>
+      <c r="E66" s="65" t="n"/>
+      <c r="F66" s="66" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="57" t="n"/>
-      <c r="C67" s="58" t="n"/>
-      <c r="D67" s="59" t="n"/>
-      <c r="E67" s="59" t="n"/>
-      <c r="F67" s="60" t="n"/>
+      <c r="B67" s="63" t="n"/>
+      <c r="C67" s="64" t="n"/>
+      <c r="D67" s="65" t="n"/>
+      <c r="E67" s="65" t="n"/>
+      <c r="F67" s="66" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="57" t="n"/>
-      <c r="C68" s="58" t="n"/>
-      <c r="D68" s="59" t="n"/>
-      <c r="E68" s="59" t="n"/>
-      <c r="F68" s="60" t="n"/>
+      <c r="B68" s="63" t="n"/>
+      <c r="C68" s="64" t="n"/>
+      <c r="D68" s="65" t="n"/>
+      <c r="E68" s="65" t="n"/>
+      <c r="F68" s="66" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="57" t="n"/>
-      <c r="C69" s="58" t="n"/>
-      <c r="D69" s="59" t="n"/>
-      <c r="E69" s="59" t="n"/>
-      <c r="F69" s="60" t="n"/>
+      <c r="B69" s="63" t="n"/>
+      <c r="C69" s="64" t="n"/>
+      <c r="D69" s="65" t="n"/>
+      <c r="E69" s="65" t="n"/>
+      <c r="F69" s="66" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="57" t="n"/>
-      <c r="C70" s="58" t="n"/>
-      <c r="D70" s="59" t="n"/>
-      <c r="E70" s="59" t="n"/>
-      <c r="F70" s="60" t="n"/>
+      <c r="B70" s="63" t="n"/>
+      <c r="C70" s="64" t="n"/>
+      <c r="D70" s="65" t="n"/>
+      <c r="E70" s="65" t="n"/>
+      <c r="F70" s="66" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="57" t="n"/>
-      <c r="C71" s="58" t="n"/>
-      <c r="D71" s="59" t="n"/>
-      <c r="E71" s="59" t="n"/>
-      <c r="F71" s="60" t="n"/>
+      <c r="B71" s="63" t="n"/>
+      <c r="C71" s="64" t="n"/>
+      <c r="D71" s="65" t="n"/>
+      <c r="E71" s="65" t="n"/>
+      <c r="F71" s="66" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="57" t="n"/>
-      <c r="C72" s="58" t="n"/>
-      <c r="D72" s="59" t="n"/>
-      <c r="E72" s="59" t="n"/>
-      <c r="F72" s="60" t="n"/>
+      <c r="B72" s="63" t="n"/>
+      <c r="C72" s="64" t="n"/>
+      <c r="D72" s="65" t="n"/>
+      <c r="E72" s="65" t="n"/>
+      <c r="F72" s="66" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="57" t="n"/>
-      <c r="C73" s="58" t="n"/>
-      <c r="D73" s="59" t="n"/>
-      <c r="E73" s="59" t="n"/>
-      <c r="F73" s="60" t="n"/>
+      <c r="B73" s="63" t="n"/>
+      <c r="C73" s="64" t="n"/>
+      <c r="D73" s="65" t="n"/>
+      <c r="E73" s="65" t="n"/>
+      <c r="F73" s="66" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="57" t="n"/>
-      <c r="C74" s="58" t="n"/>
-      <c r="D74" s="59" t="n"/>
-      <c r="E74" s="59" t="n"/>
-      <c r="F74" s="60" t="n"/>
+      <c r="B74" s="63" t="n"/>
+      <c r="C74" s="64" t="n"/>
+      <c r="D74" s="65" t="n"/>
+      <c r="E74" s="65" t="n"/>
+      <c r="F74" s="66" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="57" t="n"/>
-      <c r="C75" s="58" t="n"/>
-      <c r="D75" s="59" t="n"/>
-      <c r="E75" s="59" t="n"/>
-      <c r="F75" s="60" t="n"/>
+      <c r="B75" s="63" t="n"/>
+      <c r="C75" s="64" t="n"/>
+      <c r="D75" s="65" t="n"/>
+      <c r="E75" s="65" t="n"/>
+      <c r="F75" s="66" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="57" t="n"/>
-      <c r="C76" s="58" t="n"/>
-      <c r="D76" s="59" t="n"/>
-      <c r="E76" s="59" t="n"/>
-      <c r="F76" s="60" t="n"/>
+      <c r="B76" s="63" t="n"/>
+      <c r="C76" s="64" t="n"/>
+      <c r="D76" s="65" t="n"/>
+      <c r="E76" s="65" t="n"/>
+      <c r="F76" s="66" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="57" t="n"/>
-      <c r="C77" s="58" t="n"/>
-      <c r="D77" s="59" t="n"/>
-      <c r="E77" s="59" t="n"/>
-      <c r="F77" s="60" t="n"/>
+      <c r="B77" s="63" t="n"/>
+      <c r="C77" s="64" t="n"/>
+      <c r="D77" s="65" t="n"/>
+      <c r="E77" s="65" t="n"/>
+      <c r="F77" s="66" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="57" t="n"/>
-      <c r="C78" s="58" t="n"/>
-      <c r="D78" s="59" t="n"/>
-      <c r="E78" s="59" t="n"/>
-      <c r="F78" s="60" t="n"/>
+      <c r="B78" s="63" t="n"/>
+      <c r="C78" s="64" t="n"/>
+      <c r="D78" s="65" t="n"/>
+      <c r="E78" s="65" t="n"/>
+      <c r="F78" s="66" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="57" t="n"/>
-      <c r="C79" s="58" t="n"/>
-      <c r="D79" s="59" t="n"/>
-      <c r="E79" s="59" t="n"/>
-      <c r="F79" s="60" t="n"/>
+      <c r="B79" s="63" t="n"/>
+      <c r="C79" s="64" t="n"/>
+      <c r="D79" s="65" t="n"/>
+      <c r="E79" s="65" t="n"/>
+      <c r="F79" s="66" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="57" t="n"/>
-      <c r="C80" s="58" t="n"/>
-      <c r="D80" s="59" t="n"/>
-      <c r="E80" s="59" t="n"/>
-      <c r="F80" s="60" t="n"/>
+      <c r="B80" s="63" t="n"/>
+      <c r="C80" s="64" t="n"/>
+      <c r="D80" s="65" t="n"/>
+      <c r="E80" s="65" t="n"/>
+      <c r="F80" s="66" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="57" t="n"/>
-      <c r="C81" s="58" t="n"/>
-      <c r="D81" s="59" t="n"/>
-      <c r="E81" s="59" t="n"/>
-      <c r="F81" s="60" t="n"/>
+      <c r="B81" s="63" t="n"/>
+      <c r="C81" s="64" t="n"/>
+      <c r="D81" s="65" t="n"/>
+      <c r="E81" s="65" t="n"/>
+      <c r="F81" s="66" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="57" t="n"/>
-      <c r="C82" s="58" t="n"/>
-      <c r="D82" s="59" t="n"/>
-      <c r="E82" s="59" t="n"/>
-      <c r="F82" s="60" t="n"/>
+      <c r="B82" s="63" t="n"/>
+      <c r="C82" s="64" t="n"/>
+      <c r="D82" s="65" t="n"/>
+      <c r="E82" s="65" t="n"/>
+      <c r="F82" s="66" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="57" t="n"/>
-      <c r="C83" s="58" t="n"/>
-      <c r="D83" s="59" t="n"/>
-      <c r="E83" s="59" t="n"/>
-      <c r="F83" s="60" t="n"/>
+      <c r="B83" s="63" t="n"/>
+      <c r="C83" s="64" t="n"/>
+      <c r="D83" s="65" t="n"/>
+      <c r="E83" s="65" t="n"/>
+      <c r="F83" s="66" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="57" t="n"/>
-      <c r="C84" s="58" t="n"/>
-      <c r="D84" s="59" t="n"/>
-      <c r="E84" s="59" t="n"/>
-      <c r="F84" s="60" t="n"/>
+      <c r="B84" s="63" t="n"/>
+      <c r="C84" s="64" t="n"/>
+      <c r="D84" s="65" t="n"/>
+      <c r="E84" s="65" t="n"/>
+      <c r="F84" s="66" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="57" t="n"/>
-      <c r="C85" s="58" t="n"/>
-      <c r="D85" s="59" t="n"/>
-      <c r="E85" s="59" t="n"/>
-      <c r="F85" s="60" t="n"/>
+      <c r="B85" s="63" t="n"/>
+      <c r="C85" s="64" t="n"/>
+      <c r="D85" s="65" t="n"/>
+      <c r="E85" s="65" t="n"/>
+      <c r="F85" s="66" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="57" t="n"/>
-      <c r="C86" s="58" t="n"/>
-      <c r="D86" s="59" t="n"/>
-      <c r="E86" s="59" t="n"/>
-      <c r="F86" s="60" t="n"/>
+      <c r="B86" s="63" t="n"/>
+      <c r="C86" s="64" t="n"/>
+      <c r="D86" s="65" t="n"/>
+      <c r="E86" s="65" t="n"/>
+      <c r="F86" s="66" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="57" t="n"/>
-      <c r="C87" s="58" t="n"/>
-      <c r="D87" s="59" t="n"/>
-      <c r="E87" s="59" t="n"/>
-      <c r="F87" s="60" t="n"/>
+      <c r="B87" s="63" t="n"/>
+      <c r="C87" s="64" t="n"/>
+      <c r="D87" s="65" t="n"/>
+      <c r="E87" s="65" t="n"/>
+      <c r="F87" s="66" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="57" t="n"/>
-      <c r="C88" s="58" t="n"/>
-      <c r="D88" s="59" t="n"/>
-      <c r="E88" s="59" t="n"/>
-      <c r="F88" s="60" t="n"/>
+      <c r="B88" s="63" t="n"/>
+      <c r="C88" s="64" t="n"/>
+      <c r="D88" s="65" t="n"/>
+      <c r="E88" s="65" t="n"/>
+      <c r="F88" s="66" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="57" t="n"/>
-      <c r="C89" s="58" t="n"/>
-      <c r="D89" s="59" t="n"/>
-      <c r="E89" s="59" t="n"/>
-      <c r="F89" s="60" t="n"/>
+      <c r="B89" s="63" t="n"/>
+      <c r="C89" s="64" t="n"/>
+      <c r="D89" s="65" t="n"/>
+      <c r="E89" s="65" t="n"/>
+      <c r="F89" s="66" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="57" t="n"/>
-      <c r="C90" s="58" t="n"/>
-      <c r="D90" s="59" t="n"/>
-      <c r="E90" s="59" t="n"/>
-      <c r="F90" s="60" t="n"/>
+      <c r="B90" s="63" t="n"/>
+      <c r="C90" s="64" t="n"/>
+      <c r="D90" s="65" t="n"/>
+      <c r="E90" s="65" t="n"/>
+      <c r="F90" s="66" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="57" t="n"/>
-      <c r="C91" s="58" t="n"/>
-      <c r="D91" s="59" t="n"/>
-      <c r="E91" s="59" t="n"/>
-      <c r="F91" s="60" t="n"/>
+      <c r="B91" s="63" t="n"/>
+      <c r="C91" s="64" t="n"/>
+      <c r="D91" s="65" t="n"/>
+      <c r="E91" s="65" t="n"/>
+      <c r="F91" s="66" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="57" t="n"/>
-      <c r="C92" s="58" t="n"/>
-      <c r="D92" s="59" t="n"/>
-      <c r="E92" s="59" t="n"/>
-      <c r="F92" s="60" t="n"/>
+      <c r="B92" s="63" t="n"/>
+      <c r="C92" s="64" t="n"/>
+      <c r="D92" s="65" t="n"/>
+      <c r="E92" s="65" t="n"/>
+      <c r="F92" s="66" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="57" t="n"/>
-      <c r="C93" s="58" t="n"/>
-      <c r="D93" s="59" t="n"/>
-      <c r="E93" s="59" t="n"/>
-      <c r="F93" s="60" t="n"/>
+      <c r="B93" s="63" t="n"/>
+      <c r="C93" s="64" t="n"/>
+      <c r="D93" s="65" t="n"/>
+      <c r="E93" s="65" t="n"/>
+      <c r="F93" s="66" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="57" t="n"/>
-      <c r="C94" s="58" t="n"/>
-      <c r="D94" s="59" t="n"/>
-      <c r="E94" s="59" t="n"/>
-      <c r="F94" s="60" t="n"/>
+      <c r="B94" s="63" t="n"/>
+      <c r="C94" s="64" t="n"/>
+      <c r="D94" s="65" t="n"/>
+      <c r="E94" s="65" t="n"/>
+      <c r="F94" s="66" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="57" t="n"/>
-      <c r="C95" s="58" t="n"/>
-      <c r="D95" s="59" t="n"/>
-      <c r="E95" s="59" t="n"/>
-      <c r="F95" s="60" t="n"/>
+      <c r="B95" s="63" t="n"/>
+      <c r="C95" s="64" t="n"/>
+      <c r="D95" s="65" t="n"/>
+      <c r="E95" s="65" t="n"/>
+      <c r="F95" s="66" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="57" t="n"/>
-      <c r="C96" s="58" t="n"/>
-      <c r="D96" s="59" t="n"/>
-      <c r="E96" s="59" t="n"/>
-      <c r="F96" s="60" t="n"/>
+      <c r="B96" s="63" t="n"/>
+      <c r="C96" s="64" t="n"/>
+      <c r="D96" s="65" t="n"/>
+      <c r="E96" s="65" t="n"/>
+      <c r="F96" s="66" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="57" t="n"/>
-      <c r="C97" s="58" t="n"/>
-      <c r="D97" s="59" t="n"/>
-      <c r="E97" s="59" t="n"/>
-      <c r="F97" s="60" t="n"/>
+      <c r="B97" s="63" t="n"/>
+      <c r="C97" s="64" t="n"/>
+      <c r="D97" s="65" t="n"/>
+      <c r="E97" s="65" t="n"/>
+      <c r="F97" s="66" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="57" t="n"/>
-      <c r="C98" s="58" t="n"/>
-      <c r="D98" s="59" t="n"/>
-      <c r="E98" s="59" t="n"/>
-      <c r="F98" s="60" t="n"/>
+      <c r="B98" s="63" t="n"/>
+      <c r="C98" s="64" t="n"/>
+      <c r="D98" s="65" t="n"/>
+      <c r="E98" s="65" t="n"/>
+      <c r="F98" s="66" t="n"/>
     </row>
     <row r="99">
-      <c r="B99" s="57" t="n"/>
-      <c r="C99" s="58" t="n"/>
-      <c r="D99" s="59" t="n"/>
-      <c r="E99" s="59" t="n"/>
-      <c r="F99" s="60" t="n"/>
+      <c r="B99" s="63" t="n"/>
+      <c r="C99" s="64" t="n"/>
+      <c r="D99" s="65" t="n"/>
+      <c r="E99" s="65" t="n"/>
+      <c r="F99" s="66" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="57" t="n"/>
-      <c r="C100" s="58" t="n"/>
-      <c r="D100" s="59" t="n"/>
-      <c r="E100" s="59" t="n"/>
-      <c r="F100" s="60" t="n"/>
+      <c r="B100" s="63" t="n"/>
+      <c r="C100" s="64" t="n"/>
+      <c r="D100" s="65" t="n"/>
+      <c r="E100" s="65" t="n"/>
+      <c r="F100" s="66" t="n"/>
     </row>
     <row r="101">
-      <c r="B101" s="57" t="n"/>
-      <c r="C101" s="58" t="n"/>
-      <c r="D101" s="59" t="n"/>
-      <c r="E101" s="59" t="n"/>
-      <c r="F101" s="60" t="n"/>
+      <c r="B101" s="63" t="n"/>
+      <c r="C101" s="64" t="n"/>
+      <c r="D101" s="65" t="n"/>
+      <c r="E101" s="65" t="n"/>
+      <c r="F101" s="66" t="n"/>
     </row>
     <row r="102">
-      <c r="B102" s="57" t="n"/>
-      <c r="C102" s="58" t="n"/>
-      <c r="D102" s="59" t="n"/>
-      <c r="E102" s="59" t="n"/>
-      <c r="F102" s="60" t="n"/>
+      <c r="B102" s="63" t="n"/>
+      <c r="C102" s="64" t="n"/>
+      <c r="D102" s="65" t="n"/>
+      <c r="E102" s="65" t="n"/>
+      <c r="F102" s="66" t="n"/>
     </row>
     <row r="103">
-      <c r="B103" s="57" t="n"/>
-      <c r="C103" s="58" t="n"/>
-      <c r="D103" s="59" t="n"/>
-      <c r="E103" s="59" t="n"/>
-      <c r="F103" s="60" t="n"/>
+      <c r="B103" s="63" t="n"/>
+      <c r="C103" s="64" t="n"/>
+      <c r="D103" s="65" t="n"/>
+      <c r="E103" s="65" t="n"/>
+      <c r="F103" s="66" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="57" t="n"/>
-      <c r="C104" s="58" t="n"/>
-      <c r="D104" s="59" t="n"/>
-      <c r="E104" s="59" t="n"/>
-      <c r="F104" s="60" t="n"/>
+      <c r="B104" s="63" t="n"/>
+      <c r="C104" s="64" t="n"/>
+      <c r="D104" s="65" t="n"/>
+      <c r="E104" s="65" t="n"/>
+      <c r="F104" s="66" t="n"/>
     </row>
     <row r="105">
-      <c r="B105" s="57" t="n"/>
-      <c r="C105" s="58" t="n"/>
-      <c r="D105" s="59" t="n"/>
-      <c r="E105" s="59" t="n"/>
-      <c r="F105" s="60" t="n"/>
+      <c r="B105" s="63" t="n"/>
+      <c r="C105" s="64" t="n"/>
+      <c r="D105" s="65" t="n"/>
+      <c r="E105" s="65" t="n"/>
+      <c r="F105" s="66" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" s="57" t="n"/>
-      <c r="C106" s="58" t="n"/>
-      <c r="D106" s="59" t="n"/>
-      <c r="E106" s="59" t="n"/>
-      <c r="F106" s="60" t="n"/>
+      <c r="B106" s="63" t="n"/>
+      <c r="C106" s="64" t="n"/>
+      <c r="D106" s="65" t="n"/>
+      <c r="E106" s="65" t="n"/>
+      <c r="F106" s="66" t="n"/>
     </row>
     <row r="107">
-      <c r="B107" s="57" t="n"/>
-      <c r="C107" s="58" t="n"/>
-      <c r="D107" s="59" t="n"/>
-      <c r="E107" s="59" t="n"/>
-      <c r="F107" s="60" t="n"/>
+      <c r="B107" s="63" t="n"/>
+      <c r="C107" s="64" t="n"/>
+      <c r="D107" s="65" t="n"/>
+      <c r="E107" s="65" t="n"/>
+      <c r="F107" s="66" t="n"/>
     </row>
     <row r="108">
-      <c r="B108" s="57" t="n"/>
-      <c r="C108" s="58" t="n"/>
-      <c r="D108" s="59" t="n"/>
-      <c r="E108" s="59" t="n"/>
-      <c r="F108" s="60" t="n"/>
+      <c r="B108" s="63" t="n"/>
+      <c r="C108" s="64" t="n"/>
+      <c r="D108" s="65" t="n"/>
+      <c r="E108" s="65" t="n"/>
+      <c r="F108" s="66" t="n"/>
     </row>
     <row r="109">
-      <c r="B109" s="57" t="n"/>
-      <c r="C109" s="58" t="n"/>
-      <c r="D109" s="59" t="n"/>
-      <c r="E109" s="59" t="n"/>
-      <c r="F109" s="60" t="n"/>
+      <c r="B109" s="63" t="n"/>
+      <c r="C109" s="64" t="n"/>
+      <c r="D109" s="65" t="n"/>
+      <c r="E109" s="65" t="n"/>
+      <c r="F109" s="66" t="n"/>
     </row>
     <row r="110">
-      <c r="B110" s="57" t="n"/>
-      <c r="C110" s="58" t="n"/>
-      <c r="D110" s="59" t="n"/>
-      <c r="E110" s="59" t="n"/>
-      <c r="F110" s="60" t="n"/>
+      <c r="B110" s="63" t="n"/>
+      <c r="C110" s="64" t="n"/>
+      <c r="D110" s="65" t="n"/>
+      <c r="E110" s="65" t="n"/>
+      <c r="F110" s="66" t="n"/>
     </row>
     <row r="111">
-      <c r="B111" s="57" t="n"/>
-      <c r="C111" s="58" t="n"/>
-      <c r="D111" s="59" t="n"/>
-      <c r="E111" s="59" t="n"/>
-      <c r="F111" s="60" t="n"/>
+      <c r="B111" s="63" t="n"/>
+      <c r="C111" s="64" t="n"/>
+      <c r="D111" s="65" t="n"/>
+      <c r="E111" s="65" t="n"/>
+      <c r="F111" s="66" t="n"/>
     </row>
     <row r="112">
-      <c r="B112" s="57" t="n"/>
-      <c r="C112" s="58" t="n"/>
-      <c r="D112" s="59" t="n"/>
-      <c r="E112" s="59" t="n"/>
-      <c r="F112" s="60" t="n"/>
+      <c r="B112" s="63" t="n"/>
+      <c r="C112" s="64" t="n"/>
+      <c r="D112" s="65" t="n"/>
+      <c r="E112" s="65" t="n"/>
+      <c r="F112" s="66" t="n"/>
     </row>
     <row r="113">
-      <c r="B113" s="57" t="n"/>
-      <c r="C113" s="58" t="n"/>
-      <c r="D113" s="59" t="n"/>
-      <c r="E113" s="59" t="n"/>
-      <c r="F113" s="60" t="n"/>
+      <c r="B113" s="63" t="n"/>
+      <c r="C113" s="64" t="n"/>
+      <c r="D113" s="65" t="n"/>
+      <c r="E113" s="65" t="n"/>
+      <c r="F113" s="66" t="n"/>
     </row>
     <row r="114">
-      <c r="B114" s="57" t="n"/>
-      <c r="C114" s="58" t="n"/>
-      <c r="D114" s="59" t="n"/>
-      <c r="E114" s="59" t="n"/>
-      <c r="F114" s="60" t="n"/>
+      <c r="B114" s="63" t="n"/>
+      <c r="C114" s="64" t="n"/>
+      <c r="D114" s="65" t="n"/>
+      <c r="E114" s="65" t="n"/>
+      <c r="F114" s="66" t="n"/>
     </row>
     <row r="115">
-      <c r="B115" s="57" t="n"/>
-      <c r="C115" s="58" t="n"/>
-      <c r="D115" s="59" t="n"/>
-      <c r="E115" s="59" t="n"/>
-      <c r="F115" s="60" t="n"/>
+      <c r="B115" s="63" t="n"/>
+      <c r="C115" s="64" t="n"/>
+      <c r="D115" s="65" t="n"/>
+      <c r="E115" s="65" t="n"/>
+      <c r="F115" s="66" t="n"/>
     </row>
     <row r="116">
-      <c r="B116" s="57" t="n"/>
-      <c r="C116" s="58" t="n"/>
-      <c r="D116" s="59" t="n"/>
-      <c r="E116" s="59" t="n"/>
-      <c r="F116" s="60" t="n"/>
+      <c r="B116" s="63" t="n"/>
+      <c r="C116" s="64" t="n"/>
+      <c r="D116" s="65" t="n"/>
+      <c r="E116" s="65" t="n"/>
+      <c r="F116" s="66" t="n"/>
     </row>
     <row r="117">
-      <c r="B117" s="57" t="n"/>
-      <c r="C117" s="58" t="n"/>
-      <c r="D117" s="59" t="n"/>
-      <c r="E117" s="59" t="n"/>
-      <c r="F117" s="60" t="n"/>
+      <c r="B117" s="63" t="n"/>
+      <c r="C117" s="64" t="n"/>
+      <c r="D117" s="65" t="n"/>
+      <c r="E117" s="65" t="n"/>
+      <c r="F117" s="66" t="n"/>
     </row>
     <row r="118">
-      <c r="B118" s="57" t="n"/>
-      <c r="C118" s="58" t="n"/>
-      <c r="D118" s="59" t="n"/>
-      <c r="E118" s="59" t="n"/>
-      <c r="F118" s="60" t="n"/>
+      <c r="B118" s="63" t="n"/>
+      <c r="C118" s="64" t="n"/>
+      <c r="D118" s="65" t="n"/>
+      <c r="E118" s="65" t="n"/>
+      <c r="F118" s="66" t="n"/>
     </row>
     <row r="119">
-      <c r="B119" s="57" t="n"/>
-      <c r="C119" s="58" t="n"/>
-      <c r="D119" s="59" t="n"/>
-      <c r="E119" s="59" t="n"/>
-      <c r="F119" s="60" t="n"/>
+      <c r="B119" s="63" t="n"/>
+      <c r="C119" s="64" t="n"/>
+      <c r="D119" s="65" t="n"/>
+      <c r="E119" s="65" t="n"/>
+      <c r="F119" s="66" t="n"/>
     </row>
     <row r="120">
-      <c r="B120" s="57" t="n"/>
-      <c r="C120" s="58" t="n"/>
-      <c r="D120" s="59" t="n"/>
-      <c r="E120" s="59" t="n"/>
-      <c r="F120" s="60" t="n"/>
+      <c r="B120" s="63" t="n"/>
+      <c r="C120" s="64" t="n"/>
+      <c r="D120" s="65" t="n"/>
+      <c r="E120" s="65" t="n"/>
+      <c r="F120" s="66" t="n"/>
     </row>
     <row r="121">
-      <c r="B121" s="57" t="n"/>
-      <c r="C121" s="58" t="n"/>
-      <c r="D121" s="59" t="n"/>
-      <c r="E121" s="59" t="n"/>
-      <c r="F121" s="60" t="n"/>
+      <c r="B121" s="63" t="n"/>
+      <c r="C121" s="64" t="n"/>
+      <c r="D121" s="65" t="n"/>
+      <c r="E121" s="65" t="n"/>
+      <c r="F121" s="66" t="n"/>
     </row>
     <row r="122">
-      <c r="B122" s="57" t="n"/>
-      <c r="C122" s="58" t="n"/>
-      <c r="D122" s="59" t="n"/>
-      <c r="E122" s="59" t="n"/>
-      <c r="F122" s="60" t="n"/>
+      <c r="B122" s="63" t="n"/>
+      <c r="C122" s="64" t="n"/>
+      <c r="D122" s="65" t="n"/>
+      <c r="E122" s="65" t="n"/>
+      <c r="F122" s="66" t="n"/>
     </row>
     <row r="123">
-      <c r="B123" s="57" t="n"/>
-      <c r="C123" s="58" t="n"/>
-      <c r="D123" s="59" t="n"/>
-      <c r="E123" s="59" t="n"/>
-      <c r="F123" s="60" t="n"/>
+      <c r="B123" s="63" t="n"/>
+      <c r="C123" s="64" t="n"/>
+      <c r="D123" s="65" t="n"/>
+      <c r="E123" s="65" t="n"/>
+      <c r="F123" s="66" t="n"/>
     </row>
     <row r="124">
-      <c r="B124" s="57" t="n"/>
-      <c r="C124" s="58" t="n"/>
-      <c r="D124" s="59" t="n"/>
-      <c r="E124" s="59" t="n"/>
-      <c r="F124" s="60" t="n"/>
+      <c r="B124" s="63" t="n"/>
+      <c r="C124" s="64" t="n"/>
+      <c r="D124" s="65" t="n"/>
+      <c r="E124" s="65" t="n"/>
+      <c r="F124" s="66" t="n"/>
     </row>
     <row r="125">
-      <c r="B125" s="57" t="n"/>
-      <c r="C125" s="58" t="n"/>
-      <c r="D125" s="59" t="n"/>
-      <c r="E125" s="59" t="n"/>
-      <c r="F125" s="60" t="n"/>
+      <c r="B125" s="63" t="n"/>
+      <c r="C125" s="64" t="n"/>
+      <c r="D125" s="65" t="n"/>
+      <c r="E125" s="65" t="n"/>
+      <c r="F125" s="66" t="n"/>
     </row>
     <row r="126">
-      <c r="B126" s="57" t="n"/>
-      <c r="C126" s="58" t="n"/>
-      <c r="D126" s="59" t="n"/>
-      <c r="E126" s="59" t="n"/>
-      <c r="F126" s="60" t="n"/>
+      <c r="B126" s="63" t="n"/>
+      <c r="C126" s="64" t="n"/>
+      <c r="D126" s="65" t="n"/>
+      <c r="E126" s="65" t="n"/>
+      <c r="F126" s="66" t="n"/>
     </row>
     <row r="127">
-      <c r="B127" s="57" t="n"/>
-      <c r="C127" s="58" t="n"/>
-      <c r="D127" s="59" t="n"/>
-      <c r="E127" s="59" t="n"/>
-      <c r="F127" s="60" t="n"/>
+      <c r="B127" s="63" t="n"/>
+      <c r="C127" s="64" t="n"/>
+      <c r="D127" s="65" t="n"/>
+      <c r="E127" s="65" t="n"/>
+      <c r="F127" s="66" t="n"/>
     </row>
     <row r="128">
-      <c r="B128" s="57" t="n"/>
-      <c r="C128" s="58" t="n"/>
-      <c r="D128" s="59" t="n"/>
-      <c r="E128" s="59" t="n"/>
-      <c r="F128" s="60" t="n"/>
+      <c r="B128" s="63" t="n"/>
+      <c r="C128" s="64" t="n"/>
+      <c r="D128" s="65" t="n"/>
+      <c r="E128" s="65" t="n"/>
+      <c r="F128" s="66" t="n"/>
     </row>
     <row r="129">
-      <c r="B129" s="57" t="n"/>
-      <c r="C129" s="58" t="n"/>
-      <c r="D129" s="59" t="n"/>
-      <c r="E129" s="59" t="n"/>
-      <c r="F129" s="60" t="n"/>
+      <c r="B129" s="63" t="n"/>
+      <c r="C129" s="64" t="n"/>
+      <c r="D129" s="65" t="n"/>
+      <c r="E129" s="65" t="n"/>
+      <c r="F129" s="66" t="n"/>
     </row>
     <row r="130">
-      <c r="B130" s="57" t="n"/>
-      <c r="C130" s="58" t="n"/>
-      <c r="D130" s="59" t="n"/>
-      <c r="E130" s="59" t="n"/>
-      <c r="F130" s="60" t="n"/>
+      <c r="B130" s="63" t="n"/>
+      <c r="C130" s="64" t="n"/>
+      <c r="D130" s="65" t="n"/>
+      <c r="E130" s="65" t="n"/>
+      <c r="F130" s="66" t="n"/>
     </row>
     <row r="131">
-      <c r="B131" s="57" t="n"/>
-      <c r="C131" s="58" t="n"/>
-      <c r="D131" s="59" t="n"/>
-      <c r="E131" s="59" t="n"/>
-      <c r="F131" s="60" t="n"/>
+      <c r="B131" s="63" t="n"/>
+      <c r="C131" s="64" t="n"/>
+      <c r="D131" s="65" t="n"/>
+      <c r="E131" s="65" t="n"/>
+      <c r="F131" s="66" t="n"/>
     </row>
     <row r="132">
-      <c r="B132" s="57" t="n"/>
-      <c r="C132" s="58" t="n"/>
-      <c r="D132" s="59" t="n"/>
-      <c r="E132" s="59" t="n"/>
-      <c r="F132" s="60" t="n"/>
+      <c r="B132" s="63" t="n"/>
+      <c r="C132" s="64" t="n"/>
+      <c r="D132" s="65" t="n"/>
+      <c r="E132" s="65" t="n"/>
+      <c r="F132" s="66" t="n"/>
     </row>
     <row r="133">
-      <c r="B133" s="57" t="n"/>
-      <c r="C133" s="58" t="n"/>
-      <c r="D133" s="59" t="n"/>
-      <c r="E133" s="59" t="n"/>
-      <c r="F133" s="60" t="n"/>
+      <c r="B133" s="63" t="n"/>
+      <c r="C133" s="64" t="n"/>
+      <c r="D133" s="65" t="n"/>
+      <c r="E133" s="65" t="n"/>
+      <c r="F133" s="66" t="n"/>
     </row>
     <row r="134">
-      <c r="B134" s="57" t="n"/>
-      <c r="C134" s="58" t="n"/>
-      <c r="D134" s="59" t="n"/>
-      <c r="E134" s="59" t="n"/>
-      <c r="F134" s="60" t="n"/>
+      <c r="B134" s="63" t="n"/>
+      <c r="C134" s="64" t="n"/>
+      <c r="D134" s="65" t="n"/>
+      <c r="E134" s="65" t="n"/>
+      <c r="F134" s="66" t="n"/>
     </row>
     <row r="135">
-      <c r="B135" s="57" t="n"/>
-      <c r="C135" s="58" t="n"/>
-      <c r="D135" s="59" t="n"/>
-      <c r="E135" s="59" t="n"/>
-      <c r="F135" s="60" t="n"/>
+      <c r="B135" s="63" t="n"/>
+      <c r="C135" s="64" t="n"/>
+      <c r="D135" s="65" t="n"/>
+      <c r="E135" s="65" t="n"/>
+      <c r="F135" s="66" t="n"/>
     </row>
     <row r="136">
-      <c r="B136" s="57" t="n"/>
-      <c r="C136" s="58" t="n"/>
-      <c r="D136" s="59" t="n"/>
-      <c r="E136" s="59" t="n"/>
-      <c r="F136" s="60" t="n"/>
+      <c r="B136" s="63" t="n"/>
+      <c r="C136" s="64" t="n"/>
+      <c r="D136" s="65" t="n"/>
+      <c r="E136" s="65" t="n"/>
+      <c r="F136" s="66" t="n"/>
     </row>
     <row r="137">
-      <c r="B137" s="57" t="n"/>
-      <c r="C137" s="58" t="n"/>
-      <c r="D137" s="59" t="n"/>
-      <c r="E137" s="59" t="n"/>
-      <c r="F137" s="60" t="n"/>
+      <c r="B137" s="63" t="n"/>
+      <c r="C137" s="64" t="n"/>
+      <c r="D137" s="65" t="n"/>
+      <c r="E137" s="65" t="n"/>
+      <c r="F137" s="66" t="n"/>
     </row>
     <row r="138">
-      <c r="B138" s="57" t="n"/>
-      <c r="C138" s="58" t="n"/>
-      <c r="D138" s="59" t="n"/>
-      <c r="E138" s="59" t="n"/>
-      <c r="F138" s="60" t="n"/>
+      <c r="B138" s="63" t="n"/>
+      <c r="C138" s="64" t="n"/>
+      <c r="D138" s="65" t="n"/>
+      <c r="E138" s="65" t="n"/>
+      <c r="F138" s="66" t="n"/>
     </row>
     <row r="139">
-      <c r="B139" s="57" t="n"/>
-      <c r="C139" s="58" t="n"/>
-      <c r="D139" s="59" t="n"/>
-      <c r="E139" s="59" t="n"/>
-      <c r="F139" s="60" t="n"/>
+      <c r="B139" s="63" t="n"/>
+      <c r="C139" s="64" t="n"/>
+      <c r="D139" s="65" t="n"/>
+      <c r="E139" s="65" t="n"/>
+      <c r="F139" s="66" t="n"/>
     </row>
     <row r="140">
-      <c r="B140" s="57" t="n"/>
-      <c r="C140" s="58" t="n"/>
-      <c r="D140" s="59" t="n"/>
-      <c r="E140" s="59" t="n"/>
-      <c r="F140" s="60" t="n"/>
+      <c r="B140" s="63" t="n"/>
+      <c r="C140" s="64" t="n"/>
+      <c r="D140" s="65" t="n"/>
+      <c r="E140" s="65" t="n"/>
+      <c r="F140" s="66" t="n"/>
     </row>
     <row r="141">
-      <c r="B141" s="57" t="n"/>
-      <c r="C141" s="58" t="n"/>
-      <c r="D141" s="59" t="n"/>
-      <c r="E141" s="59" t="n"/>
-      <c r="F141" s="60" t="n"/>
+      <c r="B141" s="63" t="n"/>
+      <c r="C141" s="64" t="n"/>
+      <c r="D141" s="65" t="n"/>
+      <c r="E141" s="65" t="n"/>
+      <c r="F141" s="66" t="n"/>
     </row>
     <row r="142">
-      <c r="B142" s="57" t="n"/>
-      <c r="C142" s="58" t="n"/>
-      <c r="D142" s="59" t="n"/>
-      <c r="E142" s="59" t="n"/>
-      <c r="F142" s="60" t="n"/>
+      <c r="B142" s="63" t="n"/>
+      <c r="C142" s="64" t="n"/>
+      <c r="D142" s="65" t="n"/>
+      <c r="E142" s="65" t="n"/>
+      <c r="F142" s="66" t="n"/>
     </row>
     <row r="143">
-      <c r="B143" s="57" t="n"/>
-      <c r="C143" s="58" t="n"/>
-      <c r="D143" s="59" t="n"/>
-      <c r="E143" s="59" t="n"/>
-      <c r="F143" s="60" t="n"/>
+      <c r="B143" s="63" t="n"/>
+      <c r="C143" s="64" t="n"/>
+      <c r="D143" s="65" t="n"/>
+      <c r="E143" s="65" t="n"/>
+      <c r="F143" s="66" t="n"/>
     </row>
     <row r="144">
-      <c r="B144" s="57" t="n"/>
-      <c r="C144" s="58" t="n"/>
-      <c r="D144" s="59" t="n"/>
-      <c r="E144" s="59" t="n"/>
-      <c r="F144" s="60" t="n"/>
+      <c r="B144" s="63" t="n"/>
+      <c r="C144" s="64" t="n"/>
+      <c r="D144" s="65" t="n"/>
+      <c r="E144" s="65" t="n"/>
+      <c r="F144" s="66" t="n"/>
     </row>
     <row r="145">
-      <c r="B145" s="57" t="n"/>
-      <c r="C145" s="58" t="n"/>
-      <c r="D145" s="59" t="n"/>
-      <c r="E145" s="59" t="n"/>
-      <c r="F145" s="60" t="n"/>
+      <c r="B145" s="63" t="n"/>
+      <c r="C145" s="64" t="n"/>
+      <c r="D145" s="65" t="n"/>
+      <c r="E145" s="65" t="n"/>
+      <c r="F145" s="66" t="n"/>
     </row>
     <row r="146">
-      <c r="B146" s="57" t="n"/>
-      <c r="C146" s="58" t="n"/>
-      <c r="D146" s="59" t="n"/>
-      <c r="E146" s="59" t="n"/>
-      <c r="F146" s="60" t="n"/>
+      <c r="B146" s="63" t="n"/>
+      <c r="C146" s="64" t="n"/>
+      <c r="D146" s="65" t="n"/>
+      <c r="E146" s="65" t="n"/>
+      <c r="F146" s="66" t="n"/>
     </row>
     <row r="147">
-      <c r="B147" s="57" t="n"/>
-      <c r="C147" s="58" t="n"/>
-      <c r="D147" s="59" t="n"/>
-      <c r="E147" s="59" t="n"/>
-      <c r="F147" s="60" t="n"/>
+      <c r="B147" s="63" t="n"/>
+      <c r="C147" s="64" t="n"/>
+      <c r="D147" s="65" t="n"/>
+      <c r="E147" s="65" t="n"/>
+      <c r="F147" s="66" t="n"/>
     </row>
     <row r="148">
-      <c r="B148" s="57" t="n"/>
-      <c r="C148" s="58" t="n"/>
-      <c r="D148" s="59" t="n"/>
-      <c r="E148" s="59" t="n"/>
-      <c r="F148" s="60" t="n"/>
+      <c r="B148" s="63" t="n"/>
+      <c r="C148" s="64" t="n"/>
+      <c r="D148" s="65" t="n"/>
+      <c r="E148" s="65" t="n"/>
+      <c r="F148" s="66" t="n"/>
     </row>
     <row r="149">
-      <c r="B149" s="57" t="n"/>
-      <c r="C149" s="58" t="n"/>
-      <c r="D149" s="59" t="n"/>
-      <c r="E149" s="59" t="n"/>
-      <c r="F149" s="60" t="n"/>
+      <c r="B149" s="63" t="n"/>
+      <c r="C149" s="64" t="n"/>
+      <c r="D149" s="65" t="n"/>
+      <c r="E149" s="65" t="n"/>
+      <c r="F149" s="66" t="n"/>
     </row>
     <row r="150">
-      <c r="B150" s="57" t="n"/>
-      <c r="C150" s="58" t="n"/>
-      <c r="D150" s="59" t="n"/>
-      <c r="E150" s="59" t="n"/>
-      <c r="F150" s="60" t="n"/>
+      <c r="B150" s="63" t="n"/>
+      <c r="C150" s="64" t="n"/>
+      <c r="D150" s="65" t="n"/>
+      <c r="E150" s="65" t="n"/>
+      <c r="F150" s="66" t="n"/>
     </row>
     <row r="151">
-      <c r="B151" s="57" t="n"/>
-      <c r="C151" s="58" t="n"/>
-      <c r="D151" s="59" t="n"/>
-      <c r="E151" s="59" t="n"/>
-      <c r="F151" s="60" t="n"/>
+      <c r="B151" s="63" t="n"/>
+      <c r="C151" s="64" t="n"/>
+      <c r="D151" s="65" t="n"/>
+      <c r="E151" s="65" t="n"/>
+      <c r="F151" s="66" t="n"/>
     </row>
     <row r="152">
-      <c r="B152" s="57" t="n"/>
-      <c r="C152" s="58" t="n"/>
-      <c r="D152" s="59" t="n"/>
-      <c r="E152" s="59" t="n"/>
-      <c r="F152" s="60" t="n"/>
+      <c r="B152" s="63" t="n"/>
+      <c r="C152" s="64" t="n"/>
+      <c r="D152" s="65" t="n"/>
+      <c r="E152" s="65" t="n"/>
+      <c r="F152" s="66" t="n"/>
     </row>
     <row r="153">
-      <c r="B153" s="57" t="n"/>
-      <c r="C153" s="58" t="n"/>
-      <c r="D153" s="59" t="n"/>
-      <c r="E153" s="59" t="n"/>
-      <c r="F153" s="60" t="n"/>
+      <c r="B153" s="63" t="n"/>
+      <c r="C153" s="64" t="n"/>
+      <c r="D153" s="65" t="n"/>
+      <c r="E153" s="65" t="n"/>
+      <c r="F153" s="66" t="n"/>
     </row>
     <row r="154">
-      <c r="B154" s="57" t="n"/>
-      <c r="C154" s="58" t="n"/>
-      <c r="D154" s="59" t="n"/>
-      <c r="E154" s="59" t="n"/>
-      <c r="F154" s="60" t="n"/>
+      <c r="B154" s="63" t="n"/>
+      <c r="C154" s="64" t="n"/>
+      <c r="D154" s="65" t="n"/>
+      <c r="E154" s="65" t="n"/>
+      <c r="F154" s="66" t="n"/>
     </row>
     <row r="155">
-      <c r="B155" s="57" t="n"/>
-      <c r="C155" s="58" t="n"/>
-      <c r="D155" s="59" t="n"/>
-      <c r="E155" s="59" t="n"/>
-      <c r="F155" s="60" t="n"/>
+      <c r="B155" s="63" t="n"/>
+      <c r="C155" s="64" t="n"/>
+      <c r="D155" s="65" t="n"/>
+      <c r="E155" s="65" t="n"/>
+      <c r="F155" s="66" t="n"/>
     </row>
     <row r="156">
-      <c r="B156" s="57" t="n"/>
-      <c r="C156" s="58" t="n"/>
-      <c r="D156" s="59" t="n"/>
-      <c r="E156" s="59" t="n"/>
-      <c r="F156" s="60" t="n"/>
+      <c r="B156" s="63" t="n"/>
+      <c r="C156" s="64" t="n"/>
+      <c r="D156" s="65" t="n"/>
+      <c r="E156" s="65" t="n"/>
+      <c r="F156" s="66" t="n"/>
     </row>
     <row r="157">
-      <c r="B157" s="57" t="n"/>
-      <c r="C157" s="58" t="n"/>
-      <c r="D157" s="59" t="n"/>
-      <c r="E157" s="59" t="n"/>
-      <c r="F157" s="60" t="n"/>
+      <c r="B157" s="63" t="n"/>
+      <c r="C157" s="64" t="n"/>
+      <c r="D157" s="65" t="n"/>
+      <c r="E157" s="65" t="n"/>
+      <c r="F157" s="66" t="n"/>
     </row>
     <row r="158">
-      <c r="B158" s="57" t="n"/>
-      <c r="C158" s="58" t="n"/>
-      <c r="D158" s="59" t="n"/>
-      <c r="E158" s="59" t="n"/>
-      <c r="F158" s="60" t="n"/>
+      <c r="B158" s="63" t="n"/>
+      <c r="C158" s="64" t="n"/>
+      <c r="D158" s="65" t="n"/>
+      <c r="E158" s="65" t="n"/>
+      <c r="F158" s="66" t="n"/>
     </row>
     <row r="159">
-      <c r="B159" s="57" t="n"/>
-      <c r="C159" s="58" t="n"/>
-      <c r="D159" s="59" t="n"/>
-      <c r="E159" s="59" t="n"/>
-      <c r="F159" s="60" t="n"/>
+      <c r="B159" s="63" t="n"/>
+      <c r="C159" s="64" t="n"/>
+      <c r="D159" s="65" t="n"/>
+      <c r="E159" s="65" t="n"/>
+      <c r="F159" s="66" t="n"/>
     </row>
     <row r="160">
-      <c r="B160" s="57" t="n"/>
-      <c r="C160" s="58" t="n"/>
-      <c r="D160" s="59" t="n"/>
-      <c r="E160" s="59" t="n"/>
-      <c r="F160" s="60" t="n"/>
+      <c r="B160" s="63" t="n"/>
+      <c r="C160" s="64" t="n"/>
+      <c r="D160" s="65" t="n"/>
+      <c r="E160" s="65" t="n"/>
+      <c r="F160" s="66" t="n"/>
     </row>
     <row r="161">
-      <c r="B161" s="57" t="n"/>
-      <c r="C161" s="58" t="n"/>
-      <c r="D161" s="59" t="n"/>
-      <c r="E161" s="59" t="n"/>
-      <c r="F161" s="60" t="n"/>
+      <c r="B161" s="63" t="n"/>
+      <c r="C161" s="64" t="n"/>
+      <c r="D161" s="65" t="n"/>
+      <c r="E161" s="65" t="n"/>
+      <c r="F161" s="66" t="n"/>
     </row>
     <row r="162">
-      <c r="B162" s="57" t="n"/>
-      <c r="C162" s="58" t="n"/>
-      <c r="D162" s="59" t="n"/>
-      <c r="E162" s="59" t="n"/>
-      <c r="F162" s="60" t="n"/>
+      <c r="B162" s="63" t="n"/>
+      <c r="C162" s="64" t="n"/>
+      <c r="D162" s="65" t="n"/>
+      <c r="E162" s="65" t="n"/>
+      <c r="F162" s="66" t="n"/>
     </row>
     <row r="163">
-      <c r="B163" s="57" t="n"/>
-      <c r="C163" s="58" t="n"/>
-      <c r="D163" s="59" t="n"/>
-      <c r="E163" s="59" t="n"/>
-      <c r="F163" s="60" t="n"/>
+      <c r="B163" s="63" t="n"/>
+      <c r="C163" s="64" t="n"/>
+      <c r="D163" s="65" t="n"/>
+      <c r="E163" s="65" t="n"/>
+      <c r="F163" s="66" t="n"/>
     </row>
     <row r="164">
-      <c r="B164" s="57" t="n"/>
-      <c r="C164" s="58" t="n"/>
-      <c r="D164" s="59" t="n"/>
-      <c r="E164" s="59" t="n"/>
-      <c r="F164" s="60" t="n"/>
+      <c r="B164" s="63" t="n"/>
+      <c r="C164" s="64" t="n"/>
+      <c r="D164" s="65" t="n"/>
+      <c r="E164" s="65" t="n"/>
+      <c r="F164" s="66" t="n"/>
     </row>
     <row r="165">
-      <c r="B165" s="57" t="n"/>
-      <c r="C165" s="58" t="n"/>
-      <c r="D165" s="59" t="n"/>
-      <c r="E165" s="59" t="n"/>
-      <c r="F165" s="60" t="n"/>
+      <c r="B165" s="63" t="n"/>
+      <c r="C165" s="64" t="n"/>
+      <c r="D165" s="65" t="n"/>
+      <c r="E165" s="65" t="n"/>
+      <c r="F165" s="66" t="n"/>
     </row>
     <row r="166">
-      <c r="B166" s="57" t="n"/>
-      <c r="C166" s="58" t="n"/>
-      <c r="D166" s="59" t="n"/>
-      <c r="E166" s="59" t="n"/>
-      <c r="F166" s="60" t="n"/>
+      <c r="B166" s="63" t="n"/>
+      <c r="C166" s="64" t="n"/>
+      <c r="D166" s="65" t="n"/>
+      <c r="E166" s="65" t="n"/>
+      <c r="F166" s="66" t="n"/>
     </row>
     <row r="167">
-      <c r="B167" s="57" t="n"/>
-      <c r="C167" s="58" t="n"/>
-      <c r="D167" s="59" t="n"/>
-      <c r="E167" s="59" t="n"/>
-      <c r="F167" s="60" t="n"/>
+      <c r="B167" s="63" t="n"/>
+      <c r="C167" s="64" t="n"/>
+      <c r="D167" s="65" t="n"/>
+      <c r="E167" s="65" t="n"/>
+      <c r="F167" s="66" t="n"/>
     </row>
     <row r="168">
-      <c r="B168" s="57" t="n"/>
-      <c r="C168" s="58" t="n"/>
-      <c r="D168" s="59" t="n"/>
-      <c r="E168" s="59" t="n"/>
-      <c r="F168" s="60" t="n"/>
+      <c r="B168" s="63" t="n"/>
+      <c r="C168" s="64" t="n"/>
+      <c r="D168" s="65" t="n"/>
+      <c r="E168" s="65" t="n"/>
+      <c r="F168" s="66" t="n"/>
     </row>
     <row r="169">
-      <c r="B169" s="57" t="n"/>
-      <c r="C169" s="58" t="n"/>
-      <c r="D169" s="59" t="n"/>
-      <c r="E169" s="59" t="n"/>
-      <c r="F169" s="60" t="n"/>
+      <c r="B169" s="63" t="n"/>
+      <c r="C169" s="64" t="n"/>
+      <c r="D169" s="65" t="n"/>
+      <c r="E169" s="65" t="n"/>
+      <c r="F169" s="66" t="n"/>
     </row>
     <row r="170">
-      <c r="B170" s="57" t="n"/>
-      <c r="C170" s="58" t="n"/>
-      <c r="D170" s="59" t="n"/>
-      <c r="E170" s="59" t="n"/>
-      <c r="F170" s="60" t="n"/>
+      <c r="B170" s="63" t="n"/>
+      <c r="C170" s="64" t="n"/>
+      <c r="D170" s="65" t="n"/>
+      <c r="E170" s="65" t="n"/>
+      <c r="F170" s="66" t="n"/>
     </row>
     <row r="171">
-      <c r="B171" s="57" t="n"/>
-      <c r="C171" s="58" t="n"/>
-      <c r="D171" s="59" t="n"/>
-      <c r="E171" s="59" t="n"/>
-      <c r="F171" s="60" t="n"/>
+      <c r="B171" s="63" t="n"/>
+      <c r="C171" s="64" t="n"/>
+      <c r="D171" s="65" t="n"/>
+      <c r="E171" s="65" t="n"/>
+      <c r="F171" s="66" t="n"/>
     </row>
     <row r="172">
-      <c r="B172" s="57" t="n"/>
-      <c r="C172" s="58" t="n"/>
-      <c r="D172" s="59" t="n"/>
-      <c r="E172" s="59" t="n"/>
-      <c r="F172" s="60" t="n"/>
+      <c r="B172" s="63" t="n"/>
+      <c r="C172" s="64" t="n"/>
+      <c r="D172" s="65" t="n"/>
+      <c r="E172" s="65" t="n"/>
+      <c r="F172" s="66" t="n"/>
     </row>
     <row r="173">
-      <c r="B173" s="57" t="n"/>
-      <c r="C173" s="58" t="n"/>
-      <c r="D173" s="59" t="n"/>
-      <c r="E173" s="59" t="n"/>
-      <c r="F173" s="60" t="n"/>
+      <c r="B173" s="63" t="n"/>
+      <c r="C173" s="64" t="n"/>
+      <c r="D173" s="65" t="n"/>
+      <c r="E173" s="65" t="n"/>
+      <c r="F173" s="66" t="n"/>
     </row>
     <row r="174">
-      <c r="B174" s="57" t="n"/>
-      <c r="C174" s="58" t="n"/>
-      <c r="D174" s="59" t="n"/>
-      <c r="E174" s="59" t="n"/>
-      <c r="F174" s="60" t="n"/>
+      <c r="B174" s="63" t="n"/>
+      <c r="C174" s="64" t="n"/>
+      <c r="D174" s="65" t="n"/>
+      <c r="E174" s="65" t="n"/>
+      <c r="F174" s="66" t="n"/>
     </row>
     <row r="175">
-      <c r="B175" s="57" t="n"/>
-      <c r="C175" s="58" t="n"/>
-      <c r="D175" s="59" t="n"/>
-      <c r="E175" s="59" t="n"/>
-      <c r="F175" s="60" t="n"/>
+      <c r="B175" s="63" t="n"/>
+      <c r="C175" s="64" t="n"/>
+      <c r="D175" s="65" t="n"/>
+      <c r="E175" s="65" t="n"/>
+      <c r="F175" s="66" t="n"/>
     </row>
     <row r="176">
-      <c r="B176" s="57" t="n"/>
-      <c r="C176" s="58" t="n"/>
-      <c r="D176" s="59" t="n"/>
-      <c r="E176" s="59" t="n"/>
-      <c r="F176" s="60" t="n"/>
+      <c r="B176" s="63" t="n"/>
+      <c r="C176" s="64" t="n"/>
+      <c r="D176" s="65" t="n"/>
+      <c r="E176" s="65" t="n"/>
+      <c r="F176" s="66" t="n"/>
     </row>
     <row r="177">
-      <c r="B177" s="57" t="n"/>
-      <c r="C177" s="58" t="n"/>
-      <c r="D177" s="59" t="n"/>
-      <c r="E177" s="59" t="n"/>
-      <c r="F177" s="60" t="n"/>
+      <c r="B177" s="63" t="n"/>
+      <c r="C177" s="64" t="n"/>
+      <c r="D177" s="65" t="n"/>
+      <c r="E177" s="65" t="n"/>
+      <c r="F177" s="66" t="n"/>
     </row>
     <row r="178">
-      <c r="B178" s="57" t="n"/>
-      <c r="C178" s="58" t="n"/>
-      <c r="D178" s="59" t="n"/>
-      <c r="E178" s="59" t="n"/>
-      <c r="F178" s="60" t="n"/>
+      <c r="B178" s="63" t="n"/>
+      <c r="C178" s="64" t="n"/>
+      <c r="D178" s="65" t="n"/>
+      <c r="E178" s="65" t="n"/>
+      <c r="F178" s="66" t="n"/>
     </row>
     <row r="179">
-      <c r="B179" s="57" t="n"/>
-      <c r="C179" s="58" t="n"/>
-      <c r="D179" s="59" t="n"/>
-      <c r="E179" s="59" t="n"/>
-      <c r="F179" s="60" t="n"/>
+      <c r="B179" s="63" t="n"/>
+      <c r="C179" s="64" t="n"/>
+      <c r="D179" s="65" t="n"/>
+      <c r="E179" s="65" t="n"/>
+      <c r="F179" s="66" t="n"/>
     </row>
     <row r="180">
-      <c r="B180" s="57" t="n"/>
-      <c r="C180" s="58" t="n"/>
-      <c r="D180" s="59" t="n"/>
-      <c r="E180" s="59" t="n"/>
-      <c r="F180" s="60" t="n"/>
+      <c r="B180" s="63" t="n"/>
+      <c r="C180" s="64" t="n"/>
+      <c r="D180" s="65" t="n"/>
+      <c r="E180" s="65" t="n"/>
+      <c r="F180" s="66" t="n"/>
     </row>
     <row r="181">
-      <c r="B181" s="57" t="n"/>
-      <c r="C181" s="58" t="n"/>
-      <c r="D181" s="59" t="n"/>
-      <c r="E181" s="59" t="n"/>
-      <c r="F181" s="60" t="n"/>
+      <c r="B181" s="63" t="n"/>
+      <c r="C181" s="64" t="n"/>
+      <c r="D181" s="65" t="n"/>
+      <c r="E181" s="65" t="n"/>
+      <c r="F181" s="66" t="n"/>
     </row>
     <row r="182">
-      <c r="B182" s="57" t="n"/>
-      <c r="C182" s="58" t="n"/>
-      <c r="D182" s="59" t="n"/>
-      <c r="E182" s="59" t="n"/>
-      <c r="F182" s="60" t="n"/>
+      <c r="B182" s="63" t="n"/>
+      <c r="C182" s="64" t="n"/>
+      <c r="D182" s="65" t="n"/>
+      <c r="E182" s="65" t="n"/>
+      <c r="F182" s="66" t="n"/>
     </row>
     <row r="183">
-      <c r="B183" s="57" t="n"/>
-      <c r="C183" s="58" t="n"/>
-      <c r="D183" s="59" t="n"/>
-      <c r="E183" s="59" t="n"/>
-      <c r="F183" s="60" t="n"/>
+      <c r="B183" s="63" t="n"/>
+      <c r="C183" s="64" t="n"/>
+      <c r="D183" s="65" t="n"/>
+      <c r="E183" s="65" t="n"/>
+      <c r="F183" s="66" t="n"/>
     </row>
     <row r="184">
-      <c r="B184" s="57" t="n"/>
-      <c r="C184" s="58" t="n"/>
-      <c r="D184" s="59" t="n"/>
-      <c r="E184" s="59" t="n"/>
-      <c r="F184" s="60" t="n"/>
+      <c r="B184" s="63" t="n"/>
+      <c r="C184" s="64" t="n"/>
+      <c r="D184" s="65" t="n"/>
+      <c r="E184" s="65" t="n"/>
+      <c r="F184" s="66" t="n"/>
     </row>
     <row r="185">
-      <c r="B185" s="57" t="n"/>
-      <c r="C185" s="58" t="n"/>
-      <c r="D185" s="59" t="n"/>
-      <c r="E185" s="59" t="n"/>
-      <c r="F185" s="60" t="n"/>
+      <c r="B185" s="63" t="n"/>
+      <c r="C185" s="64" t="n"/>
+      <c r="D185" s="65" t="n"/>
+      <c r="E185" s="65" t="n"/>
+      <c r="F185" s="66" t="n"/>
     </row>
     <row r="186">
-      <c r="B186" s="57" t="n"/>
-      <c r="C186" s="58" t="n"/>
-      <c r="D186" s="59" t="n"/>
-      <c r="E186" s="59" t="n"/>
-      <c r="F186" s="60" t="n"/>
+      <c r="B186" s="63" t="n"/>
+      <c r="C186" s="64" t="n"/>
+      <c r="D186" s="65" t="n"/>
+      <c r="E186" s="65" t="n"/>
+      <c r="F186" s="66" t="n"/>
     </row>
     <row r="187">
-      <c r="B187" s="57" t="n"/>
-      <c r="C187" s="58" t="n"/>
-      <c r="D187" s="59" t="n"/>
-      <c r="E187" s="59" t="n"/>
-      <c r="F187" s="60" t="n"/>
+      <c r="B187" s="63" t="n"/>
+      <c r="C187" s="64" t="n"/>
+      <c r="D187" s="65" t="n"/>
+      <c r="E187" s="65" t="n"/>
+      <c r="F187" s="66" t="n"/>
     </row>
     <row r="188">
-      <c r="B188" s="57" t="n"/>
-      <c r="C188" s="58" t="n"/>
-      <c r="D188" s="59" t="n"/>
-      <c r="E188" s="59" t="n"/>
-      <c r="F188" s="60" t="n"/>
+      <c r="B188" s="63" t="n"/>
+      <c r="C188" s="64" t="n"/>
+      <c r="D188" s="65" t="n"/>
+      <c r="E188" s="65" t="n"/>
+      <c r="F188" s="66" t="n"/>
     </row>
     <row r="189">
-      <c r="B189" s="57" t="n"/>
-      <c r="C189" s="58" t="n"/>
-      <c r="D189" s="59" t="n"/>
-      <c r="E189" s="59" t="n"/>
-      <c r="F189" s="60" t="n"/>
+      <c r="B189" s="63" t="n"/>
+      <c r="C189" s="64" t="n"/>
+      <c r="D189" s="65" t="n"/>
+      <c r="E189" s="65" t="n"/>
+      <c r="F189" s="66" t="n"/>
     </row>
     <row r="190">
-      <c r="B190" s="57" t="n"/>
-      <c r="C190" s="58" t="n"/>
-      <c r="D190" s="59" t="n"/>
-      <c r="E190" s="59" t="n"/>
-      <c r="F190" s="60" t="n"/>
+      <c r="B190" s="63" t="n"/>
+      <c r="C190" s="64" t="n"/>
+      <c r="D190" s="65" t="n"/>
+      <c r="E190" s="65" t="n"/>
+      <c r="F190" s="66" t="n"/>
     </row>
     <row r="191">
-      <c r="B191" s="57" t="n"/>
-      <c r="C191" s="58" t="n"/>
-      <c r="D191" s="59" t="n"/>
-      <c r="E191" s="59" t="n"/>
-      <c r="F191" s="60" t="n"/>
+      <c r="B191" s="63" t="n"/>
+      <c r="C191" s="64" t="n"/>
+      <c r="D191" s="65" t="n"/>
+      <c r="E191" s="65" t="n"/>
+      <c r="F191" s="66" t="n"/>
     </row>
     <row r="192">
-      <c r="B192" s="57" t="n"/>
-      <c r="C192" s="58" t="n"/>
-      <c r="D192" s="59" t="n"/>
-      <c r="E192" s="59" t="n"/>
-      <c r="F192" s="60" t="n"/>
+      <c r="B192" s="63" t="n"/>
+      <c r="C192" s="64" t="n"/>
+      <c r="D192" s="65" t="n"/>
+      <c r="E192" s="65" t="n"/>
+      <c r="F192" s="66" t="n"/>
     </row>
     <row r="193">
-      <c r="B193" s="57" t="n"/>
-      <c r="C193" s="58" t="n"/>
-      <c r="D193" s="59" t="n"/>
-      <c r="E193" s="59" t="n"/>
-      <c r="F193" s="60" t="n"/>
+      <c r="B193" s="63" t="n"/>
+      <c r="C193" s="64" t="n"/>
+      <c r="D193" s="65" t="n"/>
+      <c r="E193" s="65" t="n"/>
+      <c r="F193" s="66" t="n"/>
     </row>
     <row r="194">
-      <c r="B194" s="57" t="n"/>
-      <c r="C194" s="58" t="n"/>
-      <c r="D194" s="59" t="n"/>
-      <c r="E194" s="59" t="n"/>
-      <c r="F194" s="60" t="n"/>
+      <c r="B194" s="63" t="n"/>
+      <c r="C194" s="64" t="n"/>
+      <c r="D194" s="65" t="n"/>
+      <c r="E194" s="65" t="n"/>
+      <c r="F194" s="66" t="n"/>
     </row>
     <row r="195">
-      <c r="B195" s="57" t="n"/>
-      <c r="C195" s="58" t="n"/>
-      <c r="D195" s="59" t="n"/>
-      <c r="E195" s="59" t="n"/>
-      <c r="F195" s="60" t="n"/>
+      <c r="B195" s="63" t="n"/>
+      <c r="C195" s="64" t="n"/>
+      <c r="D195" s="65" t="n"/>
+      <c r="E195" s="65" t="n"/>
+      <c r="F195" s="66" t="n"/>
     </row>
     <row r="196">
-      <c r="B196" s="57" t="n"/>
-      <c r="C196" s="58" t="n"/>
-      <c r="D196" s="59" t="n"/>
-      <c r="E196" s="59" t="n"/>
-      <c r="F196" s="60" t="n"/>
+      <c r="B196" s="63" t="n"/>
+      <c r="C196" s="64" t="n"/>
+      <c r="D196" s="65" t="n"/>
+      <c r="E196" s="65" t="n"/>
+      <c r="F196" s="66" t="n"/>
     </row>
     <row r="197">
-      <c r="B197" s="57" t="n"/>
-      <c r="C197" s="58" t="n"/>
-      <c r="D197" s="59" t="n"/>
-      <c r="E197" s="59" t="n"/>
-      <c r="F197" s="60" t="n"/>
+      <c r="B197" s="63" t="n"/>
+      <c r="C197" s="64" t="n"/>
+      <c r="D197" s="65" t="n"/>
+      <c r="E197" s="65" t="n"/>
+      <c r="F197" s="66" t="n"/>
     </row>
     <row r="198">
-      <c r="B198" s="57" t="n"/>
-      <c r="C198" s="58" t="n"/>
-      <c r="D198" s="59" t="n"/>
-      <c r="E198" s="59" t="n"/>
-      <c r="F198" s="60" t="n"/>
+      <c r="B198" s="63" t="n"/>
+      <c r="C198" s="64" t="n"/>
+      <c r="D198" s="65" t="n"/>
+      <c r="E198" s="65" t="n"/>
+      <c r="F198" s="66" t="n"/>
     </row>
     <row r="199">
-      <c r="B199" s="57" t="n"/>
-      <c r="C199" s="58" t="n"/>
-      <c r="D199" s="59" t="n"/>
-      <c r="E199" s="59" t="n"/>
-      <c r="F199" s="60" t="n"/>
+      <c r="B199" s="63" t="n"/>
+      <c r="C199" s="64" t="n"/>
+      <c r="D199" s="65" t="n"/>
+      <c r="E199" s="65" t="n"/>
+      <c r="F199" s="66" t="n"/>
     </row>
     <row r="200">
-      <c r="B200" s="57" t="n"/>
-      <c r="C200" s="58" t="n"/>
-      <c r="D200" s="59" t="n"/>
-      <c r="E200" s="59" t="n"/>
-      <c r="F200" s="60" t="n"/>
+      <c r="B200" s="63" t="n"/>
+      <c r="C200" s="64" t="n"/>
+      <c r="D200" s="65" t="n"/>
+      <c r="E200" s="65" t="n"/>
+      <c r="F200" s="66" t="n"/>
     </row>
     <row r="201">
-      <c r="B201" s="57" t="n"/>
-      <c r="C201" s="58" t="n"/>
-      <c r="D201" s="59" t="n"/>
-      <c r="E201" s="59" t="n"/>
-      <c r="F201" s="60" t="n"/>
+      <c r="B201" s="63" t="n"/>
+      <c r="C201" s="64" t="n"/>
+      <c r="D201" s="65" t="n"/>
+      <c r="E201" s="65" t="n"/>
+      <c r="F201" s="66" t="n"/>
     </row>
     <row r="202">
-      <c r="B202" s="57" t="n"/>
-      <c r="C202" s="58" t="n"/>
-      <c r="D202" s="59" t="n"/>
-      <c r="E202" s="59" t="n"/>
-      <c r="F202" s="60" t="n"/>
+      <c r="B202" s="63" t="n"/>
+      <c r="C202" s="64" t="n"/>
+      <c r="D202" s="65" t="n"/>
+      <c r="E202" s="65" t="n"/>
+      <c r="F202" s="66" t="n"/>
     </row>
     <row r="203">
-      <c r="B203" s="57" t="n"/>
-      <c r="C203" s="58" t="n"/>
-      <c r="D203" s="59" t="n"/>
-      <c r="E203" s="59" t="n"/>
-      <c r="F203" s="60" t="n"/>
+      <c r="B203" s="63" t="n"/>
+      <c r="C203" s="64" t="n"/>
+      <c r="D203" s="65" t="n"/>
+      <c r="E203" s="65" t="n"/>
+      <c r="F203" s="66" t="n"/>
     </row>
     <row r="204">
-      <c r="B204" s="57" t="n"/>
-      <c r="C204" s="58" t="n"/>
-      <c r="D204" s="59" t="n"/>
-      <c r="E204" s="59" t="n"/>
-      <c r="F204" s="60" t="n"/>
+      <c r="B204" s="63" t="n"/>
+      <c r="C204" s="64" t="n"/>
+      <c r="D204" s="65" t="n"/>
+      <c r="E204" s="65" t="n"/>
+      <c r="F204" s="66" t="n"/>
     </row>
     <row r="205">
-      <c r="B205" s="57" t="n"/>
-      <c r="C205" s="58" t="n"/>
-      <c r="D205" s="59" t="n"/>
-      <c r="E205" s="59" t="n"/>
-      <c r="F205" s="60" t="n"/>
+      <c r="B205" s="63" t="n"/>
+      <c r="C205" s="64" t="n"/>
+      <c r="D205" s="65" t="n"/>
+      <c r="E205" s="65" t="n"/>
+      <c r="F205" s="66" t="n"/>
     </row>
     <row r="206">
-      <c r="B206" s="57" t="n"/>
-      <c r="C206" s="58" t="n"/>
-      <c r="D206" s="59" t="n"/>
-      <c r="E206" s="59" t="n"/>
-      <c r="F206" s="60" t="n"/>
+      <c r="B206" s="63" t="n"/>
+      <c r="C206" s="64" t="n"/>
+      <c r="D206" s="65" t="n"/>
+      <c r="E206" s="65" t="n"/>
+      <c r="F206" s="66" t="n"/>
     </row>
     <row r="207">
-      <c r="B207" s="57" t="n"/>
-      <c r="C207" s="58" t="n"/>
-      <c r="D207" s="59" t="n"/>
-      <c r="E207" s="59" t="n"/>
-      <c r="F207" s="60" t="n"/>
+      <c r="B207" s="63" t="n"/>
+      <c r="C207" s="64" t="n"/>
+      <c r="D207" s="65" t="n"/>
+      <c r="E207" s="65" t="n"/>
+      <c r="F207" s="66" t="n"/>
     </row>
     <row r="208">
-      <c r="B208" s="57" t="n"/>
-      <c r="C208" s="58" t="n"/>
-      <c r="D208" s="59" t="n"/>
-      <c r="E208" s="59" t="n"/>
-      <c r="F208" s="60" t="n"/>
+      <c r="B208" s="63" t="n"/>
+      <c r="C208" s="64" t="n"/>
+      <c r="D208" s="65" t="n"/>
+      <c r="E208" s="65" t="n"/>
+      <c r="F208" s="66" t="n"/>
     </row>
     <row r="209">
-      <c r="B209" s="57" t="n"/>
-      <c r="C209" s="58" t="n"/>
-      <c r="D209" s="59" t="n"/>
-      <c r="E209" s="59" t="n"/>
-      <c r="F209" s="60" t="n"/>
+      <c r="B209" s="63" t="n"/>
+      <c r="C209" s="64" t="n"/>
+      <c r="D209" s="65" t="n"/>
+      <c r="E209" s="65" t="n"/>
+      <c r="F209" s="66" t="n"/>
     </row>
     <row r="210">
-      <c r="B210" s="57" t="n"/>
-      <c r="C210" s="58" t="n"/>
-      <c r="D210" s="59" t="n"/>
-      <c r="E210" s="59" t="n"/>
-      <c r="F210" s="60" t="n"/>
+      <c r="B210" s="63" t="n"/>
+      <c r="C210" s="64" t="n"/>
+      <c r="D210" s="65" t="n"/>
+      <c r="E210" s="65" t="n"/>
+      <c r="F210" s="66" t="n"/>
     </row>
     <row r="211">
-      <c r="B211" s="57" t="n"/>
-      <c r="C211" s="58" t="n"/>
-      <c r="D211" s="59" t="n"/>
-      <c r="E211" s="59" t="n"/>
-      <c r="F211" s="60" t="n"/>
+      <c r="B211" s="63" t="n"/>
+      <c r="C211" s="64" t="n"/>
+      <c r="D211" s="65" t="n"/>
+      <c r="E211" s="65" t="n"/>
+      <c r="F211" s="66" t="n"/>
     </row>
     <row r="212">
-      <c r="B212" s="57" t="n"/>
-      <c r="C212" s="58" t="n"/>
-      <c r="D212" s="59" t="n"/>
-      <c r="E212" s="59" t="n"/>
-      <c r="F212" s="60" t="n"/>
+      <c r="B212" s="63" t="n"/>
+      <c r="C212" s="64" t="n"/>
+      <c r="D212" s="65" t="n"/>
+      <c r="E212" s="65" t="n"/>
+      <c r="F212" s="66" t="n"/>
     </row>
     <row r="213">
-      <c r="B213" s="57" t="n"/>
-      <c r="C213" s="58" t="n"/>
-      <c r="D213" s="59" t="n"/>
-      <c r="E213" s="59" t="n"/>
-      <c r="F213" s="60" t="n"/>
+      <c r="B213" s="63" t="n"/>
+      <c r="C213" s="64" t="n"/>
+      <c r="D213" s="65" t="n"/>
+      <c r="E213" s="65" t="n"/>
+      <c r="F213" s="66" t="n"/>
     </row>
     <row r="214">
-      <c r="B214" s="57" t="n"/>
-      <c r="C214" s="58" t="n"/>
-      <c r="D214" s="59" t="n"/>
-      <c r="E214" s="59" t="n"/>
-      <c r="F214" s="60" t="n"/>
+      <c r="B214" s="63" t="n"/>
+      <c r="C214" s="64" t="n"/>
+      <c r="D214" s="65" t="n"/>
+      <c r="E214" s="65" t="n"/>
+      <c r="F214" s="66" t="n"/>
     </row>
     <row r="215">
-      <c r="B215" s="57" t="n"/>
-      <c r="C215" s="58" t="n"/>
-      <c r="D215" s="59" t="n"/>
-      <c r="E215" s="59" t="n"/>
-      <c r="F215" s="60" t="n"/>
+      <c r="B215" s="63" t="n"/>
+      <c r="C215" s="64" t="n"/>
+      <c r="D215" s="65" t="n"/>
+      <c r="E215" s="65" t="n"/>
+      <c r="F215" s="66" t="n"/>
     </row>
     <row r="216">
-      <c r="B216" s="57" t="n"/>
-      <c r="C216" s="58" t="n"/>
-      <c r="D216" s="59" t="n"/>
-      <c r="E216" s="59" t="n"/>
-      <c r="F216" s="60" t="n"/>
+      <c r="B216" s="63" t="n"/>
+      <c r="C216" s="64" t="n"/>
+      <c r="D216" s="65" t="n"/>
+      <c r="E216" s="65" t="n"/>
+      <c r="F216" s="66" t="n"/>
     </row>
     <row r="217">
-      <c r="B217" s="57" t="n"/>
-      <c r="C217" s="58" t="n"/>
-      <c r="D217" s="59" t="n"/>
-      <c r="E217" s="59" t="n"/>
-      <c r="F217" s="60" t="n"/>
+      <c r="B217" s="63" t="n"/>
+      <c r="C217" s="64" t="n"/>
+      <c r="D217" s="65" t="n"/>
+      <c r="E217" s="65" t="n"/>
+      <c r="F217" s="66" t="n"/>
     </row>
     <row r="218">
-      <c r="B218" s="57" t="n"/>
-      <c r="C218" s="58" t="n"/>
-      <c r="D218" s="59" t="n"/>
-      <c r="E218" s="59" t="n"/>
-      <c r="F218" s="60" t="n"/>
+      <c r="B218" s="63" t="n"/>
+      <c r="C218" s="64" t="n"/>
+      <c r="D218" s="65" t="n"/>
+      <c r="E218" s="65" t="n"/>
+      <c r="F218" s="66" t="n"/>
     </row>
     <row r="219">
-      <c r="B219" s="57" t="n"/>
-      <c r="C219" s="58" t="n"/>
-      <c r="D219" s="59" t="n"/>
-      <c r="E219" s="59" t="n"/>
-      <c r="F219" s="60" t="n"/>
+      <c r="B219" s="63" t="n"/>
+      <c r="C219" s="64" t="n"/>
+      <c r="D219" s="65" t="n"/>
+      <c r="E219" s="65" t="n"/>
+      <c r="F219" s="66" t="n"/>
     </row>
     <row r="220">
-      <c r="B220" s="57" t="n"/>
-      <c r="C220" s="58" t="n"/>
-      <c r="D220" s="59" t="n"/>
-      <c r="E220" s="59" t="n"/>
-      <c r="F220" s="60" t="n"/>
+      <c r="B220" s="63" t="n"/>
+      <c r="C220" s="64" t="n"/>
+      <c r="D220" s="65" t="n"/>
+      <c r="E220" s="65" t="n"/>
+      <c r="F220" s="66" t="n"/>
     </row>
     <row r="221">
-      <c r="B221" s="57" t="n"/>
-      <c r="C221" s="58" t="n"/>
-      <c r="D221" s="59" t="n"/>
-      <c r="E221" s="59" t="n"/>
-      <c r="F221" s="60" t="n"/>
+      <c r="B221" s="63" t="n"/>
+      <c r="C221" s="64" t="n"/>
+      <c r="D221" s="65" t="n"/>
+      <c r="E221" s="65" t="n"/>
+      <c r="F221" s="66" t="n"/>
     </row>
     <row r="222">
-      <c r="B222" s="57" t="n"/>
-      <c r="C222" s="58" t="n"/>
-      <c r="D222" s="59" t="n"/>
-      <c r="E222" s="59" t="n"/>
-      <c r="F222" s="60" t="n"/>
+      <c r="B222" s="63" t="n"/>
+      <c r="C222" s="64" t="n"/>
+      <c r="D222" s="65" t="n"/>
+      <c r="E222" s="65" t="n"/>
+      <c r="F222" s="66" t="n"/>
     </row>
     <row r="223">
-      <c r="B223" s="57" t="n"/>
-      <c r="C223" s="58" t="n"/>
-      <c r="D223" s="59" t="n"/>
-      <c r="E223" s="59" t="n"/>
-      <c r="F223" s="60" t="n"/>
+      <c r="B223" s="63" t="n"/>
+      <c r="C223" s="64" t="n"/>
+      <c r="D223" s="65" t="n"/>
+      <c r="E223" s="65" t="n"/>
+      <c r="F223" s="66" t="n"/>
     </row>
     <row r="224">
-      <c r="B224" s="57" t="n"/>
-      <c r="C224" s="58" t="n"/>
-      <c r="D224" s="59" t="n"/>
-      <c r="E224" s="59" t="n"/>
-      <c r="F224" s="60" t="n"/>
+      <c r="B224" s="63" t="n"/>
+      <c r="C224" s="64" t="n"/>
+      <c r="D224" s="65" t="n"/>
+      <c r="E224" s="65" t="n"/>
+      <c r="F224" s="66" t="n"/>
     </row>
     <row r="225">
-      <c r="B225" s="57" t="n"/>
-      <c r="C225" s="58" t="n"/>
-      <c r="D225" s="59" t="n"/>
-      <c r="E225" s="59" t="n"/>
-      <c r="F225" s="60" t="n"/>
+      <c r="B225" s="63" t="n"/>
+      <c r="C225" s="64" t="n"/>
+      <c r="D225" s="65" t="n"/>
+      <c r="E225" s="65" t="n"/>
+      <c r="F225" s="66" t="n"/>
     </row>
     <row r="226">
-      <c r="B226" s="57" t="n"/>
-      <c r="C226" s="58" t="n"/>
-      <c r="D226" s="59" t="n"/>
-      <c r="E226" s="59" t="n"/>
-      <c r="F226" s="60" t="n"/>
+      <c r="B226" s="63" t="n"/>
+      <c r="C226" s="64" t="n"/>
+      <c r="D226" s="65" t="n"/>
+      <c r="E226" s="65" t="n"/>
+      <c r="F226" s="66" t="n"/>
     </row>
     <row r="227">
-      <c r="B227" s="57" t="n"/>
-      <c r="C227" s="58" t="n"/>
-      <c r="D227" s="59" t="n"/>
-      <c r="E227" s="59" t="n"/>
-      <c r="F227" s="60" t="n"/>
+      <c r="B227" s="63" t="n"/>
+      <c r="C227" s="64" t="n"/>
+      <c r="D227" s="65" t="n"/>
+      <c r="E227" s="65" t="n"/>
+      <c r="F227" s="66" t="n"/>
     </row>
     <row r="228">
-      <c r="B228" s="57" t="n"/>
-      <c r="C228" s="58" t="n"/>
-      <c r="D228" s="59" t="n"/>
-      <c r="E228" s="59" t="n"/>
-      <c r="F228" s="60" t="n"/>
+      <c r="B228" s="63" t="n"/>
+      <c r="C228" s="64" t="n"/>
+      <c r="D228" s="65" t="n"/>
+      <c r="E228" s="65" t="n"/>
+      <c r="F228" s="66" t="n"/>
     </row>
     <row r="229">
-      <c r="B229" s="57" t="n"/>
-      <c r="C229" s="58" t="n"/>
-      <c r="D229" s="59" t="n"/>
-      <c r="E229" s="59" t="n"/>
-      <c r="F229" s="60" t="n"/>
+      <c r="B229" s="63" t="n"/>
+      <c r="C229" s="64" t="n"/>
+      <c r="D229" s="65" t="n"/>
+      <c r="E229" s="65" t="n"/>
+      <c r="F229" s="66" t="n"/>
     </row>
     <row r="230">
-      <c r="B230" s="57" t="n"/>
-      <c r="C230" s="58" t="n"/>
-      <c r="D230" s="59" t="n"/>
-      <c r="E230" s="59" t="n"/>
-      <c r="F230" s="60" t="n"/>
+      <c r="B230" s="63" t="n"/>
+      <c r="C230" s="64" t="n"/>
+      <c r="D230" s="65" t="n"/>
+      <c r="E230" s="65" t="n"/>
+      <c r="F230" s="66" t="n"/>
     </row>
     <row r="231">
-      <c r="B231" s="57" t="n"/>
-      <c r="C231" s="58" t="n"/>
-      <c r="D231" s="59" t="n"/>
-      <c r="E231" s="59" t="n"/>
-      <c r="F231" s="60" t="n"/>
+      <c r="B231" s="63" t="n"/>
+      <c r="C231" s="64" t="n"/>
+      <c r="D231" s="65" t="n"/>
+      <c r="E231" s="65" t="n"/>
+      <c r="F231" s="66" t="n"/>
     </row>
     <row r="232">
-      <c r="B232" s="57" t="n"/>
-      <c r="C232" s="58" t="n"/>
-      <c r="D232" s="59" t="n"/>
-      <c r="E232" s="59" t="n"/>
-      <c r="F232" s="60" t="n"/>
+      <c r="B232" s="63" t="n"/>
+      <c r="C232" s="64" t="n"/>
+      <c r="D232" s="65" t="n"/>
+      <c r="E232" s="65" t="n"/>
+      <c r="F232" s="66" t="n"/>
     </row>
     <row r="233">
-      <c r="B233" s="57" t="n"/>
-      <c r="C233" s="58" t="n"/>
-      <c r="D233" s="59" t="n"/>
-      <c r="E233" s="59" t="n"/>
-      <c r="F233" s="60" t="n"/>
+      <c r="B233" s="63" t="n"/>
+      <c r="C233" s="64" t="n"/>
+      <c r="D233" s="65" t="n"/>
+      <c r="E233" s="65" t="n"/>
+      <c r="F233" s="66" t="n"/>
     </row>
     <row r="234">
-      <c r="B234" s="57" t="n"/>
-      <c r="C234" s="58" t="n"/>
-      <c r="D234" s="59" t="n"/>
-      <c r="E234" s="59" t="n"/>
-      <c r="F234" s="60" t="n"/>
+      <c r="B234" s="63" t="n"/>
+      <c r="C234" s="64" t="n"/>
+      <c r="D234" s="65" t="n"/>
+      <c r="E234" s="65" t="n"/>
+      <c r="F234" s="66" t="n"/>
     </row>
     <row r="235">
-      <c r="B235" s="57" t="n"/>
-      <c r="C235" s="58" t="n"/>
-      <c r="D235" s="59" t="n"/>
-      <c r="E235" s="59" t="n"/>
-      <c r="F235" s="60" t="n"/>
+      <c r="B235" s="63" t="n"/>
+      <c r="C235" s="64" t="n"/>
+      <c r="D235" s="65" t="n"/>
+      <c r="E235" s="65" t="n"/>
+      <c r="F235" s="66" t="n"/>
     </row>
     <row r="236">
-      <c r="B236" s="57" t="n"/>
-      <c r="C236" s="58" t="n"/>
-      <c r="D236" s="59" t="n"/>
-      <c r="E236" s="59" t="n"/>
-      <c r="F236" s="60" t="n"/>
+      <c r="B236" s="63" t="n"/>
+      <c r="C236" s="64" t="n"/>
+      <c r="D236" s="65" t="n"/>
+      <c r="E236" s="65" t="n"/>
+      <c r="F236" s="66" t="n"/>
     </row>
     <row r="237">
-      <c r="B237" s="57" t="n"/>
-      <c r="C237" s="58" t="n"/>
-      <c r="D237" s="59" t="n"/>
-      <c r="E237" s="59" t="n"/>
-      <c r="F237" s="60" t="n"/>
+      <c r="B237" s="63" t="n"/>
+      <c r="C237" s="64" t="n"/>
+      <c r="D237" s="65" t="n"/>
+      <c r="E237" s="65" t="n"/>
+      <c r="F237" s="66" t="n"/>
     </row>
     <row r="238">
-      <c r="B238" s="57" t="n"/>
-      <c r="C238" s="58" t="n"/>
-      <c r="D238" s="59" t="n"/>
-      <c r="E238" s="59" t="n"/>
-      <c r="F238" s="60" t="n"/>
+      <c r="B238" s="63" t="n"/>
+      <c r="C238" s="64" t="n"/>
+      <c r="D238" s="65" t="n"/>
+      <c r="E238" s="65" t="n"/>
+      <c r="F238" s="66" t="n"/>
     </row>
     <row r="239">
-      <c r="B239" s="57" t="n"/>
-      <c r="C239" s="58" t="n"/>
-      <c r="D239" s="59" t="n"/>
-      <c r="E239" s="59" t="n"/>
-      <c r="F239" s="60" t="n"/>
+      <c r="B239" s="63" t="n"/>
+      <c r="C239" s="64" t="n"/>
+      <c r="D239" s="65" t="n"/>
+      <c r="E239" s="65" t="n"/>
+      <c r="F239" s="66" t="n"/>
     </row>
     <row r="240">
-      <c r="B240" s="57" t="n"/>
-      <c r="C240" s="58" t="n"/>
-      <c r="D240" s="59" t="n"/>
-      <c r="E240" s="59" t="n"/>
-      <c r="F240" s="60" t="n"/>
+      <c r="B240" s="63" t="n"/>
+      <c r="C240" s="64" t="n"/>
+      <c r="D240" s="65" t="n"/>
+      <c r="E240" s="65" t="n"/>
+      <c r="F240" s="66" t="n"/>
     </row>
     <row r="241">
-      <c r="B241" s="57" t="n"/>
-      <c r="C241" s="58" t="n"/>
-      <c r="D241" s="59" t="n"/>
-      <c r="E241" s="59" t="n"/>
-      <c r="F241" s="60" t="n"/>
+      <c r="B241" s="63" t="n"/>
+      <c r="C241" s="64" t="n"/>
+      <c r="D241" s="65" t="n"/>
+      <c r="E241" s="65" t="n"/>
+      <c r="F241" s="66" t="n"/>
     </row>
     <row r="242">
-      <c r="B242" s="57" t="n"/>
-      <c r="C242" s="58" t="n"/>
-      <c r="D242" s="59" t="n"/>
-      <c r="E242" s="59" t="n"/>
-      <c r="F242" s="60" t="n"/>
+      <c r="B242" s="63" t="n"/>
+      <c r="C242" s="64" t="n"/>
+      <c r="D242" s="65" t="n"/>
+      <c r="E242" s="65" t="n"/>
+      <c r="F242" s="66" t="n"/>
     </row>
     <row r="243">
-      <c r="B243" s="57" t="n"/>
-      <c r="C243" s="58" t="n"/>
-      <c r="D243" s="59" t="n"/>
-      <c r="E243" s="59" t="n"/>
-      <c r="F243" s="60" t="n"/>
+      <c r="B243" s="63" t="n"/>
+      <c r="C243" s="64" t="n"/>
+      <c r="D243" s="65" t="n"/>
+      <c r="E243" s="65" t="n"/>
+      <c r="F243" s="66" t="n"/>
     </row>
     <row r="244">
-      <c r="B244" s="57" t="n"/>
-      <c r="C244" s="58" t="n"/>
-      <c r="D244" s="59" t="n"/>
-      <c r="E244" s="59" t="n"/>
-      <c r="F244" s="60" t="n"/>
+      <c r="B244" s="63" t="n"/>
+      <c r="C244" s="64" t="n"/>
+      <c r="D244" s="65" t="n"/>
+      <c r="E244" s="65" t="n"/>
+      <c r="F244" s="66" t="n"/>
     </row>
     <row r="245">
-      <c r="B245" s="57" t="n"/>
-      <c r="C245" s="58" t="n"/>
-      <c r="D245" s="59" t="n"/>
-      <c r="E245" s="59" t="n"/>
-      <c r="F245" s="60" t="n"/>
+      <c r="B245" s="63" t="n"/>
+      <c r="C245" s="64" t="n"/>
+      <c r="D245" s="65" t="n"/>
+      <c r="E245" s="65" t="n"/>
+      <c r="F245" s="66" t="n"/>
     </row>
     <row r="246">
-      <c r="B246" s="57" t="n"/>
-      <c r="C246" s="58" t="n"/>
-      <c r="D246" s="59" t="n"/>
-      <c r="E246" s="59" t="n"/>
-      <c r="F246" s="60" t="n"/>
+      <c r="B246" s="63" t="n"/>
+      <c r="C246" s="64" t="n"/>
+      <c r="D246" s="65" t="n"/>
+      <c r="E246" s="65" t="n"/>
+      <c r="F246" s="66" t="n"/>
     </row>
     <row r="247">
-      <c r="B247" s="57" t="n"/>
-      <c r="C247" s="58" t="n"/>
-      <c r="D247" s="59" t="n"/>
-      <c r="E247" s="59" t="n"/>
-      <c r="F247" s="60" t="n"/>
+      <c r="B247" s="63" t="n"/>
+      <c r="C247" s="64" t="n"/>
+      <c r="D247" s="65" t="n"/>
+      <c r="E247" s="65" t="n"/>
+      <c r="F247" s="66" t="n"/>
     </row>
     <row r="248">
-      <c r="B248" s="57" t="n"/>
-      <c r="C248" s="58" t="n"/>
-      <c r="D248" s="59" t="n"/>
-      <c r="E248" s="59" t="n"/>
-      <c r="F248" s="60" t="n"/>
+      <c r="B248" s="63" t="n"/>
+      <c r="C248" s="64" t="n"/>
+      <c r="D248" s="65" t="n"/>
+      <c r="E248" s="65" t="n"/>
+      <c r="F248" s="66" t="n"/>
     </row>
     <row r="249">
-      <c r="B249" s="57" t="n"/>
-      <c r="C249" s="58" t="n"/>
-      <c r="D249" s="59" t="n"/>
-      <c r="E249" s="59" t="n"/>
-      <c r="F249" s="60" t="n"/>
+      <c r="B249" s="63" t="n"/>
+      <c r="C249" s="64" t="n"/>
+      <c r="D249" s="65" t="n"/>
+      <c r="E249" s="65" t="n"/>
+      <c r="F249" s="66" t="n"/>
     </row>
     <row r="250">
-      <c r="B250" s="57" t="n"/>
-      <c r="C250" s="58" t="n"/>
-      <c r="D250" s="59" t="n"/>
-      <c r="E250" s="59" t="n"/>
-      <c r="F250" s="60" t="n"/>
+      <c r="B250" s="63" t="n"/>
+      <c r="C250" s="64" t="n"/>
+      <c r="D250" s="65" t="n"/>
+      <c r="E250" s="65" t="n"/>
+      <c r="F250" s="66" t="n"/>
     </row>
     <row r="251">
-      <c r="B251" s="57" t="n"/>
-      <c r="C251" s="58" t="n"/>
-      <c r="D251" s="59" t="n"/>
-      <c r="E251" s="59" t="n"/>
-      <c r="F251" s="60" t="n"/>
+      <c r="B251" s="63" t="n"/>
+      <c r="C251" s="64" t="n"/>
+      <c r="D251" s="65" t="n"/>
+      <c r="E251" s="65" t="n"/>
+      <c r="F251" s="66" t="n"/>
     </row>
     <row r="252">
-      <c r="B252" s="57" t="n"/>
-      <c r="C252" s="58" t="n"/>
-      <c r="D252" s="59" t="n"/>
-      <c r="E252" s="59" t="n"/>
-      <c r="F252" s="60" t="n"/>
+      <c r="B252" s="63" t="n"/>
+      <c r="C252" s="64" t="n"/>
+      <c r="D252" s="65" t="n"/>
+      <c r="E252" s="65" t="n"/>
+      <c r="F252" s="66" t="n"/>
     </row>
     <row r="253">
-      <c r="B253" s="57" t="n"/>
-      <c r="C253" s="58" t="n"/>
-      <c r="D253" s="59" t="n"/>
-      <c r="E253" s="59" t="n"/>
-      <c r="F253" s="60" t="n"/>
+      <c r="B253" s="63" t="n"/>
+      <c r="C253" s="64" t="n"/>
+      <c r="D253" s="65" t="n"/>
+      <c r="E253" s="65" t="n"/>
+      <c r="F253" s="66" t="n"/>
     </row>
     <row r="254">
-      <c r="B254" s="57" t="n"/>
-      <c r="C254" s="58" t="n"/>
-      <c r="D254" s="59" t="n"/>
-      <c r="E254" s="59" t="n"/>
-      <c r="F254" s="60" t="n"/>
+      <c r="B254" s="63" t="n"/>
+      <c r="C254" s="64" t="n"/>
+      <c r="D254" s="65" t="n"/>
+      <c r="E254" s="65" t="n"/>
+      <c r="F254" s="66" t="n"/>
     </row>
     <row r="255">
-      <c r="B255" s="57" t="n"/>
-      <c r="C255" s="58" t="n"/>
-      <c r="D255" s="59" t="n"/>
-      <c r="E255" s="59" t="n"/>
-      <c r="F255" s="60" t="n"/>
+      <c r="B255" s="63" t="n"/>
+      <c r="C255" s="64" t="n"/>
+      <c r="D255" s="65" t="n"/>
+      <c r="E255" s="65" t="n"/>
+      <c r="F255" s="66" t="n"/>
     </row>
     <row r="256">
-      <c r="B256" s="57" t="n"/>
-      <c r="C256" s="58" t="n"/>
-      <c r="D256" s="59" t="n"/>
-      <c r="E256" s="59" t="n"/>
-      <c r="F256" s="60" t="n"/>
+      <c r="B256" s="63" t="n"/>
+      <c r="C256" s="64" t="n"/>
+      <c r="D256" s="65" t="n"/>
+      <c r="E256" s="65" t="n"/>
+      <c r="F256" s="66" t="n"/>
     </row>
     <row r="257">
-      <c r="B257" s="57" t="n"/>
-      <c r="C257" s="58" t="n"/>
-      <c r="D257" s="59" t="n"/>
-      <c r="E257" s="59" t="n"/>
-      <c r="F257" s="60" t="n"/>
+      <c r="B257" s="63" t="n"/>
+      <c r="C257" s="64" t="n"/>
+      <c r="D257" s="65" t="n"/>
+      <c r="E257" s="65" t="n"/>
+      <c r="F257" s="66" t="n"/>
     </row>
     <row r="258">
-      <c r="B258" s="57" t="n"/>
-      <c r="C258" s="58" t="n"/>
-      <c r="D258" s="59" t="n"/>
-      <c r="E258" s="59" t="n"/>
-      <c r="F258" s="60" t="n"/>
+      <c r="B258" s="63" t="n"/>
+      <c r="C258" s="64" t="n"/>
+      <c r="D258" s="65" t="n"/>
+      <c r="E258" s="65" t="n"/>
+      <c r="F258" s="66" t="n"/>
     </row>
     <row r="259">
-      <c r="B259" s="57" t="n"/>
-      <c r="C259" s="58" t="n"/>
-      <c r="D259" s="59" t="n"/>
-      <c r="E259" s="59" t="n"/>
-      <c r="F259" s="60" t="n"/>
+      <c r="B259" s="63" t="n"/>
+      <c r="C259" s="64" t="n"/>
+      <c r="D259" s="65" t="n"/>
+      <c r="E259" s="65" t="n"/>
+      <c r="F259" s="66" t="n"/>
     </row>
     <row r="260">
-      <c r="B260" s="57" t="n"/>
-      <c r="C260" s="58" t="n"/>
-      <c r="D260" s="59" t="n"/>
-      <c r="E260" s="59" t="n"/>
-      <c r="F260" s="60" t="n"/>
+      <c r="B260" s="63" t="n"/>
+      <c r="C260" s="64" t="n"/>
+      <c r="D260" s="65" t="n"/>
+      <c r="E260" s="65" t="n"/>
+      <c r="F260" s="66" t="n"/>
     </row>
     <row r="261">
-      <c r="B261" s="57" t="n"/>
-      <c r="C261" s="58" t="n"/>
-      <c r="D261" s="59" t="n"/>
-      <c r="E261" s="59" t="n"/>
-      <c r="F261" s="60" t="n"/>
+      <c r="B261" s="63" t="n"/>
+      <c r="C261" s="64" t="n"/>
+      <c r="D261" s="65" t="n"/>
+      <c r="E261" s="65" t="n"/>
+      <c r="F261" s="66" t="n"/>
     </row>
     <row r="262">
-      <c r="B262" s="57" t="n"/>
-      <c r="C262" s="58" t="n"/>
-      <c r="D262" s="59" t="n"/>
-      <c r="E262" s="59" t="n"/>
-      <c r="F262" s="60" t="n"/>
+      <c r="B262" s="63" t="n"/>
+      <c r="C262" s="64" t="n"/>
+      <c r="D262" s="65" t="n"/>
+      <c r="E262" s="65" t="n"/>
+      <c r="F262" s="66" t="n"/>
     </row>
     <row r="263">
-      <c r="B263" s="57" t="n"/>
-      <c r="C263" s="58" t="n"/>
-      <c r="D263" s="59" t="n"/>
-      <c r="E263" s="59" t="n"/>
-      <c r="F263" s="60" t="n"/>
+      <c r="B263" s="63" t="n"/>
+      <c r="C263" s="64" t="n"/>
+      <c r="D263" s="65" t="n"/>
+      <c r="E263" s="65" t="n"/>
+      <c r="F263" s="66" t="n"/>
     </row>
     <row r="264">
-      <c r="B264" s="57" t="n"/>
-      <c r="C264" s="58" t="n"/>
-      <c r="D264" s="59" t="n"/>
-      <c r="E264" s="59" t="n"/>
-      <c r="F264" s="60" t="n"/>
+      <c r="B264" s="63" t="n"/>
+      <c r="C264" s="64" t="n"/>
+      <c r="D264" s="65" t="n"/>
+      <c r="E264" s="65" t="n"/>
+      <c r="F264" s="66" t="n"/>
     </row>
     <row r="265">
-      <c r="B265" s="57" t="n"/>
-      <c r="C265" s="58" t="n"/>
-      <c r="D265" s="59" t="n"/>
-      <c r="E265" s="59" t="n"/>
-      <c r="F265" s="60" t="n"/>
+      <c r="B265" s="63" t="n"/>
+      <c r="C265" s="64" t="n"/>
+      <c r="D265" s="65" t="n"/>
+      <c r="E265" s="65" t="n"/>
+      <c r="F265" s="66" t="n"/>
     </row>
     <row r="266">
-      <c r="B266" s="57" t="n"/>
-      <c r="C266" s="58" t="n"/>
-      <c r="D266" s="59" t="n"/>
-      <c r="E266" s="59" t="n"/>
-      <c r="F266" s="60" t="n"/>
+      <c r="B266" s="63" t="n"/>
+      <c r="C266" s="64" t="n"/>
+      <c r="D266" s="65" t="n"/>
+      <c r="E266" s="65" t="n"/>
+      <c r="F266" s="66" t="n"/>
     </row>
     <row r="267">
-      <c r="B267" s="57" t="n"/>
-      <c r="C267" s="58" t="n"/>
-      <c r="D267" s="59" t="n"/>
-      <c r="E267" s="59" t="n"/>
-      <c r="F267" s="60" t="n"/>
+      <c r="B267" s="63" t="n"/>
+      <c r="C267" s="64" t="n"/>
+      <c r="D267" s="65" t="n"/>
+      <c r="E267" s="65" t="n"/>
+      <c r="F267" s="66" t="n"/>
     </row>
     <row r="268">
-      <c r="B268" s="57" t="n"/>
-      <c r="C268" s="58" t="n"/>
-      <c r="D268" s="59" t="n"/>
-      <c r="E268" s="59" t="n"/>
-      <c r="F268" s="60" t="n"/>
+      <c r="B268" s="63" t="n"/>
+      <c r="C268" s="64" t="n"/>
+      <c r="D268" s="65" t="n"/>
+      <c r="E268" s="65" t="n"/>
+      <c r="F268" s="66" t="n"/>
     </row>
     <row r="269">
-      <c r="B269" s="57" t="n"/>
-      <c r="C269" s="58" t="n"/>
-      <c r="D269" s="59" t="n"/>
-      <c r="E269" s="59" t="n"/>
-      <c r="F269" s="60" t="n"/>
+      <c r="B269" s="63" t="n"/>
+      <c r="C269" s="64" t="n"/>
+      <c r="D269" s="65" t="n"/>
+      <c r="E269" s="65" t="n"/>
+      <c r="F269" s="66" t="n"/>
     </row>
     <row r="270">
-      <c r="B270" s="57" t="n"/>
-      <c r="C270" s="58" t="n"/>
-      <c r="D270" s="59" t="n"/>
-      <c r="E270" s="59" t="n"/>
-      <c r="F270" s="60" t="n"/>
+      <c r="B270" s="63" t="n"/>
+      <c r="C270" s="64" t="n"/>
+      <c r="D270" s="65" t="n"/>
+      <c r="E270" s="65" t="n"/>
+      <c r="F270" s="66" t="n"/>
     </row>
     <row r="271">
-      <c r="B271" s="57" t="n"/>
-      <c r="C271" s="58" t="n"/>
-      <c r="D271" s="59" t="n"/>
-      <c r="E271" s="59" t="n"/>
-      <c r="F271" s="60" t="n"/>
+      <c r="B271" s="63" t="n"/>
+      <c r="C271" s="64" t="n"/>
+      <c r="D271" s="65" t="n"/>
+      <c r="E271" s="65" t="n"/>
+      <c r="F271" s="66" t="n"/>
     </row>
     <row r="272">
-      <c r="B272" s="57" t="n"/>
-      <c r="C272" s="58" t="n"/>
-      <c r="D272" s="59" t="n"/>
-      <c r="E272" s="59" t="n"/>
-      <c r="F272" s="60" t="n"/>
+      <c r="B272" s="63" t="n"/>
+      <c r="C272" s="64" t="n"/>
+      <c r="D272" s="65" t="n"/>
+      <c r="E272" s="65" t="n"/>
+      <c r="F272" s="66" t="n"/>
     </row>
     <row r="273">
-      <c r="B273" s="57" t="n"/>
-      <c r="C273" s="58" t="n"/>
-      <c r="D273" s="59" t="n"/>
-      <c r="E273" s="59" t="n"/>
-      <c r="F273" s="60" t="n"/>
+      <c r="B273" s="63" t="n"/>
+      <c r="C273" s="64" t="n"/>
+      <c r="D273" s="65" t="n"/>
+      <c r="E273" s="65" t="n"/>
+      <c r="F273" s="66" t="n"/>
     </row>
     <row r="274">
-      <c r="B274" s="57" t="n"/>
-      <c r="C274" s="58" t="n"/>
-      <c r="D274" s="59" t="n"/>
-      <c r="E274" s="59" t="n"/>
-      <c r="F274" s="60" t="n"/>
+      <c r="B274" s="63" t="n"/>
+      <c r="C274" s="64" t="n"/>
+      <c r="D274" s="65" t="n"/>
+      <c r="E274" s="65" t="n"/>
+      <c r="F274" s="66" t="n"/>
     </row>
     <row r="275">
-      <c r="B275" s="57" t="n"/>
-      <c r="C275" s="58" t="n"/>
-      <c r="D275" s="59" t="n"/>
-      <c r="E275" s="59" t="n"/>
-      <c r="F275" s="60" t="n"/>
+      <c r="B275" s="63" t="n"/>
+      <c r="C275" s="64" t="n"/>
+      <c r="D275" s="65" t="n"/>
+      <c r="E275" s="65" t="n"/>
+      <c r="F275" s="66" t="n"/>
     </row>
     <row r="276">
-      <c r="B276" s="57" t="n"/>
-      <c r="C276" s="58" t="n"/>
-      <c r="D276" s="59" t="n"/>
-      <c r="E276" s="59" t="n"/>
-      <c r="F276" s="60" t="n"/>
+      <c r="B276" s="63" t="n"/>
+      <c r="C276" s="64" t="n"/>
+      <c r="D276" s="65" t="n"/>
+      <c r="E276" s="65" t="n"/>
+      <c r="F276" s="66" t="n"/>
     </row>
     <row r="277">
-      <c r="B277" s="57" t="n"/>
-      <c r="C277" s="58" t="n"/>
-      <c r="D277" s="59" t="n"/>
-      <c r="E277" s="59" t="n"/>
-      <c r="F277" s="60" t="n"/>
+      <c r="B277" s="63" t="n"/>
+      <c r="C277" s="64" t="n"/>
+      <c r="D277" s="65" t="n"/>
+      <c r="E277" s="65" t="n"/>
+      <c r="F277" s="66" t="n"/>
     </row>
     <row r="278">
-      <c r="B278" s="57" t="n"/>
-      <c r="C278" s="58" t="n"/>
-      <c r="D278" s="59" t="n"/>
-      <c r="E278" s="59" t="n"/>
-      <c r="F278" s="60" t="n"/>
+      <c r="B278" s="63" t="n"/>
+      <c r="C278" s="64" t="n"/>
+      <c r="D278" s="65" t="n"/>
+      <c r="E278" s="65" t="n"/>
+      <c r="F278" s="66" t="n"/>
     </row>
     <row r="279">
-      <c r="B279" s="57" t="n"/>
-      <c r="C279" s="58" t="n"/>
-      <c r="D279" s="59" t="n"/>
-      <c r="E279" s="59" t="n"/>
-      <c r="F279" s="60" t="n"/>
+      <c r="B279" s="63" t="n"/>
+      <c r="C279" s="64" t="n"/>
+      <c r="D279" s="65" t="n"/>
+      <c r="E279" s="65" t="n"/>
+      <c r="F279" s="66" t="n"/>
     </row>
     <row r="280">
-      <c r="B280" s="57" t="n"/>
-      <c r="C280" s="58" t="n"/>
-      <c r="D280" s="59" t="n"/>
-      <c r="E280" s="59" t="n"/>
-      <c r="F280" s="60" t="n"/>
+      <c r="B280" s="63" t="n"/>
+      <c r="C280" s="64" t="n"/>
+      <c r="D280" s="65" t="n"/>
+      <c r="E280" s="65" t="n"/>
+      <c r="F280" s="66" t="n"/>
     </row>
     <row r="281">
-      <c r="B281" s="57" t="n"/>
-      <c r="C281" s="58" t="n"/>
-      <c r="D281" s="59" t="n"/>
-      <c r="E281" s="59" t="n"/>
-      <c r="F281" s="60" t="n"/>
+      <c r="B281" s="63" t="n"/>
+      <c r="C281" s="64" t="n"/>
+      <c r="D281" s="65" t="n"/>
+      <c r="E281" s="65" t="n"/>
+      <c r="F281" s="66" t="n"/>
     </row>
     <row r="282">
-      <c r="B282" s="57" t="n"/>
-      <c r="C282" s="58" t="n"/>
-      <c r="D282" s="59" t="n"/>
-      <c r="E282" s="59" t="n"/>
-      <c r="F282" s="60" t="n"/>
+      <c r="B282" s="63" t="n"/>
+      <c r="C282" s="64" t="n"/>
+      <c r="D282" s="65" t="n"/>
+      <c r="E282" s="65" t="n"/>
+      <c r="F282" s="66" t="n"/>
     </row>
     <row r="283">
-      <c r="B283" s="57" t="n"/>
-      <c r="C283" s="58" t="n"/>
-      <c r="D283" s="59" t="n"/>
-      <c r="E283" s="59" t="n"/>
-      <c r="F283" s="60" t="n"/>
+      <c r="B283" s="63" t="n"/>
+      <c r="C283" s="64" t="n"/>
+      <c r="D283" s="65" t="n"/>
+      <c r="E283" s="65" t="n"/>
+      <c r="F283" s="66" t="n"/>
     </row>
     <row r="284">
-      <c r="B284" s="57" t="n"/>
-      <c r="C284" s="58" t="n"/>
-      <c r="D284" s="59" t="n"/>
-      <c r="E284" s="59" t="n"/>
-      <c r="F284" s="60" t="n"/>
+      <c r="B284" s="63" t="n"/>
+      <c r="C284" s="64" t="n"/>
+      <c r="D284" s="65" t="n"/>
+      <c r="E284" s="65" t="n"/>
+      <c r="F284" s="66" t="n"/>
     </row>
     <row r="285">
-      <c r="B285" s="57" t="n"/>
-      <c r="C285" s="58" t="n"/>
-      <c r="D285" s="59" t="n"/>
-      <c r="E285" s="59" t="n"/>
-      <c r="F285" s="60" t="n"/>
+      <c r="B285" s="63" t="n"/>
+      <c r="C285" s="64" t="n"/>
+      <c r="D285" s="65" t="n"/>
+      <c r="E285" s="65" t="n"/>
+      <c r="F285" s="66" t="n"/>
     </row>
     <row r="286">
-      <c r="B286" s="57" t="n"/>
-      <c r="C286" s="58" t="n"/>
-      <c r="D286" s="59" t="n"/>
-      <c r="E286" s="59" t="n"/>
-      <c r="F286" s="60" t="n"/>
+      <c r="B286" s="63" t="n"/>
+      <c r="C286" s="64" t="n"/>
+      <c r="D286" s="65" t="n"/>
+      <c r="E286" s="65" t="n"/>
+      <c r="F286" s="66" t="n"/>
     </row>
     <row r="287">
-      <c r="B287" s="57" t="n"/>
-      <c r="C287" s="58" t="n"/>
-      <c r="D287" s="59" t="n"/>
-      <c r="E287" s="59" t="n"/>
-      <c r="F287" s="60" t="n"/>
+      <c r="B287" s="63" t="n"/>
+      <c r="C287" s="64" t="n"/>
+      <c r="D287" s="65" t="n"/>
+      <c r="E287" s="65" t="n"/>
+      <c r="F287" s="66" t="n"/>
     </row>
     <row r="288">
-      <c r="B288" s="57" t="n"/>
-      <c r="C288" s="58" t="n"/>
-      <c r="D288" s="59" t="n"/>
-      <c r="E288" s="59" t="n"/>
-      <c r="F288" s="60" t="n"/>
+      <c r="B288" s="63" t="n"/>
+      <c r="C288" s="64" t="n"/>
+      <c r="D288" s="65" t="n"/>
+      <c r="E288" s="65" t="n"/>
+      <c r="F288" s="66" t="n"/>
     </row>
     <row r="289">
-      <c r="B289" s="57" t="n"/>
-      <c r="C289" s="58" t="n"/>
-      <c r="D289" s="59" t="n"/>
-      <c r="E289" s="59" t="n"/>
-      <c r="F289" s="60" t="n"/>
+      <c r="B289" s="63" t="n"/>
+      <c r="C289" s="64" t="n"/>
+      <c r="D289" s="65" t="n"/>
+      <c r="E289" s="65" t="n"/>
+      <c r="F289" s="66" t="n"/>
     </row>
     <row r="290">
-      <c r="B290" s="57" t="n"/>
-      <c r="C290" s="58" t="n"/>
-      <c r="D290" s="59" t="n"/>
-      <c r="E290" s="59" t="n"/>
-      <c r="F290" s="60" t="n"/>
+      <c r="B290" s="63" t="n"/>
+      <c r="C290" s="64" t="n"/>
+      <c r="D290" s="65" t="n"/>
+      <c r="E290" s="65" t="n"/>
+      <c r="F290" s="66" t="n"/>
     </row>
     <row r="291">
-      <c r="B291" s="57" t="n"/>
-      <c r="C291" s="58" t="n"/>
-      <c r="D291" s="59" t="n"/>
-      <c r="E291" s="59" t="n"/>
-      <c r="F291" s="60" t="n"/>
+      <c r="B291" s="63" t="n"/>
+      <c r="C291" s="64" t="n"/>
+      <c r="D291" s="65" t="n"/>
+      <c r="E291" s="65" t="n"/>
+      <c r="F291" s="66" t="n"/>
     </row>
     <row r="292">
-      <c r="B292" s="57" t="n"/>
-      <c r="C292" s="58" t="n"/>
-      <c r="D292" s="59" t="n"/>
-      <c r="E292" s="59" t="n"/>
-      <c r="F292" s="60" t="n"/>
+      <c r="B292" s="63" t="n"/>
+      <c r="C292" s="64" t="n"/>
+      <c r="D292" s="65" t="n"/>
+      <c r="E292" s="65" t="n"/>
+      <c r="F292" s="66" t="n"/>
     </row>
     <row r="293">
-      <c r="B293" s="57" t="n"/>
-      <c r="C293" s="58" t="n"/>
-      <c r="D293" s="59" t="n"/>
-      <c r="E293" s="59" t="n"/>
-      <c r="F293" s="60" t="n"/>
+      <c r="B293" s="63" t="n"/>
+      <c r="C293" s="64" t="n"/>
+      <c r="D293" s="65" t="n"/>
+      <c r="E293" s="65" t="n"/>
+      <c r="F293" s="66" t="n"/>
     </row>
     <row r="294">
-      <c r="B294" s="57" t="n"/>
-      <c r="C294" s="58" t="n"/>
-      <c r="D294" s="59" t="n"/>
-      <c r="E294" s="59" t="n"/>
-      <c r="F294" s="60" t="n"/>
+      <c r="B294" s="63" t="n"/>
+      <c r="C294" s="64" t="n"/>
+      <c r="D294" s="65" t="n"/>
+      <c r="E294" s="65" t="n"/>
+      <c r="F294" s="66" t="n"/>
     </row>
     <row r="295">
-      <c r="B295" s="57" t="n"/>
-      <c r="C295" s="58" t="n"/>
-      <c r="D295" s="59" t="n"/>
-      <c r="E295" s="59" t="n"/>
-      <c r="F295" s="60" t="n"/>
+      <c r="B295" s="63" t="n"/>
+      <c r="C295" s="64" t="n"/>
+      <c r="D295" s="65" t="n"/>
+      <c r="E295" s="65" t="n"/>
+      <c r="F295" s="66" t="n"/>
     </row>
     <row r="296">
-      <c r="B296" s="57" t="n"/>
-      <c r="C296" s="58" t="n"/>
-      <c r="D296" s="59" t="n"/>
-      <c r="E296" s="59" t="n"/>
-      <c r="F296" s="60" t="n"/>
+      <c r="B296" s="63" t="n"/>
+      <c r="C296" s="64" t="n"/>
+      <c r="D296" s="65" t="n"/>
+      <c r="E296" s="65" t="n"/>
+      <c r="F296" s="66" t="n"/>
     </row>
     <row r="297">
-      <c r="B297" s="57" t="n"/>
-      <c r="C297" s="58" t="n"/>
-      <c r="D297" s="59" t="n"/>
-      <c r="E297" s="59" t="n"/>
-      <c r="F297" s="60" t="n"/>
+      <c r="B297" s="63" t="n"/>
+      <c r="C297" s="64" t="n"/>
+      <c r="D297" s="65" t="n"/>
+      <c r="E297" s="65" t="n"/>
+      <c r="F297" s="66" t="n"/>
     </row>
     <row r="298">
-      <c r="B298" s="57" t="n"/>
-      <c r="C298" s="58" t="n"/>
-      <c r="D298" s="59" t="n"/>
-      <c r="E298" s="59" t="n"/>
-      <c r="F298" s="60" t="n"/>
+      <c r="B298" s="63" t="n"/>
+      <c r="C298" s="64" t="n"/>
+      <c r="D298" s="65" t="n"/>
+      <c r="E298" s="65" t="n"/>
+      <c r="F298" s="66" t="n"/>
     </row>
     <row r="299">
-      <c r="B299" s="57" t="n"/>
-      <c r="C299" s="58" t="n"/>
-      <c r="D299" s="59" t="n"/>
-      <c r="E299" s="59" t="n"/>
-      <c r="F299" s="60" t="n"/>
+      <c r="B299" s="63" t="n"/>
+      <c r="C299" s="64" t="n"/>
+      <c r="D299" s="65" t="n"/>
+      <c r="E299" s="65" t="n"/>
+      <c r="F299" s="66" t="n"/>
     </row>
     <row r="300">
-      <c r="B300" s="57" t="n"/>
-      <c r="C300" s="58" t="n"/>
-      <c r="D300" s="59" t="n"/>
-      <c r="E300" s="59" t="n"/>
-      <c r="F300" s="60" t="n"/>
+      <c r="B300" s="63" t="n"/>
+      <c r="C300" s="64" t="n"/>
+      <c r="D300" s="65" t="n"/>
+      <c r="E300" s="65" t="n"/>
+      <c r="F300" s="66" t="n"/>
     </row>
     <row r="301">
-      <c r="B301" s="57" t="n"/>
-      <c r="C301" s="58" t="n"/>
-      <c r="D301" s="59" t="n"/>
-      <c r="E301" s="59" t="n"/>
-      <c r="F301" s="60" t="n"/>
+      <c r="B301" s="63" t="n"/>
+      <c r="C301" s="64" t="n"/>
+      <c r="D301" s="65" t="n"/>
+      <c r="E301" s="65" t="n"/>
+      <c r="F301" s="66" t="n"/>
     </row>
     <row r="302">
-      <c r="B302" s="57" t="n"/>
-      <c r="C302" s="58" t="n"/>
-      <c r="D302" s="59" t="n"/>
-      <c r="E302" s="59" t="n"/>
-      <c r="F302" s="60" t="n"/>
+      <c r="B302" s="63" t="n"/>
+      <c r="C302" s="64" t="n"/>
+      <c r="D302" s="65" t="n"/>
+      <c r="E302" s="65" t="n"/>
+      <c r="F302" s="66" t="n"/>
     </row>
     <row r="303">
-      <c r="B303" s="57" t="n"/>
-      <c r="C303" s="58" t="n"/>
-      <c r="D303" s="59" t="n"/>
-      <c r="E303" s="59" t="n"/>
-      <c r="F303" s="60" t="n"/>
+      <c r="B303" s="63" t="n"/>
+      <c r="C303" s="64" t="n"/>
+      <c r="D303" s="65" t="n"/>
+      <c r="E303" s="65" t="n"/>
+      <c r="F303" s="66" t="n"/>
     </row>
     <row r="304">
-      <c r="B304" s="57" t="n"/>
-      <c r="C304" s="58" t="n"/>
-      <c r="D304" s="59" t="n"/>
-      <c r="E304" s="59" t="n"/>
-      <c r="F304" s="60" t="n"/>
+      <c r="B304" s="63" t="n"/>
+      <c r="C304" s="64" t="n"/>
+      <c r="D304" s="65" t="n"/>
+      <c r="E304" s="65" t="n"/>
+      <c r="F304" s="66" t="n"/>
     </row>
     <row r="305">
-      <c r="B305" s="57" t="n"/>
-      <c r="C305" s="58" t="n"/>
-      <c r="D305" s="59" t="n"/>
-      <c r="E305" s="59" t="n"/>
-      <c r="F305" s="60" t="n"/>
+      <c r="B305" s="63" t="n"/>
+      <c r="C305" s="64" t="n"/>
+      <c r="D305" s="65" t="n"/>
+      <c r="E305" s="65" t="n"/>
+      <c r="F305" s="66" t="n"/>
     </row>
     <row r="306">
-      <c r="B306" s="57" t="n"/>
-      <c r="C306" s="58" t="n"/>
-      <c r="D306" s="59" t="n"/>
-      <c r="E306" s="59" t="n"/>
-      <c r="F306" s="60" t="n"/>
+      <c r="B306" s="63" t="n"/>
+      <c r="C306" s="64" t="n"/>
+      <c r="D306" s="65" t="n"/>
+      <c r="E306" s="65" t="n"/>
+      <c r="F306" s="66" t="n"/>
     </row>
     <row r="307">
-      <c r="B307" s="57" t="n"/>
-      <c r="C307" s="58" t="n"/>
-      <c r="D307" s="59" t="n"/>
-      <c r="E307" s="59" t="n"/>
-      <c r="F307" s="60" t="n"/>
+      <c r="B307" s="63" t="n"/>
+      <c r="C307" s="64" t="n"/>
+      <c r="D307" s="65" t="n"/>
+      <c r="E307" s="65" t="n"/>
+      <c r="F307" s="66" t="n"/>
     </row>
     <row r="308">
-      <c r="B308" s="57" t="n"/>
-      <c r="C308" s="58" t="n"/>
-      <c r="D308" s="59" t="n"/>
-      <c r="E308" s="59" t="n"/>
-      <c r="F308" s="60" t="n"/>
+      <c r="B308" s="63" t="n"/>
+      <c r="C308" s="64" t="n"/>
+      <c r="D308" s="65" t="n"/>
+      <c r="E308" s="65" t="n"/>
+      <c r="F308" s="66" t="n"/>
     </row>
     <row r="309">
-      <c r="B309" s="57" t="n"/>
-      <c r="C309" s="58" t="n"/>
-      <c r="D309" s="59" t="n"/>
-      <c r="E309" s="59" t="n"/>
-      <c r="F309" s="60" t="n"/>
+      <c r="B309" s="63" t="n"/>
+      <c r="C309" s="64" t="n"/>
+      <c r="D309" s="65" t="n"/>
+      <c r="E309" s="65" t="n"/>
+      <c r="F309" s="66" t="n"/>
     </row>
     <row r="310">
-      <c r="B310" s="57" t="n"/>
-      <c r="C310" s="58" t="n"/>
-      <c r="D310" s="59" t="n"/>
-      <c r="E310" s="59" t="n"/>
-      <c r="F310" s="60" t="n"/>
+      <c r="B310" s="63" t="n"/>
+      <c r="C310" s="64" t="n"/>
+      <c r="D310" s="65" t="n"/>
+      <c r="E310" s="65" t="n"/>
+      <c r="F310" s="66" t="n"/>
     </row>
     <row r="311">
-      <c r="B311" s="57" t="n"/>
-      <c r="C311" s="58" t="n"/>
-      <c r="D311" s="59" t="n"/>
-      <c r="E311" s="59" t="n"/>
-      <c r="F311" s="60" t="n"/>
+      <c r="B311" s="63" t="n"/>
+      <c r="C311" s="64" t="n"/>
+      <c r="D311" s="65" t="n"/>
+      <c r="E311" s="65" t="n"/>
+      <c r="F311" s="66" t="n"/>
     </row>
     <row r="312">
-      <c r="B312" s="57" t="n"/>
-      <c r="C312" s="58" t="n"/>
-      <c r="D312" s="59" t="n"/>
-      <c r="E312" s="59" t="n"/>
-      <c r="F312" s="60" t="n"/>
+      <c r="B312" s="63" t="n"/>
+      <c r="C312" s="64" t="n"/>
+      <c r="D312" s="65" t="n"/>
+      <c r="E312" s="65" t="n"/>
+      <c r="F312" s="66" t="n"/>
     </row>
     <row r="313">
-      <c r="B313" s="57" t="n"/>
-      <c r="C313" s="58" t="n"/>
-      <c r="D313" s="59" t="n"/>
-      <c r="E313" s="59" t="n"/>
-      <c r="F313" s="60" t="n"/>
+      <c r="B313" s="63" t="n"/>
+      <c r="C313" s="64" t="n"/>
+      <c r="D313" s="65" t="n"/>
+      <c r="E313" s="65" t="n"/>
+      <c r="F313" s="66" t="n"/>
     </row>
     <row r="314">
-      <c r="B314" s="57" t="n"/>
-      <c r="C314" s="58" t="n"/>
-      <c r="D314" s="59" t="n"/>
-      <c r="E314" s="59" t="n"/>
-      <c r="F314" s="60" t="n"/>
+      <c r="B314" s="63" t="n"/>
+      <c r="C314" s="64" t="n"/>
+      <c r="D314" s="65" t="n"/>
+      <c r="E314" s="65" t="n"/>
+      <c r="F314" s="66" t="n"/>
     </row>
     <row r="315">
-      <c r="B315" s="57" t="n"/>
-      <c r="C315" s="58" t="n"/>
-      <c r="D315" s="59" t="n"/>
-      <c r="E315" s="59" t="n"/>
-      <c r="F315" s="60" t="n"/>
+      <c r="B315" s="63" t="n"/>
+      <c r="C315" s="64" t="n"/>
+      <c r="D315" s="65" t="n"/>
+      <c r="E315" s="65" t="n"/>
+      <c r="F315" s="66" t="n"/>
     </row>
     <row r="316">
-      <c r="B316" s="57" t="n"/>
-      <c r="C316" s="58" t="n"/>
-      <c r="D316" s="59" t="n"/>
-      <c r="E316" s="59" t="n"/>
-      <c r="F316" s="60" t="n"/>
+      <c r="B316" s="63" t="n"/>
+      <c r="C316" s="64" t="n"/>
+      <c r="D316" s="65" t="n"/>
+      <c r="E316" s="65" t="n"/>
+      <c r="F316" s="66" t="n"/>
     </row>
     <row r="317">
-      <c r="B317" s="57" t="n"/>
-      <c r="C317" s="58" t="n"/>
-      <c r="D317" s="59" t="n"/>
-      <c r="E317" s="59" t="n"/>
-      <c r="F317" s="60" t="n"/>
+      <c r="B317" s="63" t="n"/>
+      <c r="C317" s="64" t="n"/>
+      <c r="D317" s="65" t="n"/>
+      <c r="E317" s="65" t="n"/>
+      <c r="F317" s="66" t="n"/>
     </row>
     <row r="318">
-      <c r="B318" s="57" t="n"/>
-      <c r="C318" s="58" t="n"/>
-      <c r="D318" s="59" t="n"/>
-      <c r="E318" s="59" t="n"/>
-      <c r="F318" s="60" t="n"/>
+      <c r="B318" s="63" t="n"/>
+      <c r="C318" s="64" t="n"/>
+      <c r="D318" s="65" t="n"/>
+      <c r="E318" s="65" t="n"/>
+      <c r="F318" s="66" t="n"/>
     </row>
     <row r="319">
-      <c r="B319" s="57" t="n"/>
-      <c r="C319" s="58" t="n"/>
-      <c r="D319" s="59" t="n"/>
-      <c r="E319" s="59" t="n"/>
-      <c r="F319" s="60" t="n"/>
+      <c r="B319" s="63" t="n"/>
+      <c r="C319" s="64" t="n"/>
+      <c r="D319" s="65" t="n"/>
+      <c r="E319" s="65" t="n"/>
+      <c r="F319" s="66" t="n"/>
     </row>
     <row r="320">
-      <c r="B320" s="57" t="n"/>
-      <c r="C320" s="58" t="n"/>
-      <c r="D320" s="59" t="n"/>
-      <c r="E320" s="59" t="n"/>
-      <c r="F320" s="60" t="n"/>
+      <c r="B320" s="63" t="n"/>
+      <c r="C320" s="64" t="n"/>
+      <c r="D320" s="65" t="n"/>
+      <c r="E320" s="65" t="n"/>
+      <c r="F320" s="66" t="n"/>
     </row>
     <row r="321">
-      <c r="B321" s="57" t="n"/>
-      <c r="C321" s="58" t="n"/>
-      <c r="D321" s="59" t="n"/>
-      <c r="E321" s="59" t="n"/>
-      <c r="F321" s="60" t="n"/>
+      <c r="B321" s="63" t="n"/>
+      <c r="C321" s="64" t="n"/>
+      <c r="D321" s="65" t="n"/>
+      <c r="E321" s="65" t="n"/>
+      <c r="F321" s="66" t="n"/>
     </row>
     <row r="322">
-      <c r="B322" s="57" t="n"/>
-      <c r="C322" s="58" t="n"/>
-      <c r="D322" s="59" t="n"/>
-      <c r="E322" s="59" t="n"/>
-      <c r="F322" s="60" t="n"/>
+      <c r="B322" s="63" t="n"/>
+      <c r="C322" s="64" t="n"/>
+      <c r="D322" s="65" t="n"/>
+      <c r="E322" s="65" t="n"/>
+      <c r="F322" s="66" t="n"/>
     </row>
     <row r="323">
-      <c r="B323" s="57" t="n"/>
-      <c r="C323" s="58" t="n"/>
-      <c r="D323" s="59" t="n"/>
-      <c r="E323" s="59" t="n"/>
-      <c r="F323" s="60" t="n"/>
+      <c r="B323" s="63" t="n"/>
+      <c r="C323" s="64" t="n"/>
+      <c r="D323" s="65" t="n"/>
+      <c r="E323" s="65" t="n"/>
+      <c r="F323" s="66" t="n"/>
     </row>
     <row r="324">
-      <c r="B324" s="57" t="n"/>
-      <c r="C324" s="58" t="n"/>
-      <c r="D324" s="59" t="n"/>
-      <c r="E324" s="59" t="n"/>
-      <c r="F324" s="60" t="n"/>
+      <c r="B324" s="63" t="n"/>
+      <c r="C324" s="64" t="n"/>
+      <c r="D324" s="65" t="n"/>
+      <c r="E324" s="65" t="n"/>
+      <c r="F324" s="66" t="n"/>
     </row>
     <row r="325">
-      <c r="B325" s="57" t="n"/>
-      <c r="C325" s="58" t="n"/>
-      <c r="D325" s="59" t="n"/>
-      <c r="E325" s="59" t="n"/>
-      <c r="F325" s="60" t="n"/>
+      <c r="B325" s="63" t="n"/>
+      <c r="C325" s="64" t="n"/>
+      <c r="D325" s="65" t="n"/>
+      <c r="E325" s="65" t="n"/>
+      <c r="F325" s="66" t="n"/>
     </row>
     <row r="326">
-      <c r="B326" s="57" t="n"/>
-      <c r="C326" s="58" t="n"/>
-      <c r="D326" s="59" t="n"/>
-      <c r="E326" s="59" t="n"/>
-      <c r="F326" s="60" t="n"/>
+      <c r="B326" s="63" t="n"/>
+      <c r="C326" s="64" t="n"/>
+      <c r="D326" s="65" t="n"/>
+      <c r="E326" s="65" t="n"/>
+      <c r="F326" s="66" t="n"/>
     </row>
     <row r="327">
-      <c r="B327" s="57" t="n"/>
-      <c r="C327" s="58" t="n"/>
-      <c r="D327" s="59" t="n"/>
-      <c r="E327" s="59" t="n"/>
-      <c r="F327" s="60" t="n"/>
+      <c r="B327" s="63" t="n"/>
+      <c r="C327" s="64" t="n"/>
+      <c r="D327" s="65" t="n"/>
+      <c r="E327" s="65" t="n"/>
+      <c r="F327" s="66" t="n"/>
     </row>
     <row r="328">
-      <c r="B328" s="57" t="n"/>
-      <c r="C328" s="58" t="n"/>
-      <c r="D328" s="59" t="n"/>
-      <c r="E328" s="59" t="n"/>
-      <c r="F328" s="60" t="n"/>
+      <c r="B328" s="63" t="n"/>
+      <c r="C328" s="64" t="n"/>
+      <c r="D328" s="65" t="n"/>
+      <c r="E328" s="65" t="n"/>
+      <c r="F328" s="66" t="n"/>
     </row>
     <row r="329">
-      <c r="B329" s="57" t="n"/>
-      <c r="C329" s="58" t="n"/>
-      <c r="D329" s="59" t="n"/>
-      <c r="E329" s="59" t="n"/>
-      <c r="F329" s="60" t="n"/>
+      <c r="B329" s="63" t="n"/>
+      <c r="C329" s="64" t="n"/>
+      <c r="D329" s="65" t="n"/>
+      <c r="E329" s="65" t="n"/>
+      <c r="F329" s="66" t="n"/>
     </row>
     <row r="330">
-      <c r="B330" s="57" t="n"/>
-      <c r="C330" s="58" t="n"/>
-      <c r="D330" s="59" t="n"/>
-      <c r="E330" s="59" t="n"/>
-      <c r="F330" s="60" t="n"/>
+      <c r="B330" s="63" t="n"/>
+      <c r="C330" s="64" t="n"/>
+      <c r="D330" s="65" t="n"/>
+      <c r="E330" s="65" t="n"/>
+      <c r="F330" s="66" t="n"/>
     </row>
     <row r="331">
-      <c r="B331" s="57" t="n"/>
-      <c r="C331" s="58" t="n"/>
-      <c r="D331" s="59" t="n"/>
-      <c r="E331" s="59" t="n"/>
-      <c r="F331" s="60" t="n"/>
+      <c r="B331" s="63" t="n"/>
+      <c r="C331" s="64" t="n"/>
+      <c r="D331" s="65" t="n"/>
+      <c r="E331" s="65" t="n"/>
+      <c r="F331" s="66" t="n"/>
     </row>
     <row r="332">
-      <c r="B332" s="57" t="n"/>
-      <c r="C332" s="58" t="n"/>
-      <c r="D332" s="59" t="n"/>
-      <c r="E332" s="59" t="n"/>
-      <c r="F332" s="60" t="n"/>
+      <c r="B332" s="63" t="n"/>
+      <c r="C332" s="64" t="n"/>
+      <c r="D332" s="65" t="n"/>
+      <c r="E332" s="65" t="n"/>
+      <c r="F332" s="66" t="n"/>
     </row>
     <row r="333">
-      <c r="B333" s="57" t="n"/>
-      <c r="C333" s="58" t="n"/>
-      <c r="D333" s="59" t="n"/>
-      <c r="E333" s="59" t="n"/>
-      <c r="F333" s="60" t="n"/>
+      <c r="B333" s="63" t="n"/>
+      <c r="C333" s="64" t="n"/>
+      <c r="D333" s="65" t="n"/>
+      <c r="E333" s="65" t="n"/>
+      <c r="F333" s="66" t="n"/>
     </row>
     <row r="334">
-      <c r="B334" s="57" t="n"/>
-      <c r="C334" s="58" t="n"/>
-      <c r="D334" s="59" t="n"/>
-      <c r="E334" s="59" t="n"/>
-      <c r="F334" s="60" t="n"/>
+      <c r="B334" s="63" t="n"/>
+      <c r="C334" s="64" t="n"/>
+      <c r="D334" s="65" t="n"/>
+      <c r="E334" s="65" t="n"/>
+      <c r="F334" s="66" t="n"/>
     </row>
     <row r="335">
-      <c r="B335" s="57" t="n"/>
-      <c r="C335" s="58" t="n"/>
-      <c r="D335" s="59" t="n"/>
-      <c r="E335" s="59" t="n"/>
-      <c r="F335" s="60" t="n"/>
+      <c r="B335" s="63" t="n"/>
+      <c r="C335" s="64" t="n"/>
+      <c r="D335" s="65" t="n"/>
+      <c r="E335" s="65" t="n"/>
+      <c r="F335" s="66" t="n"/>
     </row>
     <row r="336">
-      <c r="B336" s="57" t="n"/>
-      <c r="C336" s="58" t="n"/>
-      <c r="D336" s="59" t="n"/>
-      <c r="E336" s="59" t="n"/>
-      <c r="F336" s="60" t="n"/>
+      <c r="B336" s="63" t="n"/>
+      <c r="C336" s="64" t="n"/>
+      <c r="D336" s="65" t="n"/>
+      <c r="E336" s="65" t="n"/>
+      <c r="F336" s="66" t="n"/>
     </row>
     <row r="337">
-      <c r="B337" s="57" t="n"/>
-      <c r="C337" s="58" t="n"/>
-      <c r="D337" s="59" t="n"/>
-      <c r="E337" s="59" t="n"/>
-      <c r="F337" s="60" t="n"/>
+      <c r="B337" s="63" t="n"/>
+      <c r="C337" s="64" t="n"/>
+      <c r="D337" s="65" t="n"/>
+      <c r="E337" s="65" t="n"/>
+      <c r="F337" s="66" t="n"/>
     </row>
     <row r="338">
-      <c r="B338" s="57" t="n"/>
-      <c r="C338" s="58" t="n"/>
-      <c r="D338" s="59" t="n"/>
-      <c r="E338" s="59" t="n"/>
-      <c r="F338" s="60" t="n"/>
+      <c r="B338" s="63" t="n"/>
+      <c r="C338" s="64" t="n"/>
+      <c r="D338" s="65" t="n"/>
+      <c r="E338" s="65" t="n"/>
+      <c r="F338" s="66" t="n"/>
     </row>
     <row r="339">
-      <c r="B339" s="57" t="n"/>
-      <c r="C339" s="58" t="n"/>
-      <c r="D339" s="59" t="n"/>
-      <c r="E339" s="59" t="n"/>
-      <c r="F339" s="60" t="n"/>
+      <c r="B339" s="63" t="n"/>
+      <c r="C339" s="64" t="n"/>
+      <c r="D339" s="65" t="n"/>
+      <c r="E339" s="65" t="n"/>
+      <c r="F339" s="66" t="n"/>
     </row>
     <row r="340">
-      <c r="B340" s="57" t="n"/>
-      <c r="C340" s="58" t="n"/>
-      <c r="D340" s="59" t="n"/>
-      <c r="E340" s="59" t="n"/>
-      <c r="F340" s="60" t="n"/>
+      <c r="B340" s="63" t="n"/>
+      <c r="C340" s="64" t="n"/>
+      <c r="D340" s="65" t="n"/>
+      <c r="E340" s="65" t="n"/>
+      <c r="F340" s="66" t="n"/>
     </row>
     <row r="341">
-      <c r="B341" s="57" t="n"/>
-      <c r="C341" s="58" t="n"/>
-      <c r="D341" s="59" t="n"/>
-      <c r="E341" s="59" t="n"/>
-      <c r="F341" s="60" t="n"/>
+      <c r="B341" s="63" t="n"/>
+      <c r="C341" s="64" t="n"/>
+      <c r="D341" s="65" t="n"/>
+      <c r="E341" s="65" t="n"/>
+      <c r="F341" s="66" t="n"/>
     </row>
     <row r="342">
-      <c r="B342" s="57" t="n"/>
-      <c r="C342" s="58" t="n"/>
-      <c r="D342" s="59" t="n"/>
-      <c r="E342" s="59" t="n"/>
-      <c r="F342" s="60" t="n"/>
+      <c r="B342" s="63" t="n"/>
+      <c r="C342" s="64" t="n"/>
+      <c r="D342" s="65" t="n"/>
+      <c r="E342" s="65" t="n"/>
+      <c r="F342" s="66" t="n"/>
     </row>
     <row r="343">
-      <c r="B343" s="57" t="n"/>
-      <c r="C343" s="58" t="n"/>
-      <c r="D343" s="59" t="n"/>
-      <c r="E343" s="59" t="n"/>
-      <c r="F343" s="60" t="n"/>
+      <c r="B343" s="63" t="n"/>
+      <c r="C343" s="64" t="n"/>
+      <c r="D343" s="65" t="n"/>
+      <c r="E343" s="65" t="n"/>
+      <c r="F343" s="66" t="n"/>
     </row>
     <row r="344">
-      <c r="B344" s="57" t="n"/>
-      <c r="C344" s="58" t="n"/>
-      <c r="D344" s="59" t="n"/>
-      <c r="E344" s="59" t="n"/>
-      <c r="F344" s="60" t="n"/>
+      <c r="B344" s="63" t="n"/>
+      <c r="C344" s="64" t="n"/>
+      <c r="D344" s="65" t="n"/>
+      <c r="E344" s="65" t="n"/>
+      <c r="F344" s="66" t="n"/>
     </row>
     <row r="345">
-      <c r="B345" s="57" t="n"/>
-      <c r="C345" s="58" t="n"/>
-      <c r="D345" s="59" t="n"/>
-      <c r="E345" s="59" t="n"/>
-      <c r="F345" s="60" t="n"/>
+      <c r="B345" s="63" t="n"/>
+      <c r="C345" s="64" t="n"/>
+      <c r="D345" s="65" t="n"/>
+      <c r="E345" s="65" t="n"/>
+      <c r="F345" s="66" t="n"/>
     </row>
     <row r="346">
-      <c r="B346" s="57" t="n"/>
-      <c r="C346" s="58" t="n"/>
-      <c r="D346" s="59" t="n"/>
-      <c r="E346" s="59" t="n"/>
-      <c r="F346" s="60" t="n"/>
+      <c r="B346" s="63" t="n"/>
+      <c r="C346" s="64" t="n"/>
+      <c r="D346" s="65" t="n"/>
+      <c r="E346" s="65" t="n"/>
+      <c r="F346" s="66" t="n"/>
     </row>
     <row r="347">
-      <c r="B347" s="57" t="n"/>
-      <c r="C347" s="58" t="n"/>
-      <c r="D347" s="59" t="n"/>
-      <c r="E347" s="59" t="n"/>
-      <c r="F347" s="60" t="n"/>
+      <c r="B347" s="63" t="n"/>
+      <c r="C347" s="64" t="n"/>
+      <c r="D347" s="65" t="n"/>
+      <c r="E347" s="65" t="n"/>
+      <c r="F347" s="66" t="n"/>
     </row>
     <row r="348">
-      <c r="B348" s="57" t="n"/>
-      <c r="C348" s="58" t="n"/>
-      <c r="D348" s="59" t="n"/>
-      <c r="E348" s="59" t="n"/>
-      <c r="F348" s="60" t="n"/>
+      <c r="B348" s="63" t="n"/>
+      <c r="C348" s="64" t="n"/>
+      <c r="D348" s="65" t="n"/>
+      <c r="E348" s="65" t="n"/>
+      <c r="F348" s="66" t="n"/>
     </row>
     <row r="349">
-      <c r="B349" s="57" t="n"/>
-      <c r="C349" s="58" t="n"/>
-      <c r="D349" s="59" t="n"/>
-      <c r="E349" s="59" t="n"/>
-      <c r="F349" s="60" t="n"/>
+      <c r="B349" s="63" t="n"/>
+      <c r="C349" s="64" t="n"/>
+      <c r="D349" s="65" t="n"/>
+      <c r="E349" s="65" t="n"/>
+      <c r="F349" s="66" t="n"/>
     </row>
     <row r="350">
-      <c r="B350" s="57" t="n"/>
-      <c r="C350" s="58" t="n"/>
-      <c r="D350" s="59" t="n"/>
-      <c r="E350" s="59" t="n"/>
-      <c r="F350" s="60" t="n"/>
+      <c r="B350" s="63" t="n"/>
+      <c r="C350" s="64" t="n"/>
+      <c r="D350" s="65" t="n"/>
+      <c r="E350" s="65" t="n"/>
+      <c r="F350" s="66" t="n"/>
     </row>
     <row r="351">
-      <c r="B351" s="57" t="n"/>
-      <c r="C351" s="58" t="n"/>
-      <c r="D351" s="59" t="n"/>
-      <c r="E351" s="59" t="n"/>
-      <c r="F351" s="60" t="n"/>
+      <c r="B351" s="63" t="n"/>
+      <c r="C351" s="64" t="n"/>
+      <c r="D351" s="65" t="n"/>
+      <c r="E351" s="65" t="n"/>
+      <c r="F351" s="66" t="n"/>
     </row>
     <row r="352">
-      <c r="B352" s="57" t="n"/>
-      <c r="C352" s="58" t="n"/>
-      <c r="D352" s="59" t="n"/>
-      <c r="E352" s="59" t="n"/>
-      <c r="F352" s="60" t="n"/>
+      <c r="B352" s="63" t="n"/>
+      <c r="C352" s="64" t="n"/>
+      <c r="D352" s="65" t="n"/>
+      <c r="E352" s="65" t="n"/>
+      <c r="F352" s="66" t="n"/>
     </row>
     <row r="353">
-      <c r="B353" s="57" t="n"/>
-      <c r="C353" s="58" t="n"/>
-      <c r="D353" s="59" t="n"/>
-      <c r="E353" s="59" t="n"/>
-      <c r="F353" s="60" t="n"/>
+      <c r="B353" s="63" t="n"/>
+      <c r="C353" s="64" t="n"/>
+      <c r="D353" s="65" t="n"/>
+      <c r="E353" s="65" t="n"/>
+      <c r="F353" s="66" t="n"/>
     </row>
     <row r="354">
-      <c r="B354" s="57" t="n"/>
-      <c r="C354" s="58" t="n"/>
-      <c r="D354" s="59" t="n"/>
-      <c r="E354" s="59" t="n"/>
-      <c r="F354" s="60" t="n"/>
+      <c r="B354" s="63" t="n"/>
+      <c r="C354" s="64" t="n"/>
+      <c r="D354" s="65" t="n"/>
+      <c r="E354" s="65" t="n"/>
+      <c r="F354" s="66" t="n"/>
     </row>
     <row r="355">
-      <c r="B355" s="57" t="n"/>
-      <c r="C355" s="58" t="n"/>
-      <c r="D355" s="59" t="n"/>
-      <c r="E355" s="59" t="n"/>
-      <c r="F355" s="60" t="n"/>
+      <c r="B355" s="63" t="n"/>
+      <c r="C355" s="64" t="n"/>
+      <c r="D355" s="65" t="n"/>
+      <c r="E355" s="65" t="n"/>
+      <c r="F355" s="66" t="n"/>
     </row>
     <row r="356">
-      <c r="B356" s="57" t="n"/>
-      <c r="C356" s="58" t="n"/>
-      <c r="D356" s="59" t="n"/>
-      <c r="E356" s="59" t="n"/>
-      <c r="F356" s="60" t="n"/>
+      <c r="B356" s="63" t="n"/>
+      <c r="C356" s="64" t="n"/>
+      <c r="D356" s="65" t="n"/>
+      <c r="E356" s="65" t="n"/>
+      <c r="F356" s="66" t="n"/>
     </row>
     <row r="357">
-      <c r="B357" s="57" t="n"/>
-      <c r="C357" s="58" t="n"/>
-      <c r="D357" s="59" t="n"/>
-      <c r="E357" s="59" t="n"/>
-      <c r="F357" s="60" t="n"/>
+      <c r="B357" s="63" t="n"/>
+      <c r="C357" s="64" t="n"/>
+      <c r="D357" s="65" t="n"/>
+      <c r="E357" s="65" t="n"/>
+      <c r="F357" s="66" t="n"/>
     </row>
     <row r="358">
-      <c r="B358" s="57" t="n"/>
-      <c r="C358" s="58" t="n"/>
-      <c r="D358" s="59" t="n"/>
-      <c r="E358" s="59" t="n"/>
-      <c r="F358" s="60" t="n"/>
+      <c r="B358" s="63" t="n"/>
+      <c r="C358" s="64" t="n"/>
+      <c r="D358" s="65" t="n"/>
+      <c r="E358" s="65" t="n"/>
+      <c r="F358" s="66" t="n"/>
     </row>
     <row r="359">
-      <c r="B359" s="57" t="n"/>
-      <c r="C359" s="58" t="n"/>
-      <c r="D359" s="59" t="n"/>
-      <c r="E359" s="59" t="n"/>
-      <c r="F359" s="60" t="n"/>
+      <c r="B359" s="63" t="n"/>
+      <c r="C359" s="64" t="n"/>
+      <c r="D359" s="65" t="n"/>
+      <c r="E359" s="65" t="n"/>
+      <c r="F359" s="66" t="n"/>
     </row>
     <row r="360">
-      <c r="B360" s="57" t="n"/>
-      <c r="C360" s="58" t="n"/>
-      <c r="D360" s="59" t="n"/>
-      <c r="E360" s="59" t="n"/>
-      <c r="F360" s="60" t="n"/>
+      <c r="B360" s="63" t="n"/>
+      <c r="C360" s="64" t="n"/>
+      <c r="D360" s="65" t="n"/>
+      <c r="E360" s="65" t="n"/>
+      <c r="F360" s="66" t="n"/>
     </row>
     <row r="361">
-      <c r="B361" s="57" t="n"/>
-      <c r="C361" s="58" t="n"/>
-      <c r="D361" s="59" t="n"/>
-      <c r="E361" s="59" t="n"/>
-      <c r="F361" s="60" t="n"/>
+      <c r="B361" s="63" t="n"/>
+      <c r="C361" s="64" t="n"/>
+      <c r="D361" s="65" t="n"/>
+      <c r="E361" s="65" t="n"/>
+      <c r="F361" s="66" t="n"/>
     </row>
     <row r="362">
-      <c r="B362" s="57" t="n"/>
-      <c r="C362" s="58" t="n"/>
-      <c r="D362" s="59" t="n"/>
-      <c r="E362" s="59" t="n"/>
-      <c r="F362" s="60" t="n"/>
+      <c r="B362" s="63" t="n"/>
+      <c r="C362" s="64" t="n"/>
+      <c r="D362" s="65" t="n"/>
+      <c r="E362" s="65" t="n"/>
+      <c r="F362" s="66" t="n"/>
     </row>
     <row r="363">
-      <c r="B363" s="57" t="n"/>
-      <c r="C363" s="58" t="n"/>
-      <c r="D363" s="59" t="n"/>
-      <c r="E363" s="59" t="n"/>
-      <c r="F363" s="60" t="n"/>
+      <c r="B363" s="63" t="n"/>
+      <c r="C363" s="64" t="n"/>
+      <c r="D363" s="65" t="n"/>
+      <c r="E363" s="65" t="n"/>
+      <c r="F363" s="66" t="n"/>
     </row>
     <row r="364">
-      <c r="B364" s="57" t="n"/>
-      <c r="C364" s="58" t="n"/>
-      <c r="D364" s="59" t="n"/>
-      <c r="E364" s="59" t="n"/>
-      <c r="F364" s="60" t="n"/>
+      <c r="B364" s="63" t="n"/>
+      <c r="C364" s="64" t="n"/>
+      <c r="D364" s="65" t="n"/>
+      <c r="E364" s="65" t="n"/>
+      <c r="F364" s="66" t="n"/>
     </row>
     <row r="365">
-      <c r="B365" s="57" t="n"/>
-      <c r="C365" s="58" t="n"/>
-      <c r="D365" s="59" t="n"/>
-      <c r="E365" s="59" t="n"/>
-      <c r="F365" s="60" t="n"/>
+      <c r="B365" s="63" t="n"/>
+      <c r="C365" s="64" t="n"/>
+      <c r="D365" s="65" t="n"/>
+      <c r="E365" s="65" t="n"/>
+      <c r="F365" s="66" t="n"/>
     </row>
     <row r="366">
-      <c r="B366" s="57" t="n"/>
-      <c r="C366" s="58" t="n"/>
-      <c r="D366" s="59" t="n"/>
-      <c r="E366" s="59" t="n"/>
-      <c r="F366" s="60" t="n"/>
+      <c r="B366" s="63" t="n"/>
+      <c r="C366" s="64" t="n"/>
+      <c r="D366" s="65" t="n"/>
+      <c r="E366" s="65" t="n"/>
+      <c r="F366" s="66" t="n"/>
     </row>
     <row r="367">
-      <c r="B367" s="57" t="n"/>
-      <c r="C367" s="58" t="n"/>
-      <c r="D367" s="59" t="n"/>
-      <c r="E367" s="59" t="n"/>
-      <c r="F367" s="60" t="n"/>
+      <c r="B367" s="63" t="n"/>
+      <c r="C367" s="64" t="n"/>
+      <c r="D367" s="65" t="n"/>
+      <c r="E367" s="65" t="n"/>
+      <c r="F367" s="66" t="n"/>
     </row>
     <row r="368">
-      <c r="B368" s="57" t="n"/>
-      <c r="C368" s="58" t="n"/>
-      <c r="D368" s="59" t="n"/>
-      <c r="E368" s="59" t="n"/>
-      <c r="F368" s="60" t="n"/>
+      <c r="B368" s="63" t="n"/>
+      <c r="C368" s="64" t="n"/>
+      <c r="D368" s="65" t="n"/>
+      <c r="E368" s="65" t="n"/>
+      <c r="F368" s="66" t="n"/>
     </row>
     <row r="369">
-      <c r="B369" s="57" t="n"/>
-      <c r="C369" s="58" t="n"/>
-      <c r="D369" s="59" t="n"/>
-      <c r="E369" s="59" t="n"/>
-      <c r="F369" s="60" t="n"/>
+      <c r="B369" s="63" t="n"/>
+      <c r="C369" s="64" t="n"/>
+      <c r="D369" s="65" t="n"/>
+      <c r="E369" s="65" t="n"/>
+      <c r="F369" s="66" t="n"/>
     </row>
     <row r="370">
-      <c r="B370" s="57" t="n"/>
-      <c r="C370" s="58" t="n"/>
-      <c r="D370" s="59" t="n"/>
-      <c r="E370" s="59" t="n"/>
-      <c r="F370" s="60" t="n"/>
+      <c r="B370" s="63" t="n"/>
+      <c r="C370" s="64" t="n"/>
+      <c r="D370" s="65" t="n"/>
+      <c r="E370" s="65" t="n"/>
+      <c r="F370" s="66" t="n"/>
     </row>
     <row r="371">
-      <c r="B371" s="57" t="n"/>
-      <c r="C371" s="58" t="n"/>
-      <c r="D371" s="59" t="n"/>
-      <c r="E371" s="59" t="n"/>
-      <c r="F371" s="60" t="n"/>
+      <c r="B371" s="63" t="n"/>
+      <c r="C371" s="64" t="n"/>
+      <c r="D371" s="65" t="n"/>
+      <c r="E371" s="65" t="n"/>
+      <c r="F371" s="66" t="n"/>
     </row>
     <row r="372">
-      <c r="B372" s="57" t="n"/>
-      <c r="C372" s="58" t="n"/>
-      <c r="D372" s="59" t="n"/>
-      <c r="E372" s="59" t="n"/>
-      <c r="F372" s="60" t="n"/>
+      <c r="B372" s="63" t="n"/>
+      <c r="C372" s="64" t="n"/>
+      <c r="D372" s="65" t="n"/>
+      <c r="E372" s="65" t="n"/>
+      <c r="F372" s="66" t="n"/>
     </row>
     <row r="373">
-      <c r="B373" s="57" t="n"/>
-      <c r="C373" s="58" t="n"/>
-      <c r="D373" s="59" t="n"/>
-      <c r="E373" s="59" t="n"/>
-      <c r="F373" s="60" t="n"/>
+      <c r="B373" s="63" t="n"/>
+      <c r="C373" s="64" t="n"/>
+      <c r="D373" s="65" t="n"/>
+      <c r="E373" s="65" t="n"/>
+      <c r="F373" s="66" t="n"/>
     </row>
     <row r="374">
-      <c r="B374" s="57" t="n"/>
-      <c r="C374" s="58" t="n"/>
-      <c r="D374" s="59" t="n"/>
-      <c r="E374" s="59" t="n"/>
-      <c r="F374" s="60" t="n"/>
+      <c r="B374" s="63" t="n"/>
+      <c r="C374" s="64" t="n"/>
+      <c r="D374" s="65" t="n"/>
+      <c r="E374" s="65" t="n"/>
+      <c r="F374" s="66" t="n"/>
     </row>
     <row r="375">
-      <c r="B375" s="57" t="n"/>
-      <c r="C375" s="58" t="n"/>
-      <c r="D375" s="59" t="n"/>
-      <c r="E375" s="59" t="n"/>
-      <c r="F375" s="60" t="n"/>
+      <c r="B375" s="63" t="n"/>
+      <c r="C375" s="64" t="n"/>
+      <c r="D375" s="65" t="n"/>
+      <c r="E375" s="65" t="n"/>
+      <c r="F375" s="66" t="n"/>
     </row>
     <row r="376">
-      <c r="B376" s="57" t="n"/>
-      <c r="C376" s="58" t="n"/>
-      <c r="D376" s="59" t="n"/>
-      <c r="E376" s="59" t="n"/>
-      <c r="F376" s="60" t="n"/>
+      <c r="B376" s="63" t="n"/>
+      <c r="C376" s="64" t="n"/>
+      <c r="D376" s="65" t="n"/>
+      <c r="E376" s="65" t="n"/>
+      <c r="F376" s="66" t="n"/>
     </row>
     <row r="377">
-      <c r="B377" s="57" t="n"/>
-      <c r="C377" s="58" t="n"/>
-      <c r="D377" s="59" t="n"/>
-      <c r="E377" s="59" t="n"/>
-      <c r="F377" s="60" t="n"/>
+      <c r="B377" s="63" t="n"/>
+      <c r="C377" s="64" t="n"/>
+      <c r="D377" s="65" t="n"/>
+      <c r="E377" s="65" t="n"/>
+      <c r="F377" s="66" t="n"/>
     </row>
     <row r="378">
-      <c r="B378" s="57" t="n"/>
-      <c r="C378" s="58" t="n"/>
-      <c r="D378" s="59" t="n"/>
-      <c r="E378" s="59" t="n"/>
-      <c r="F378" s="60" t="n"/>
+      <c r="B378" s="63" t="n"/>
+      <c r="C378" s="64" t="n"/>
+      <c r="D378" s="65" t="n"/>
+      <c r="E378" s="65" t="n"/>
+      <c r="F378" s="66" t="n"/>
     </row>
     <row r="379">
-      <c r="B379" s="57" t="n"/>
-      <c r="C379" s="58" t="n"/>
-      <c r="D379" s="59" t="n"/>
-      <c r="E379" s="59" t="n"/>
-      <c r="F379" s="60" t="n"/>
+      <c r="B379" s="63" t="n"/>
+      <c r="C379" s="64" t="n"/>
+      <c r="D379" s="65" t="n"/>
+      <c r="E379" s="65" t="n"/>
+      <c r="F379" s="66" t="n"/>
     </row>
     <row r="380">
-      <c r="B380" s="57" t="n"/>
-      <c r="C380" s="58" t="n"/>
-      <c r="D380" s="59" t="n"/>
-      <c r="E380" s="59" t="n"/>
-      <c r="F380" s="60" t="n"/>
+      <c r="B380" s="63" t="n"/>
+      <c r="C380" s="64" t="n"/>
+      <c r="D380" s="65" t="n"/>
+      <c r="E380" s="65" t="n"/>
+      <c r="F380" s="66" t="n"/>
     </row>
     <row r="381">
-      <c r="B381" s="57" t="n"/>
-      <c r="C381" s="58" t="n"/>
-      <c r="D381" s="59" t="n"/>
-      <c r="E381" s="59" t="n"/>
-      <c r="F381" s="60" t="n"/>
+      <c r="B381" s="63" t="n"/>
+      <c r="C381" s="64" t="n"/>
+      <c r="D381" s="65" t="n"/>
+      <c r="E381" s="65" t="n"/>
+      <c r="F381" s="66" t="n"/>
     </row>
     <row r="382">
-      <c r="B382" s="57" t="n"/>
-      <c r="C382" s="58" t="n"/>
-      <c r="D382" s="59" t="n"/>
-      <c r="E382" s="59" t="n"/>
-      <c r="F382" s="60" t="n"/>
+      <c r="B382" s="63" t="n"/>
+      <c r="C382" s="64" t="n"/>
+      <c r="D382" s="65" t="n"/>
+      <c r="E382" s="65" t="n"/>
+      <c r="F382" s="66" t="n"/>
     </row>
     <row r="383">
-      <c r="B383" s="57" t="n"/>
-      <c r="C383" s="58" t="n"/>
-      <c r="D383" s="59" t="n"/>
-      <c r="E383" s="59" t="n"/>
-      <c r="F383" s="60" t="n"/>
+      <c r="B383" s="63" t="n"/>
+      <c r="C383" s="64" t="n"/>
+      <c r="D383" s="65" t="n"/>
+      <c r="E383" s="65" t="n"/>
+      <c r="F383" s="66" t="n"/>
     </row>
     <row r="384">
-      <c r="B384" s="57" t="n"/>
-      <c r="C384" s="58" t="n"/>
-      <c r="D384" s="59" t="n"/>
-      <c r="E384" s="59" t="n"/>
-      <c r="F384" s="60" t="n"/>
+      <c r="B384" s="63" t="n"/>
+      <c r="C384" s="64" t="n"/>
+      <c r="D384" s="65" t="n"/>
+      <c r="E384" s="65" t="n"/>
+      <c r="F384" s="66" t="n"/>
     </row>
     <row r="385">
-      <c r="B385" s="57" t="n"/>
-      <c r="C385" s="58" t="n"/>
-      <c r="D385" s="59" t="n"/>
-      <c r="E385" s="59" t="n"/>
-      <c r="F385" s="60" t="n"/>
+      <c r="B385" s="63" t="n"/>
+      <c r="C385" s="64" t="n"/>
+      <c r="D385" s="65" t="n"/>
+      <c r="E385" s="65" t="n"/>
+      <c r="F385" s="66" t="n"/>
     </row>
     <row r="386">
-      <c r="B386" s="57" t="n"/>
-      <c r="C386" s="58" t="n"/>
-      <c r="D386" s="59" t="n"/>
-      <c r="E386" s="59" t="n"/>
-      <c r="F386" s="60" t="n"/>
+      <c r="B386" s="63" t="n"/>
+      <c r="C386" s="64" t="n"/>
+      <c r="D386" s="65" t="n"/>
+      <c r="E386" s="65" t="n"/>
+      <c r="F386" s="66" t="n"/>
     </row>
     <row r="387">
-      <c r="B387" s="57" t="n"/>
-      <c r="C387" s="58" t="n"/>
-      <c r="D387" s="59" t="n"/>
-      <c r="E387" s="59" t="n"/>
-      <c r="F387" s="60" t="n"/>
+      <c r="B387" s="63" t="n"/>
+      <c r="C387" s="64" t="n"/>
+      <c r="D387" s="65" t="n"/>
+      <c r="E387" s="65" t="n"/>
+      <c r="F387" s="66" t="n"/>
     </row>
     <row r="388">
-      <c r="B388" s="57" t="n"/>
-      <c r="C388" s="58" t="n"/>
-      <c r="D388" s="59" t="n"/>
-      <c r="E388" s="59" t="n"/>
-      <c r="F388" s="60" t="n"/>
+      <c r="B388" s="63" t="n"/>
+      <c r="C388" s="64" t="n"/>
+      <c r="D388" s="65" t="n"/>
+      <c r="E388" s="65" t="n"/>
+      <c r="F388" s="66" t="n"/>
     </row>
     <row r="389">
-      <c r="B389" s="57" t="n"/>
-      <c r="C389" s="58" t="n"/>
-      <c r="D389" s="59" t="n"/>
-      <c r="E389" s="59" t="n"/>
-      <c r="F389" s="60" t="n"/>
+      <c r="B389" s="63" t="n"/>
+      <c r="C389" s="64" t="n"/>
+      <c r="D389" s="65" t="n"/>
+      <c r="E389" s="65" t="n"/>
+      <c r="F389" s="66" t="n"/>
     </row>
     <row r="390">
-      <c r="B390" s="57" t="n"/>
-      <c r="C390" s="58" t="n"/>
-      <c r="D390" s="59" t="n"/>
-      <c r="E390" s="59" t="n"/>
-      <c r="F390" s="60" t="n"/>
+      <c r="B390" s="63" t="n"/>
+      <c r="C390" s="64" t="n"/>
+      <c r="D390" s="65" t="n"/>
+      <c r="E390" s="65" t="n"/>
+      <c r="F390" s="66" t="n"/>
     </row>
     <row r="391">
-      <c r="B391" s="57" t="n"/>
-      <c r="C391" s="58" t="n"/>
-      <c r="D391" s="59" t="n"/>
-      <c r="E391" s="59" t="n"/>
-      <c r="F391" s="60" t="n"/>
+      <c r="B391" s="63" t="n"/>
+      <c r="C391" s="64" t="n"/>
+      <c r="D391" s="65" t="n"/>
+      <c r="E391" s="65" t="n"/>
+      <c r="F391" s="66" t="n"/>
     </row>
     <row r="392">
-      <c r="B392" s="57" t="n"/>
-      <c r="C392" s="58" t="n"/>
-      <c r="D392" s="59" t="n"/>
-      <c r="E392" s="59" t="n"/>
-      <c r="F392" s="60" t="n"/>
+      <c r="B392" s="63" t="n"/>
+      <c r="C392" s="64" t="n"/>
+      <c r="D392" s="65" t="n"/>
+      <c r="E392" s="65" t="n"/>
+      <c r="F392" s="66" t="n"/>
     </row>
     <row r="393">
-      <c r="B393" s="57" t="n"/>
-      <c r="C393" s="58" t="n"/>
-      <c r="D393" s="59" t="n"/>
-      <c r="E393" s="59" t="n"/>
-      <c r="F393" s="60" t="n"/>
+      <c r="B393" s="63" t="n"/>
+      <c r="C393" s="64" t="n"/>
+      <c r="D393" s="65" t="n"/>
+      <c r="E393" s="65" t="n"/>
+      <c r="F393" s="66" t="n"/>
     </row>
     <row r="394">
-      <c r="B394" s="57" t="n"/>
-      <c r="C394" s="58" t="n"/>
-      <c r="D394" s="59" t="n"/>
-      <c r="E394" s="59" t="n"/>
-      <c r="F394" s="60" t="n"/>
+      <c r="B394" s="63" t="n"/>
+      <c r="C394" s="64" t="n"/>
+      <c r="D394" s="65" t="n"/>
+      <c r="E394" s="65" t="n"/>
+      <c r="F394" s="66" t="n"/>
     </row>
     <row r="395">
-      <c r="B395" s="57" t="n"/>
-      <c r="C395" s="58" t="n"/>
-      <c r="D395" s="59" t="n"/>
-      <c r="E395" s="59" t="n"/>
-      <c r="F395" s="60" t="n"/>
+      <c r="B395" s="63" t="n"/>
+      <c r="C395" s="64" t="n"/>
+      <c r="D395" s="65" t="n"/>
+      <c r="E395" s="65" t="n"/>
+      <c r="F395" s="66" t="n"/>
     </row>
     <row r="396">
-      <c r="B396" s="57" t="n"/>
-      <c r="C396" s="58" t="n"/>
-      <c r="D396" s="59" t="n"/>
-      <c r="E396" s="59" t="n"/>
-      <c r="F396" s="60" t="n"/>
+      <c r="B396" s="63" t="n"/>
+      <c r="C396" s="64" t="n"/>
+      <c r="D396" s="65" t="n"/>
+      <c r="E396" s="65" t="n"/>
+      <c r="F396" s="66" t="n"/>
     </row>
     <row r="397">
-      <c r="B397" s="57" t="n"/>
-      <c r="C397" s="58" t="n"/>
-      <c r="D397" s="59" t="n"/>
-      <c r="E397" s="59" t="n"/>
-      <c r="F397" s="60" t="n"/>
+      <c r="B397" s="63" t="n"/>
+      <c r="C397" s="64" t="n"/>
+      <c r="D397" s="65" t="n"/>
+      <c r="E397" s="65" t="n"/>
+      <c r="F397" s="66" t="n"/>
     </row>
     <row r="398">
-      <c r="B398" s="57" t="n"/>
-      <c r="C398" s="58" t="n"/>
-      <c r="D398" s="59" t="n"/>
-      <c r="E398" s="59" t="n"/>
-      <c r="F398" s="60" t="n"/>
+      <c r="B398" s="63" t="n"/>
+      <c r="C398" s="64" t="n"/>
+      <c r="D398" s="65" t="n"/>
+      <c r="E398" s="65" t="n"/>
+      <c r="F398" s="66" t="n"/>
     </row>
     <row r="399">
-      <c r="B399" s="57" t="n"/>
-      <c r="C399" s="58" t="n"/>
-      <c r="D399" s="59" t="n"/>
-      <c r="E399" s="59" t="n"/>
-      <c r="F399" s="60" t="n"/>
+      <c r="B399" s="63" t="n"/>
+      <c r="C399" s="64" t="n"/>
+      <c r="D399" s="65" t="n"/>
+      <c r="E399" s="65" t="n"/>
+      <c r="F399" s="66" t="n"/>
     </row>
     <row r="400">
-      <c r="B400" s="57" t="n"/>
-      <c r="C400" s="58" t="n"/>
-      <c r="D400" s="59" t="n"/>
-      <c r="E400" s="59" t="n"/>
-      <c r="F400" s="60" t="n"/>
+      <c r="B400" s="63" t="n"/>
+      <c r="C400" s="64" t="n"/>
+      <c r="D400" s="65" t="n"/>
+      <c r="E400" s="65" t="n"/>
+      <c r="F400" s="66" t="n"/>
     </row>
     <row r="401">
-      <c r="B401" s="57" t="n"/>
-      <c r="C401" s="58" t="n"/>
-      <c r="D401" s="59" t="n"/>
-      <c r="E401" s="59" t="n"/>
-      <c r="F401" s="60" t="n"/>
+      <c r="B401" s="63" t="n"/>
+      <c r="C401" s="64" t="n"/>
+      <c r="D401" s="65" t="n"/>
+      <c r="E401" s="65" t="n"/>
+      <c r="F401" s="66" t="n"/>
     </row>
     <row r="402">
-      <c r="B402" s="57" t="n"/>
-      <c r="C402" s="58" t="n"/>
-      <c r="D402" s="59" t="n"/>
-      <c r="E402" s="59" t="n"/>
-      <c r="F402" s="60" t="n"/>
+      <c r="B402" s="63" t="n"/>
+      <c r="C402" s="64" t="n"/>
+      <c r="D402" s="65" t="n"/>
+      <c r="E402" s="65" t="n"/>
+      <c r="F402" s="66" t="n"/>
     </row>
     <row r="403">
-      <c r="B403" s="57" t="n"/>
-      <c r="C403" s="58" t="n"/>
-      <c r="D403" s="59" t="n"/>
-      <c r="E403" s="59" t="n"/>
-      <c r="F403" s="60" t="n"/>
+      <c r="B403" s="63" t="n"/>
+      <c r="C403" s="64" t="n"/>
+      <c r="D403" s="65" t="n"/>
+      <c r="E403" s="65" t="n"/>
+      <c r="F403" s="66" t="n"/>
     </row>
     <row r="404">
-      <c r="B404" s="57" t="n"/>
-      <c r="C404" s="58" t="n"/>
-      <c r="D404" s="59" t="n"/>
-      <c r="E404" s="59" t="n"/>
-      <c r="F404" s="60" t="n"/>
+      <c r="B404" s="63" t="n"/>
+      <c r="C404" s="64" t="n"/>
+      <c r="D404" s="65" t="n"/>
+      <c r="E404" s="65" t="n"/>
+      <c r="F404" s="66" t="n"/>
     </row>
     <row r="405">
-      <c r="B405" s="57" t="n"/>
-      <c r="C405" s="58" t="n"/>
-      <c r="D405" s="59" t="n"/>
-      <c r="E405" s="59" t="n"/>
-      <c r="F405" s="60" t="n"/>
+      <c r="B405" s="63" t="n"/>
+      <c r="C405" s="64" t="n"/>
+      <c r="D405" s="65" t="n"/>
+      <c r="E405" s="65" t="n"/>
+      <c r="F405" s="66" t="n"/>
     </row>
     <row r="406">
-      <c r="B406" s="57" t="n"/>
-      <c r="C406" s="58" t="n"/>
-      <c r="D406" s="59" t="n"/>
-      <c r="E406" s="59" t="n"/>
-      <c r="F406" s="60" t="n"/>
+      <c r="B406" s="63" t="n"/>
+      <c r="C406" s="64" t="n"/>
+      <c r="D406" s="65" t="n"/>
+      <c r="E406" s="65" t="n"/>
+      <c r="F406" s="66" t="n"/>
     </row>
     <row r="408" ht="8" customHeight="1">
-      <c r="B408" s="52" t="n"/>
+      <c r="B408" s="58" t="n"/>
     </row>
     <row r="409" ht="16" customHeight="1">
-      <c r="B409" s="53" t="inlineStr">
+      <c r="B409" s="59" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="410" ht="16" customHeight="1">
-      <c r="B410" s="54" t="inlineStr">
+      <c r="B410" s="60" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Para gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY  →  mixshopdigital.com.py</t>
         </is>
@@ -5325,12 +5501,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="89C1"/>
   <autoFilter ref="B6:F406"/>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="B408:F408"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B410:F410"/>
     <mergeCell ref="B1:C1"/>
@@ -5380,6 +5555,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5399,260 +5575,259 @@
     <col width="56" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>AJUSTES</t>
         </is>
       </c>
+      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Cargalos una sola vez</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="10" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>← PANEL</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Completá solamente las celdas amarillas. Estos datos alimentan el PANEL automáticamente.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>1. TU NEGOCIO</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="67" t="inlineStr">
         <is>
           <t>Nombre del negocio</t>
         </is>
       </c>
-      <c r="C7" s="62" t="inlineStr">
+      <c r="C7" s="68" t="inlineStr">
         <is>
           <t>Mi negocio</t>
         </is>
       </c>
-      <c r="D7" s="51" t="inlineStr">
+      <c r="D7" s="57" t="inlineStr">
         <is>
           <t>Aparece en el PANEL.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="67" t="inlineStr">
         <is>
           <t>Año a controlar</t>
         </is>
       </c>
-      <c r="C8" s="63" t="n">
+      <c r="C8" s="69" t="n">
         <v>2026</v>
       </c>
-      <c r="D8" s="51" t="inlineStr">
+      <c r="D8" s="57" t="inlineStr">
         <is>
           <t>El PANEL muestra los 12 meses de este año. Los movimientos de otros años se ignoran.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="67" t="inlineStr">
         <is>
           <t>Moneda</t>
         </is>
       </c>
-      <c r="C9" s="62" t="inlineStr">
+      <c r="C9" s="68" t="inlineStr">
         <is>
           <t>Gs.</t>
         </is>
       </c>
-      <c r="D9" s="51" t="inlineStr">
+      <c r="D9" s="57" t="inlineStr">
         <is>
           <t>Símbolo que se muestra en el PANEL.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>Meta de ganancia por mes</t>
         </is>
       </c>
-      <c r="C10" s="64" t="n">
+      <c r="C10" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="51" t="inlineStr">
+      <c r="D10" s="57" t="inlineStr">
         <is>
           <t>Cuánto querés ganar por mes. El PANEL te muestra cuánto te falta. Si no tenés meta, dejala en 0.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="52" t="inlineStr">
         <is>
           <t>2. TUS CATEGORÍAS (podés renombrarlas)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Se usan en las listas desplegables de MOVIMIENTOS. Cambiá el nombre, pero no dejes huecos entre medio.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Categorías de INGRESO</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>Categorías de GASTO</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="62" t="inlineStr">
+      <c r="B15" s="68" t="inlineStr">
         <is>
           <t>Ventas de productos</t>
         </is>
       </c>
-      <c r="C15" s="62" t="inlineStr">
+      <c r="C15" s="68" t="inlineStr">
         <is>
           <t>Mercadería e insumos</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Ingresos: hasta 6 categorías.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="68" t="inlineStr">
         <is>
           <t>Ventas de servicios</t>
         </is>
       </c>
-      <c r="C16" s="62" t="inlineStr">
+      <c r="C16" s="68" t="inlineStr">
         <is>
           <t>Alquiler</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Gastos: hasta 10 categorías (el PANEL las muestra todas).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="62" t="inlineStr">
+      <c r="B17" s="68" t="inlineStr">
         <is>
           <t>Ventas online</t>
         </is>
       </c>
-      <c r="C17" s="62" t="inlineStr">
+      <c r="C17" s="68" t="inlineStr">
         <is>
           <t>Servicios (luz, agua, internet)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="62" t="inlineStr">
+      <c r="B18" s="68" t="inlineStr">
         <is>
           <t>Otros ingresos</t>
         </is>
       </c>
-      <c r="C18" s="62" t="inlineStr">
+      <c r="C18" s="68" t="inlineStr">
         <is>
           <t>Sueldos y mano de obra</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="62" t="n"/>
-      <c r="C19" s="62" t="inlineStr">
+      <c r="B19" s="68" t="n"/>
+      <c r="C19" s="68" t="inlineStr">
         <is>
           <t>Publicidad</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="62" t="n"/>
-      <c r="C20" s="62" t="inlineStr">
+      <c r="B20" s="68" t="n"/>
+      <c r="C20" s="68" t="inlineStr">
         <is>
           <t>Transporte y envíos</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="65" t="n"/>
-      <c r="C21" s="62" t="inlineStr">
+      <c r="B21" s="71" t="n"/>
+      <c r="C21" s="68" t="inlineStr">
         <is>
           <t>Impuestos</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="65" t="n"/>
-      <c r="C22" s="62" t="inlineStr">
+      <c r="B22" s="71" t="n"/>
+      <c r="C22" s="68" t="inlineStr">
         <is>
           <t>Comisiones y bancos</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="65" t="n"/>
-      <c r="C23" s="62" t="inlineStr">
+      <c r="B23" s="71" t="n"/>
+      <c r="C23" s="68" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="65" t="n"/>
-      <c r="C24" s="62" t="inlineStr">
+      <c r="B24" s="71" t="n"/>
+      <c r="C24" s="68" t="inlineStr">
         <is>
           <t>Otros gastos</t>
         </is>
       </c>
     </row>
     <row r="27" ht="8" customHeight="1">
-      <c r="B27" s="52" t="n"/>
+      <c r="B27" s="58" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="53" t="inlineStr">
+      <c r="B28" s="59" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="54" t="inlineStr">
+      <c r="B29" s="60" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Para gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY  →  mixshopdigital.com.py</t>
         </is>
@@ -5660,9 +5835,8 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="89C1"/>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B3:D3"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C1:D1"/>
@@ -5698,6 +5872,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5721,197 +5896,204 @@
     <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>AYUDA</t>
         </is>
       </c>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Se aprende en 2 minutos</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>← PANEL</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Leé esta hoja una vez. Después ya no la vas a necesitar.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>¿PARA QUÉ SIRVE?</t>
         </is>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1">
-      <c r="B7" s="66" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Para saber cuánto vendés, cuánto gastás y cuánto te queda, mes por mes. Sin fórmulas, sin Internet y sin saber Excel.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="46" t="inlineStr">
+      <c r="B9" s="52" t="inlineStr">
         <is>
           <t>EMPEZÁ EN 3 PASOS</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18.5" customHeight="1">
-      <c r="B10" s="66" t="inlineStr">
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>1) En AJUSTES poné el nombre de tu negocio, el año que querés controlar y tu meta de ganancia mensual.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="B11" s="66" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>2) En MOVIMIENTOS anotá cada venta (Ingreso) y cada gasto (Gasto): fecha, tipo, categoría y monto. Una fila por movimiento.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18.5" customHeight="1">
-      <c r="B12" s="66" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>3) Mirá el PANEL: se actualiza solo con tarjetas, gráficos y un mensaje que te dice cómo vas.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>COLORES</t>
         </is>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1">
-      <c r="B15" s="66" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Amarillo: celdas que completás vos.   Gris o blanco: se calcula solo (bloqueado).   Verde: ganancia.   Coral: gastos.   Rojo: pérdida.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="52" t="inlineStr">
         <is>
           <t>PREGUNTAS FRECUENTES</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18.5" customHeight="1">
-      <c r="B18" s="66" t="inlineStr">
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>• Veo todo en cero: hacé clic en «Habilitar edición» en la barra amarilla de Excel.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="33" customHeight="1">
-      <c r="B19" s="66" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>• ¿El monto de un gasto va con signo menos? No. Escribí siempre el monto en positivo; el Tipo (Ingreso o Gasto) dice si entra o sale.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="33" customHeight="1">
-      <c r="B20" s="66" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>• ¿Por qué un movimiento no aparece? Revisá que la fecha sea del año elegido en AJUSTES y que el Tipo esté cargado. Los de otros años se ven en gris.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18.5" customHeight="1">
-      <c r="B21" s="66" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>• ¿Cómo cambio las categorías? En AJUSTES, escribiendo encima del nombre.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18.5" customHeight="1">
-      <c r="B22" s="66" t="inlineStr">
+      <c r="B22" s="72" t="inlineStr">
         <is>
           <t>• ¿Cuántos movimientos entran? 400 filas. Cuando se llene, duplicá el archivo y usá otro por año.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33" customHeight="1">
-      <c r="B23" s="66" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>• Solo se editan las celdas amarillas: el resto está protegido para que no se rompan las fórmulas por accidente.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="46" t="inlineStr">
+      <c r="B25" s="52" t="inlineStr">
         <is>
           <t>SOBRE LA PROTECCIÓN</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33" customHeight="1">
-      <c r="B26" s="66" t="inlineStr">
+      <c r="B26" s="72" t="inlineStr">
         <is>
           <t>La protección de Excel evita borrados accidentales, pero no es un sistema de seguridad criptográfico. La marca de Mix Shop Digital en encabezados y pies funciona del mismo modo.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="67" t="inlineStr">
+      <c r="B28" s="73" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL Y MI NEGOCIO PY</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33" customHeight="1">
-      <c r="B29" s="66" t="inlineStr">
+      <c r="B29" s="72" t="inlineStr">
         <is>
           <t>Esta planilla es una herramienta gratuita de Mix Shop Digital. Si querés gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY, el sistema de gestión para pequeños negocios de Paraguay.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="68" t="inlineStr">
+      <c r="B30" s="74" t="inlineStr">
         <is>
           <t>→ mixshopdigital.com.py</t>
         </is>
       </c>
     </row>
     <row r="32" ht="8" customHeight="1">
-      <c r="B32" s="52" t="n"/>
+      <c r="B32" s="58" t="n"/>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="53" t="inlineStr">
+      <c r="B33" s="59" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="54" t="inlineStr">
+      <c r="B34" s="60" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Para gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY  →  mixshopdigital.com.py</t>
         </is>
@@ -5919,7 +6101,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="89C1"/>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="B6:H6"/>
@@ -5934,7 +6116,6 @@
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B3:H3"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="B21:H21"/>
@@ -5966,5 +6147,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>